--- a/PTS44/source_data/PTS44_scenario_data.xlsx
+++ b/PTS44/source_data/PTS44_scenario_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -669,13 +669,13 @@
         <v>163.1557176549866</v>
       </c>
       <c r="C4" t="n">
-        <v>58.77656081754736</v>
+        <v>56.7488976400837</v>
       </c>
       <c r="D4" t="n">
-        <v>163.1557176549866</v>
+        <v>183.5266913746631</v>
       </c>
       <c r="E4" t="n">
-        <v>58.77656081754736</v>
+        <v>58.06136886770518</v>
       </c>
       <c r="F4" t="n">
         <v>29.16866840731072</v>
@@ -698,13 +698,13 @@
         <v>163.0490633423181</v>
       </c>
       <c r="C5" t="n">
-        <v>58.81321934197408</v>
+        <v>56.62958207393629</v>
       </c>
       <c r="D5" t="n">
-        <v>163.0490633423181</v>
+        <v>183.4200370619946</v>
       </c>
       <c r="E5" t="n">
-        <v>58.81321934197408</v>
+        <v>57.94205330155778</v>
       </c>
       <c r="F5" t="n">
         <v>28.36778067885118</v>
@@ -727,13 +727,13 @@
         <v>162.9424090296496</v>
       </c>
       <c r="C6" t="n">
-        <v>58.8498778664008</v>
+        <v>56.51026650778888</v>
       </c>
       <c r="D6" t="n">
-        <v>162.9424090296496</v>
+        <v>183.3133827493262</v>
       </c>
       <c r="E6" t="n">
-        <v>58.8498778664008</v>
+        <v>57.82273773541036</v>
       </c>
       <c r="F6" t="n">
         <v>27.56689295039166</v>
@@ -756,13 +756,13 @@
         <v>162.8357547169812</v>
       </c>
       <c r="C7" t="n">
-        <v>58.88653639082752</v>
+        <v>56.39095094164148</v>
       </c>
       <c r="D7" t="n">
-        <v>162.8357547169812</v>
+        <v>183.2067284366577</v>
       </c>
       <c r="E7" t="n">
-        <v>58.88653639082752</v>
+        <v>57.70342216926296</v>
       </c>
       <c r="F7" t="n">
         <v>26.76600522193212</v>
@@ -785,13 +785,13 @@
         <v>162.7291004043127</v>
       </c>
       <c r="C8" t="n">
-        <v>58.92319491525424</v>
+        <v>56.27163537549407</v>
       </c>
       <c r="D8" t="n">
-        <v>162.7291004043127</v>
+        <v>183.1000741239892</v>
       </c>
       <c r="E8" t="n">
-        <v>58.92319491525424</v>
+        <v>57.58410660311555</v>
       </c>
       <c r="F8" t="n">
         <v>25.96511749347258</v>
@@ -814,13 +814,13 @@
         <v>162.6224460916443</v>
       </c>
       <c r="C9" t="n">
-        <v>58.95985343968096</v>
+        <v>56.15231980934666</v>
       </c>
       <c r="D9" t="n">
-        <v>162.6224460916443</v>
+        <v>182.9934198113208</v>
       </c>
       <c r="E9" t="n">
-        <v>58.95985343968096</v>
+        <v>57.46479103696814</v>
       </c>
       <c r="F9" t="n">
         <v>25.16422976501306</v>
@@ -843,13 +843,13 @@
         <v>162.5157917789758</v>
       </c>
       <c r="C10" t="n">
-        <v>58.99651196410768</v>
+        <v>56.03300424319925</v>
       </c>
       <c r="D10" t="n">
-        <v>162.5157917789758</v>
+        <v>182.8867654986523</v>
       </c>
       <c r="E10" t="n">
-        <v>58.99651196410768</v>
+        <v>57.34547547082074</v>
       </c>
       <c r="F10" t="n">
         <v>24.36334203655352</v>
@@ -872,13 +872,13 @@
         <v>162.4091374663073</v>
       </c>
       <c r="C11" t="n">
-        <v>59.0331704885344</v>
+        <v>55.91368867705184</v>
       </c>
       <c r="D11" t="n">
-        <v>162.4091374663073</v>
+        <v>182.7801111859838</v>
       </c>
       <c r="E11" t="n">
-        <v>59.0331704885344</v>
+        <v>57.22615990467333</v>
       </c>
       <c r="F11" t="n">
         <v>23.562454308094</v>
@@ -901,13 +901,13 @@
         <v>162.3024831536389</v>
       </c>
       <c r="C12" t="n">
-        <v>59.06982901296112</v>
+        <v>55.79437311090444</v>
       </c>
       <c r="D12" t="n">
-        <v>162.3024831536389</v>
+        <v>182.6734568733154</v>
       </c>
       <c r="E12" t="n">
-        <v>59.06982901296112</v>
+        <v>57.10684433852592</v>
       </c>
       <c r="F12" t="n">
         <v>22.76156657963446</v>
@@ -930,13 +930,13 @@
         <v>162.1958288409704</v>
       </c>
       <c r="C13" t="n">
-        <v>59.10648753738784</v>
+        <v>55.67505754475703</v>
       </c>
       <c r="D13" t="n">
-        <v>162.1958288409704</v>
+        <v>182.5668025606469</v>
       </c>
       <c r="E13" t="n">
-        <v>59.10648753738784</v>
+        <v>56.98752877237851</v>
       </c>
       <c r="F13" t="n">
         <v>21.96067885117495</v>
@@ -959,13 +959,13 @@
         <v>162.089174528302</v>
       </c>
       <c r="C14" t="n">
-        <v>59.14314606181456</v>
+        <v>55.55574197860962</v>
       </c>
       <c r="D14" t="n">
-        <v>162.089174528302</v>
+        <v>182.4601482479785</v>
       </c>
       <c r="E14" t="n">
-        <v>59.14314606181456</v>
+        <v>56.8682132062311</v>
       </c>
       <c r="F14" t="n">
         <v>21.1597911227154</v>
@@ -988,13 +988,13 @@
         <v>161.9825202156335</v>
       </c>
       <c r="C15" t="n">
-        <v>59.17980458624127</v>
+        <v>55.43642641246222</v>
       </c>
       <c r="D15" t="n">
-        <v>161.9825202156335</v>
+        <v>182.35349393531</v>
       </c>
       <c r="E15" t="n">
-        <v>59.17980458624127</v>
+        <v>56.7488976400837</v>
       </c>
       <c r="F15" t="n">
         <v>20.35890339425589</v>
@@ -1017,13 +1017,13 @@
         <v>161.875865902965</v>
       </c>
       <c r="C16" t="n">
-        <v>59.21646311066799</v>
+        <v>55.3171108463148</v>
       </c>
       <c r="D16" t="n">
-        <v>161.875865902965</v>
+        <v>182.2468396226415</v>
       </c>
       <c r="E16" t="n">
-        <v>59.21646311066799</v>
+        <v>56.62958207393629</v>
       </c>
       <c r="F16" t="n">
         <v>19.55801566579635</v>
@@ -1046,13 +1046,13 @@
         <v>161.7692115902965</v>
       </c>
       <c r="C17" t="n">
-        <v>59.25312163509471</v>
+        <v>55.1977952801674</v>
       </c>
       <c r="D17" t="n">
-        <v>161.7692115902965</v>
+        <v>182.140185309973</v>
       </c>
       <c r="E17" t="n">
-        <v>59.25312163509471</v>
+        <v>56.51026650778888</v>
       </c>
       <c r="F17" t="n">
         <v>18.75712793733683</v>
@@ -1075,13 +1075,13 @@
         <v>161.6625572776281</v>
       </c>
       <c r="C18" t="n">
-        <v>59.28978015952143</v>
+        <v>55.07847971401999</v>
       </c>
       <c r="D18" t="n">
-        <v>161.6625572776281</v>
+        <v>182.0335309973046</v>
       </c>
       <c r="E18" t="n">
-        <v>59.28978015952143</v>
+        <v>56.39095094164148</v>
       </c>
       <c r="F18" t="n">
         <v>17.95624020887729</v>
@@ -1104,13 +1104,13 @@
         <v>161.5559029649596</v>
       </c>
       <c r="C19" t="n">
-        <v>59.32643868394815</v>
+        <v>54.95916414787258</v>
       </c>
       <c r="D19" t="n">
-        <v>161.5559029649596</v>
+        <v>181.9268766846361</v>
       </c>
       <c r="E19" t="n">
-        <v>59.32643868394815</v>
+        <v>56.27163537549407</v>
       </c>
       <c r="F19" t="n">
         <v>17.15535248041775</v>
@@ -1133,13 +1133,13 @@
         <v>161.4492486522912</v>
       </c>
       <c r="C20" t="n">
-        <v>59.36309720837487</v>
+        <v>54.83984858172518</v>
       </c>
       <c r="D20" t="n">
-        <v>161.4492486522912</v>
+        <v>181.8202223719677</v>
       </c>
       <c r="E20" t="n">
-        <v>59.36309720837487</v>
+        <v>56.15231980934666</v>
       </c>
       <c r="F20" t="n">
         <v>16.35446475195823</v>
@@ -1162,13 +1162,13 @@
         <v>161.3425943396227</v>
       </c>
       <c r="C21" t="n">
-        <v>59.39975573280159</v>
+        <v>54.72053301557777</v>
       </c>
       <c r="D21" t="n">
-        <v>161.3425943396227</v>
+        <v>181.7135680592992</v>
       </c>
       <c r="E21" t="n">
-        <v>59.39975573280159</v>
+        <v>56.03300424319925</v>
       </c>
       <c r="F21" t="n">
         <v>15.55357702349869</v>
@@ -1191,13 +1191,13 @@
         <v>161.2359400269542</v>
       </c>
       <c r="C22" t="n">
-        <v>59.43641425722831</v>
+        <v>54.60121744943037</v>
       </c>
       <c r="D22" t="n">
-        <v>161.2359400269542</v>
+        <v>181.6069137466307</v>
       </c>
       <c r="E22" t="n">
-        <v>59.43641425722831</v>
+        <v>55.91368867705184</v>
       </c>
       <c r="F22" t="n">
         <v>14.75268929503918</v>
@@ -1220,13 +1220,13 @@
         <v>161.1292857142858</v>
       </c>
       <c r="C23" t="n">
-        <v>59.47307278165503</v>
+        <v>54.48190188328295</v>
       </c>
       <c r="D23" t="n">
-        <v>161.1292857142858</v>
+        <v>181.5002594339623</v>
       </c>
       <c r="E23" t="n">
-        <v>59.47307278165503</v>
+        <v>55.79437311090444</v>
       </c>
       <c r="F23" t="n">
         <v>13.95180156657963</v>
@@ -1249,13 +1249,13 @@
         <v>161.0226314016173</v>
       </c>
       <c r="C24" t="n">
-        <v>59.50973130608175</v>
+        <v>54.36258631713554</v>
       </c>
       <c r="D24" t="n">
-        <v>161.0226314016173</v>
+        <v>181.3936051212938</v>
       </c>
       <c r="E24" t="n">
-        <v>59.50973130608175</v>
+        <v>55.67505754475703</v>
       </c>
       <c r="F24" t="n">
         <v>13.15091383812012</v>
@@ -1278,13 +1278,13 @@
         <v>160.9159770889489</v>
       </c>
       <c r="C25" t="n">
-        <v>59.54638983050847</v>
+        <v>54.24327075098814</v>
       </c>
       <c r="D25" t="n">
-        <v>160.9159770889489</v>
+        <v>181.2869508086254</v>
       </c>
       <c r="E25" t="n">
-        <v>59.54638983050847</v>
+        <v>55.55574197860962</v>
       </c>
       <c r="F25" t="n">
         <v>12.35002610966058</v>
@@ -1307,13 +1307,13 @@
         <v>160.8093227762804</v>
       </c>
       <c r="C26" t="n">
-        <v>59.58304835493519</v>
+        <v>54.12395518484073</v>
       </c>
       <c r="D26" t="n">
-        <v>160.8093227762804</v>
+        <v>181.1802964959569</v>
       </c>
       <c r="E26" t="n">
-        <v>59.58304835493519</v>
+        <v>55.43642641246222</v>
       </c>
       <c r="F26" t="n">
         <v>11.54913838120106</v>
@@ -1336,13 +1336,13 @@
         <v>160.7026684636119</v>
       </c>
       <c r="C27" t="n">
-        <v>59.61970687936191</v>
+        <v>54.00463961869333</v>
       </c>
       <c r="D27" t="n">
-        <v>160.7026684636119</v>
+        <v>181.0736421832884</v>
       </c>
       <c r="E27" t="n">
-        <v>59.61970687936191</v>
+        <v>55.3171108463148</v>
       </c>
       <c r="F27" t="n">
         <v>10.74825065274152</v>
@@ -1365,13 +1365,13 @@
         <v>160.5960141509435</v>
       </c>
       <c r="C28" t="n">
-        <v>59.65636540378863</v>
+        <v>53.88532405254592</v>
       </c>
       <c r="D28" t="n">
-        <v>160.5960141509435</v>
+        <v>180.96698787062</v>
       </c>
       <c r="E28" t="n">
-        <v>59.65636540378863</v>
+        <v>55.1977952801674</v>
       </c>
       <c r="F28" t="n">
         <v>9.947362924281975</v>
@@ -1394,13 +1394,13 @@
         <v>160.489359838275</v>
       </c>
       <c r="C29" t="n">
-        <v>59.69302392821535</v>
+        <v>53.76600848639851</v>
       </c>
       <c r="D29" t="n">
-        <v>160.489359838275</v>
+        <v>180.8603335579515</v>
       </c>
       <c r="E29" t="n">
-        <v>59.69302392821535</v>
+        <v>55.07847971401999</v>
       </c>
       <c r="F29" t="n">
         <v>9.146475195822461</v>
@@ -1423,13 +1423,13 @@
         <v>160.3827055256065</v>
       </c>
       <c r="C30" t="n">
-        <v>59.72968245264207</v>
+        <v>53.6466929202511</v>
       </c>
       <c r="D30" t="n">
-        <v>160.3827055256065</v>
+        <v>180.753679245283</v>
       </c>
       <c r="E30" t="n">
-        <v>59.72968245264207</v>
+        <v>54.95916414787258</v>
       </c>
       <c r="F30" t="n">
         <v>8.345587467362918</v>
@@ -1452,13 +1452,13 @@
         <v>160.2760512129381</v>
       </c>
       <c r="C31" t="n">
-        <v>59.76634097706879</v>
+        <v>53.52737735410369</v>
       </c>
       <c r="D31" t="n">
-        <v>160.2760512129381</v>
+        <v>180.6470249326146</v>
       </c>
       <c r="E31" t="n">
-        <v>59.76634097706879</v>
+        <v>54.83984858172518</v>
       </c>
       <c r="F31" t="n">
         <v>7.544699738903404</v>
@@ -1481,13 +1481,13 @@
         <v>160.1693969002696</v>
       </c>
       <c r="C32" t="n">
-        <v>59.80299950149551</v>
+        <v>53.40806178795629</v>
       </c>
       <c r="D32" t="n">
-        <v>160.1693969002696</v>
+        <v>180.5403706199461</v>
       </c>
       <c r="E32" t="n">
-        <v>59.80299950149551</v>
+        <v>54.72053301557777</v>
       </c>
       <c r="F32" t="n">
         <v>6.743812010443861</v>
@@ -1510,13 +1510,13 @@
         <v>160.0627425876012</v>
       </c>
       <c r="C33" t="n">
-        <v>59.83965802592223</v>
+        <v>53.28874622180888</v>
       </c>
       <c r="D33" t="n">
-        <v>160.0627425876012</v>
+        <v>180.4337163072776</v>
       </c>
       <c r="E33" t="n">
-        <v>59.83965802592223</v>
+        <v>54.60121744943037</v>
       </c>
       <c r="F33" t="n">
         <v>5.942924281984347</v>
@@ -1539,13 +1539,13 @@
         <v>159.9560882749327</v>
       </c>
       <c r="C34" t="n">
-        <v>59.87631655034895</v>
+        <v>53.16943065566147</v>
       </c>
       <c r="D34" t="n">
-        <v>159.9560882749327</v>
+        <v>180.3270619946092</v>
       </c>
       <c r="E34" t="n">
-        <v>59.87631655034895</v>
+        <v>54.48190188328295</v>
       </c>
       <c r="F34" t="n">
         <v>5.142036553524804</v>
@@ -1568,13 +1568,13 @@
         <v>159.8494339622642</v>
       </c>
       <c r="C35" t="n">
-        <v>59.91297507477567</v>
+        <v>53.05011508951407</v>
       </c>
       <c r="D35" t="n">
-        <v>159.8494339622642</v>
+        <v>180.2204076819407</v>
       </c>
       <c r="E35" t="n">
-        <v>59.91297507477567</v>
+        <v>54.36258631713554</v>
       </c>
       <c r="F35" t="n">
         <v>4.341148825065289</v>
@@ -1597,13 +1597,13 @@
         <v>159.7427796495957</v>
       </c>
       <c r="C36" t="n">
-        <v>59.94963359920239</v>
+        <v>52.93079952336666</v>
       </c>
       <c r="D36" t="n">
-        <v>159.7427796495957</v>
+        <v>180.1137533692722</v>
       </c>
       <c r="E36" t="n">
-        <v>59.94963359920239</v>
+        <v>54.24327075098814</v>
       </c>
       <c r="F36" t="n">
         <v>3.540261096605747</v>
@@ -1626,13 +1626,13 @@
         <v>159.6361253369273</v>
       </c>
       <c r="C37" t="n">
-        <v>59.98629212362911</v>
+        <v>52.81148395721925</v>
       </c>
       <c r="D37" t="n">
-        <v>159.6361253369273</v>
+        <v>180.0070990566038</v>
       </c>
       <c r="E37" t="n">
-        <v>59.98629212362911</v>
+        <v>54.12395518484073</v>
       </c>
       <c r="F37" t="n">
         <v>2.739373368146232</v>
@@ -1655,13 +1655,13 @@
         <v>159.5294710242588</v>
       </c>
       <c r="C38" t="n">
-        <v>60.02295064805583</v>
+        <v>52.69216839107184</v>
       </c>
       <c r="D38" t="n">
-        <v>159.5294710242588</v>
+        <v>179.9004447439353</v>
       </c>
       <c r="E38" t="n">
-        <v>60.02295064805583</v>
+        <v>54.00463961869333</v>
       </c>
       <c r="F38" t="n">
         <v>1.938485639686689</v>
@@ -1684,13 +1684,13 @@
         <v>159.4228167115904</v>
       </c>
       <c r="C39" t="n">
-        <v>60.05960917248255</v>
+        <v>52.57285282492443</v>
       </c>
       <c r="D39" t="n">
-        <v>159.4228167115904</v>
+        <v>179.7937904312669</v>
       </c>
       <c r="E39" t="n">
-        <v>60.05960917248255</v>
+        <v>53.88532405254592</v>
       </c>
       <c r="F39" t="n">
         <v>1.137597911227147</v>
@@ -1713,13 +1713,13 @@
         <v>159.3161623989219</v>
       </c>
       <c r="C40" t="n">
-        <v>60.09626769690927</v>
+        <v>52.45353725877703</v>
       </c>
       <c r="D40" t="n">
-        <v>159.3161623989219</v>
+        <v>179.6871361185984</v>
       </c>
       <c r="E40" t="n">
-        <v>60.09626769690927</v>
+        <v>53.76600848639851</v>
       </c>
       <c r="F40" t="n">
         <v>0.3367101827676322</v>
@@ -1742,13 +1742,13 @@
         <v>159.2095080862534</v>
       </c>
       <c r="C41" t="n">
-        <v>60.13292622133599</v>
+        <v>52.33422169262962</v>
       </c>
       <c r="D41" t="n">
-        <v>159.2095080862534</v>
+        <v>179.5804818059299</v>
       </c>
       <c r="E41" t="n">
-        <v>60.13292622133599</v>
+        <v>53.6466929202511</v>
       </c>
       <c r="F41" t="n">
         <v>-0.4641775456919106</v>
@@ -1771,13 +1771,13 @@
         <v>159.102853773585</v>
       </c>
       <c r="C42" t="n">
-        <v>60.16958474576271</v>
+        <v>52.21490612648221</v>
       </c>
       <c r="D42" t="n">
-        <v>159.102853773585</v>
+        <v>179.4738274932615</v>
       </c>
       <c r="E42" t="n">
-        <v>60.16958474576271</v>
+        <v>53.52737735410369</v>
       </c>
       <c r="F42" t="n">
         <v>-1.265065274151425</v>
@@ -1800,13 +1800,13 @@
         <v>158.9961994609165</v>
       </c>
       <c r="C43" t="n">
-        <v>60.20624327018943</v>
+        <v>52.09559056033481</v>
       </c>
       <c r="D43" t="n">
-        <v>158.9961994609165</v>
+        <v>179.367173180593</v>
       </c>
       <c r="E43" t="n">
-        <v>60.20624327018943</v>
+        <v>53.40806178795629</v>
       </c>
       <c r="F43" t="n">
         <v>-2.065953002610968</v>
@@ -1829,13 +1829,13 @@
         <v>158.889545148248</v>
       </c>
       <c r="C44" t="n">
-        <v>60.24290179461615</v>
+        <v>51.97627499418739</v>
       </c>
       <c r="D44" t="n">
-        <v>158.889545148248</v>
+        <v>179.2605188679246</v>
       </c>
       <c r="E44" t="n">
-        <v>60.24290179461615</v>
+        <v>53.28874622180888</v>
       </c>
       <c r="F44" t="n">
         <v>-2.866840731070482</v>
@@ -1858,13 +1858,13 @@
         <v>158.7828908355796</v>
       </c>
       <c r="C45" t="n">
-        <v>60.27956031904287</v>
+        <v>51.85695942803999</v>
       </c>
       <c r="D45" t="n">
-        <v>158.7828908355796</v>
+        <v>179.1538645552561</v>
       </c>
       <c r="E45" t="n">
-        <v>60.27956031904287</v>
+        <v>53.16943065566147</v>
       </c>
       <c r="F45" t="n">
         <v>-3.667728459530025</v>
@@ -1887,13 +1887,13 @@
         <v>158.6762365229111</v>
       </c>
       <c r="C46" t="n">
-        <v>60.31621884346958</v>
+        <v>51.73764386189258</v>
       </c>
       <c r="D46" t="n">
-        <v>158.6762365229111</v>
+        <v>179.0472102425876</v>
       </c>
       <c r="E46" t="n">
-        <v>60.31621884346958</v>
+        <v>53.05011508951407</v>
       </c>
       <c r="F46" t="n">
         <v>-4.468616187989539</v>
@@ -1916,13 +1916,13 @@
         <v>158.5695822102427</v>
       </c>
       <c r="C47" t="n">
-        <v>60.3528773678963</v>
+        <v>51.61832829574517</v>
       </c>
       <c r="D47" t="n">
-        <v>158.5695822102427</v>
+        <v>178.9405559299192</v>
       </c>
       <c r="E47" t="n">
-        <v>60.3528773678963</v>
+        <v>52.93079952336666</v>
       </c>
       <c r="F47" t="n">
         <v>-5.269503916449082</v>
@@ -1945,13 +1945,13 @@
         <v>158.4629278975742</v>
       </c>
       <c r="C48" t="n">
-        <v>60.38953589232302</v>
+        <v>51.49901272959777</v>
       </c>
       <c r="D48" t="n">
-        <v>158.4629278975742</v>
+        <v>178.8339016172507</v>
       </c>
       <c r="E48" t="n">
-        <v>60.38953589232302</v>
+        <v>52.81148395721925</v>
       </c>
       <c r="F48" t="n">
         <v>-6.070391644908625</v>
@@ -1974,13 +1974,13 @@
         <v>158.3562735849057</v>
       </c>
       <c r="C49" t="n">
-        <v>60.42619441674974</v>
+        <v>51.37969716345036</v>
       </c>
       <c r="D49" t="n">
-        <v>158.3562735849057</v>
+        <v>178.7272473045822</v>
       </c>
       <c r="E49" t="n">
-        <v>60.42619441674974</v>
+        <v>52.69216839107184</v>
       </c>
       <c r="F49" t="n">
         <v>-6.871279373368139</v>
@@ -2003,13 +2003,13 @@
         <v>158.2496192722373</v>
       </c>
       <c r="C50" t="n">
-        <v>60.46285294117646</v>
+        <v>51.26038159730295</v>
       </c>
       <c r="D50" t="n">
-        <v>158.2496192722373</v>
+        <v>178.6205929919138</v>
       </c>
       <c r="E50" t="n">
-        <v>60.46285294117646</v>
+        <v>52.57285282492443</v>
       </c>
       <c r="F50" t="n">
         <v>-7.672167101827682</v>
@@ -2032,13 +2032,13 @@
         <v>158.1429649595688</v>
       </c>
       <c r="C51" t="n">
-        <v>60.49951146560318</v>
+        <v>51.14106603115555</v>
       </c>
       <c r="D51" t="n">
-        <v>158.1429649595688</v>
+        <v>178.5139386792453</v>
       </c>
       <c r="E51" t="n">
-        <v>60.49951146560318</v>
+        <v>52.45353725877703</v>
       </c>
       <c r="F51" t="n">
         <v>-8.473054830287197</v>
@@ -2061,13 +2061,13 @@
         <v>158.0363106469003</v>
       </c>
       <c r="C52" t="n">
-        <v>60.5361699900299</v>
+        <v>51.02175046500813</v>
       </c>
       <c r="D52" t="n">
-        <v>158.0363106469003</v>
+        <v>178.4072843665768</v>
       </c>
       <c r="E52" t="n">
-        <v>60.5361699900299</v>
+        <v>52.33422169262962</v>
       </c>
       <c r="F52" t="n">
         <v>-9.273942558746739</v>
@@ -2090,13 +2090,13 @@
         <v>157.9296563342319</v>
       </c>
       <c r="C53" t="n">
-        <v>60.57282851445662</v>
+        <v>50.90243489886073</v>
       </c>
       <c r="D53" t="n">
-        <v>157.9296563342319</v>
+        <v>178.3006300539084</v>
       </c>
       <c r="E53" t="n">
-        <v>60.57282851445662</v>
+        <v>52.21490612648221</v>
       </c>
       <c r="F53" t="n">
         <v>-10.07483028720625</v>
@@ -2119,13 +2119,13 @@
         <v>157.8230020215634</v>
       </c>
       <c r="C54" t="n">
-        <v>60.60948703888334</v>
+        <v>50.78311933271332</v>
       </c>
       <c r="D54" t="n">
-        <v>157.8230020215634</v>
+        <v>178.1939757412399</v>
       </c>
       <c r="E54" t="n">
-        <v>60.60948703888334</v>
+        <v>52.09559056033481</v>
       </c>
       <c r="F54" t="n">
         <v>-10.8757180156658</v>
@@ -2148,13 +2148,13 @@
         <v>157.7163477088949</v>
       </c>
       <c r="C55" t="n">
-        <v>60.64614556331006</v>
+        <v>50.66380376656591</v>
       </c>
       <c r="D55" t="n">
-        <v>157.7163477088949</v>
+        <v>178.0873214285714</v>
       </c>
       <c r="E55" t="n">
-        <v>60.64614556331006</v>
+        <v>51.97627499418739</v>
       </c>
       <c r="F55" t="n">
         <v>-11.67660574412531</v>
@@ -2177,13 +2177,13 @@
         <v>157.6096933962265</v>
       </c>
       <c r="C56" t="n">
-        <v>60.68280408773678</v>
+        <v>50.54448820041851</v>
       </c>
       <c r="D56" t="n">
-        <v>157.6096933962265</v>
+        <v>177.980667115903</v>
       </c>
       <c r="E56" t="n">
-        <v>60.68280408773678</v>
+        <v>51.85695942803999</v>
       </c>
       <c r="F56" t="n">
         <v>-12.47749347258485</v>
@@ -2206,13 +2206,13 @@
         <v>157.503039083558</v>
       </c>
       <c r="C57" t="n">
-        <v>60.7194626121635</v>
+        <v>50.4251726342711</v>
       </c>
       <c r="D57" t="n">
-        <v>157.503039083558</v>
+        <v>177.8740128032345</v>
       </c>
       <c r="E57" t="n">
-        <v>60.7194626121635</v>
+        <v>51.73764386189258</v>
       </c>
       <c r="F57" t="n">
         <v>-13.27838120104437</v>
@@ -2235,13 +2235,13 @@
         <v>157.3963847708896</v>
       </c>
       <c r="C58" t="n">
-        <v>60.75612113659022</v>
+        <v>50.30585706812369</v>
       </c>
       <c r="D58" t="n">
-        <v>157.3963847708896</v>
+        <v>177.7673584905661</v>
       </c>
       <c r="E58" t="n">
-        <v>60.75612113659022</v>
+        <v>51.61832829574517</v>
       </c>
       <c r="F58" t="n">
         <v>-14.07926892950391</v>
@@ -2264,13 +2264,13 @@
         <v>157.2897304582211</v>
       </c>
       <c r="C59" t="n">
-        <v>60.79277966101694</v>
+        <v>50.18654150197628</v>
       </c>
       <c r="D59" t="n">
-        <v>157.2897304582211</v>
+        <v>177.6607041778976</v>
       </c>
       <c r="E59" t="n">
-        <v>60.79277966101694</v>
+        <v>51.49901272959777</v>
       </c>
       <c r="F59" t="n">
         <v>-14.88015665796345</v>
@@ -2293,13 +2293,13 @@
         <v>157.1830761455526</v>
       </c>
       <c r="C60" t="n">
-        <v>60.82943818544366</v>
+        <v>50.06722593582887</v>
       </c>
       <c r="D60" t="n">
-        <v>157.1830761455526</v>
+        <v>177.5540498652291</v>
       </c>
       <c r="E60" t="n">
-        <v>60.82943818544366</v>
+        <v>51.37969716345036</v>
       </c>
       <c r="F60" t="n">
         <v>-15.68104438642297</v>
@@ -2322,13 +2322,13 @@
         <v>157.0764218328842</v>
       </c>
       <c r="C61" t="n">
-        <v>60.86609670987038</v>
+        <v>49.94791036968147</v>
       </c>
       <c r="D61" t="n">
-        <v>157.0764218328842</v>
+        <v>177.4473955525607</v>
       </c>
       <c r="E61" t="n">
-        <v>60.86609670987038</v>
+        <v>51.26038159730295</v>
       </c>
       <c r="F61" t="n">
         <v>-16.48193211488251</v>
@@ -2351,13 +2351,13 @@
         <v>156.9697675202157</v>
       </c>
       <c r="C62" t="n">
-        <v>60.9027552342971</v>
+        <v>49.82859480353406</v>
       </c>
       <c r="D62" t="n">
-        <v>156.9697675202157</v>
+        <v>177.3407412398922</v>
       </c>
       <c r="E62" t="n">
-        <v>60.9027552342971</v>
+        <v>51.14106603115555</v>
       </c>
       <c r="F62" t="n">
         <v>-17.28281984334203</v>
@@ -2380,13 +2380,13 @@
         <v>156.8631132075472</v>
       </c>
       <c r="C63" t="n">
-        <v>60.93941375872382</v>
+        <v>49.70927923738665</v>
       </c>
       <c r="D63" t="n">
-        <v>156.8631132075472</v>
+        <v>177.2340869272238</v>
       </c>
       <c r="E63" t="n">
-        <v>60.93941375872382</v>
+        <v>51.02175046500813</v>
       </c>
       <c r="F63" t="n">
         <v>-18.08370757180157</v>
@@ -2409,13 +2409,13 @@
         <v>156.7564588948788</v>
       </c>
       <c r="C64" t="n">
-        <v>60.97607228315054</v>
+        <v>49.58996367123925</v>
       </c>
       <c r="D64" t="n">
-        <v>156.7564588948788</v>
+        <v>177.1274326145553</v>
       </c>
       <c r="E64" t="n">
-        <v>60.97607228315054</v>
+        <v>50.90243489886073</v>
       </c>
       <c r="F64" t="n">
         <v>-18.88459530026108</v>
@@ -2438,13 +2438,13 @@
         <v>156.6498045822103</v>
       </c>
       <c r="C65" t="n">
-        <v>61.01273080757726</v>
+        <v>49.47064810509184</v>
       </c>
       <c r="D65" t="n">
-        <v>156.6498045822103</v>
+        <v>177.0207783018868</v>
       </c>
       <c r="E65" t="n">
-        <v>61.01273080757726</v>
+        <v>50.78311933271332</v>
       </c>
       <c r="F65" t="n">
         <v>-19.68548302872063</v>
@@ -2467,13 +2467,13 @@
         <v>156.5431502695419</v>
       </c>
       <c r="C66" t="n">
-        <v>61.04938933200398</v>
+        <v>49.35133253894443</v>
       </c>
       <c r="D66" t="n">
-        <v>156.5431502695419</v>
+        <v>176.9141239892184</v>
       </c>
       <c r="E66" t="n">
-        <v>61.04938933200398</v>
+        <v>50.66380376656591</v>
       </c>
       <c r="F66" t="n">
         <v>-20.48637075718014</v>
@@ -2496,13 +2496,13 @@
         <v>156.4364959568734</v>
       </c>
       <c r="C67" t="n">
-        <v>61.0860478564307</v>
+        <v>49.23201697279702</v>
       </c>
       <c r="D67" t="n">
-        <v>156.4364959568734</v>
+        <v>176.8074696765499</v>
       </c>
       <c r="E67" t="n">
-        <v>61.0860478564307</v>
+        <v>50.54448820041851</v>
       </c>
       <c r="F67" t="n">
         <v>-21.28725848563968</v>
@@ -2525,13 +2525,13 @@
         <v>156.3298416442049</v>
       </c>
       <c r="C68" t="n">
-        <v>61.12270638085742</v>
+        <v>49.11270140664961</v>
       </c>
       <c r="D68" t="n">
-        <v>156.3298416442049</v>
+        <v>176.7008153638814</v>
       </c>
       <c r="E68" t="n">
-        <v>61.12270638085742</v>
+        <v>50.4251726342711</v>
       </c>
       <c r="F68" t="n">
         <v>-22.08814621409923</v>
@@ -2554,13 +2554,13 @@
         <v>156.2231873315365</v>
       </c>
       <c r="C69" t="n">
-        <v>61.15936490528414</v>
+        <v>48.99338584050221</v>
       </c>
       <c r="D69" t="n">
-        <v>156.2231873315365</v>
+        <v>176.594161051213</v>
       </c>
       <c r="E69" t="n">
-        <v>61.15936490528414</v>
+        <v>50.30585706812369</v>
       </c>
       <c r="F69" t="n">
         <v>-22.88903394255874</v>
@@ -2583,13 +2583,13 @@
         <v>156.116533018868</v>
       </c>
       <c r="C70" t="n">
-        <v>61.19602342971086</v>
+        <v>48.8740702743548</v>
       </c>
       <c r="D70" t="n">
-        <v>156.116533018868</v>
+        <v>176.4875067385445</v>
       </c>
       <c r="E70" t="n">
-        <v>61.19602342971086</v>
+        <v>50.18654150197628</v>
       </c>
       <c r="F70" t="n">
         <v>-23.68992167101828</v>
@@ -2612,13 +2612,13 @@
         <v>156.0098787061995</v>
       </c>
       <c r="C71" t="n">
-        <v>61.23268195413758</v>
+        <v>48.75475470820739</v>
       </c>
       <c r="D71" t="n">
-        <v>156.0098787061995</v>
+        <v>176.380852425876</v>
       </c>
       <c r="E71" t="n">
-        <v>61.23268195413758</v>
+        <v>50.06722593582887</v>
       </c>
       <c r="F71" t="n">
         <v>-24.4908093994778</v>
@@ -2641,13 +2641,13 @@
         <v>155.9032243935311</v>
       </c>
       <c r="C72" t="n">
-        <v>61.2693404785643</v>
+        <v>48.63543914205998</v>
       </c>
       <c r="D72" t="n">
-        <v>155.9032243935311</v>
+        <v>176.2741981132076</v>
       </c>
       <c r="E72" t="n">
-        <v>61.2693404785643</v>
+        <v>49.94791036968147</v>
       </c>
       <c r="F72" t="n">
         <v>-25.29169712793734</v>
@@ -2670,13 +2670,13 @@
         <v>155.7965700808626</v>
       </c>
       <c r="C73" t="n">
-        <v>61.30599900299102</v>
+        <v>48.51612357591257</v>
       </c>
       <c r="D73" t="n">
-        <v>155.7965700808626</v>
+        <v>176.1675438005391</v>
       </c>
       <c r="E73" t="n">
-        <v>61.30599900299102</v>
+        <v>49.82859480353406</v>
       </c>
       <c r="F73" t="n">
         <v>-26.09258485639685</v>
@@ -2699,13 +2699,13 @@
         <v>155.6899157681941</v>
       </c>
       <c r="C74" t="n">
-        <v>61.34265752741774</v>
+        <v>48.39680800976517</v>
       </c>
       <c r="D74" t="n">
-        <v>155.6899157681941</v>
+        <v>176.0608894878706</v>
       </c>
       <c r="E74" t="n">
-        <v>61.34265752741774</v>
+        <v>49.70927923738665</v>
       </c>
       <c r="F74" t="n">
         <v>-26.8934725848564</v>
@@ -2728,13 +2728,13 @@
         <v>155.5832614555257</v>
       </c>
       <c r="C75" t="n">
-        <v>61.37931605184446</v>
+        <v>48.27749244361776</v>
       </c>
       <c r="D75" t="n">
-        <v>155.5832614555257</v>
+        <v>175.9542351752022</v>
       </c>
       <c r="E75" t="n">
-        <v>61.37931605184446</v>
+        <v>49.58996367123925</v>
       </c>
       <c r="F75" t="n">
         <v>-27.69436031331591</v>
@@ -2757,13 +2757,13 @@
         <v>155.4766071428572</v>
       </c>
       <c r="C76" t="n">
-        <v>61.41597457627118</v>
+        <v>48.15817687747035</v>
       </c>
       <c r="D76" t="n">
-        <v>155.4766071428572</v>
+        <v>175.8475808625337</v>
       </c>
       <c r="E76" t="n">
-        <v>61.41597457627118</v>
+        <v>49.47064810509184</v>
       </c>
       <c r="F76" t="n">
         <v>-28.49524804177545</v>
@@ -2786,13 +2786,13 @@
         <v>155.3699528301888</v>
       </c>
       <c r="C77" t="n">
-        <v>61.4526331006979</v>
+        <v>48.03886131132295</v>
       </c>
       <c r="D77" t="n">
-        <v>155.3699528301888</v>
+        <v>175.7409265498653</v>
       </c>
       <c r="E77" t="n">
-        <v>61.4526331006979</v>
+        <v>49.35133253894443</v>
       </c>
       <c r="F77" t="n">
         <v>-29.296135770235</v>
@@ -2815,13 +2815,13 @@
         <v>155.2632985175203</v>
       </c>
       <c r="C78" t="n">
-        <v>61.48929162512462</v>
+        <v>47.91954574517554</v>
       </c>
       <c r="D78" t="n">
-        <v>155.2632985175203</v>
+        <v>175.6342722371968</v>
       </c>
       <c r="E78" t="n">
-        <v>61.48929162512462</v>
+        <v>49.23201697279702</v>
       </c>
       <c r="F78" t="n">
         <v>-30.09702349869451</v>
@@ -2844,13 +2844,13 @@
         <v>155.1566442048518</v>
       </c>
       <c r="C79" t="n">
-        <v>61.52595014955134</v>
+        <v>47.80023017902813</v>
       </c>
       <c r="D79" t="n">
-        <v>155.1566442048518</v>
+        <v>175.5276179245283</v>
       </c>
       <c r="E79" t="n">
-        <v>61.52595014955134</v>
+        <v>49.11270140664961</v>
       </c>
       <c r="F79" t="n">
         <v>-30.89791122715405</v>
@@ -2873,13 +2873,13 @@
         <v>155.0499898921834</v>
       </c>
       <c r="C80" t="n">
-        <v>61.56260867397806</v>
+        <v>47.68091461288072</v>
       </c>
       <c r="D80" t="n">
-        <v>155.0499898921834</v>
+        <v>175.4209636118599</v>
       </c>
       <c r="E80" t="n">
-        <v>61.56260867397806</v>
+        <v>48.99338584050221</v>
       </c>
       <c r="F80" t="n">
         <v>-31.69879895561357</v>
@@ -2902,13 +2902,13 @@
         <v>154.9433355795149</v>
       </c>
       <c r="C81" t="n">
-        <v>61.59926719840478</v>
+        <v>47.56159904673331</v>
       </c>
       <c r="D81" t="n">
-        <v>154.9433355795149</v>
+        <v>175.3143092991914</v>
       </c>
       <c r="E81" t="n">
-        <v>61.59926719840478</v>
+        <v>48.8740702743548</v>
       </c>
       <c r="F81" t="n">
         <v>-32.49968668407311</v>
@@ -2931,13 +2931,13 @@
         <v>154.8366812668464</v>
       </c>
       <c r="C82" t="n">
-        <v>61.6359257228315</v>
+        <v>47.44228348058591</v>
       </c>
       <c r="D82" t="n">
-        <v>154.8366812668464</v>
+        <v>175.2076549865229</v>
       </c>
       <c r="E82" t="n">
-        <v>61.6359257228315</v>
+        <v>48.75475470820739</v>
       </c>
       <c r="F82" t="n">
         <v>-33.30057441253263</v>
@@ -2960,13 +2960,13 @@
         <v>154.730026954178</v>
       </c>
       <c r="C83" t="n">
-        <v>61.67258424725822</v>
+        <v>47.3229679144385</v>
       </c>
       <c r="D83" t="n">
-        <v>154.730026954178</v>
+        <v>175.1010006738545</v>
       </c>
       <c r="E83" t="n">
-        <v>61.67258424725822</v>
+        <v>48.63543914205998</v>
       </c>
       <c r="F83" t="n">
         <v>-34.10146214099217</v>
@@ -2989,13 +2989,13 @@
         <v>154.6233726415095</v>
       </c>
       <c r="C84" t="n">
-        <v>61.70924277168494</v>
+        <v>47.20365234829109</v>
       </c>
       <c r="D84" t="n">
-        <v>154.6233726415095</v>
+        <v>174.994346361186</v>
       </c>
       <c r="E84" t="n">
-        <v>61.70924277168494</v>
+        <v>48.51612357591257</v>
       </c>
       <c r="F84" t="n">
         <v>-34.90234986945168</v>
@@ -3018,13 +3018,13 @@
         <v>154.5167183288411</v>
       </c>
       <c r="C85" t="n">
-        <v>61.74590129611166</v>
+        <v>47.08433678214368</v>
       </c>
       <c r="D85" t="n">
-        <v>154.5167183288411</v>
+        <v>174.8876920485176</v>
       </c>
       <c r="E85" t="n">
-        <v>61.74590129611166</v>
+        <v>48.39680800976517</v>
       </c>
       <c r="F85" t="n">
         <v>-35.70323759791123</v>
@@ -3047,13 +3047,13 @@
         <v>154.4100640161726</v>
       </c>
       <c r="C86" t="n">
-        <v>61.78255982053838</v>
+        <v>46.96502121599627</v>
       </c>
       <c r="D86" t="n">
-        <v>154.4100640161726</v>
+        <v>174.7810377358491</v>
       </c>
       <c r="E86" t="n">
-        <v>61.78255982053838</v>
+        <v>48.27749244361776</v>
       </c>
       <c r="F86" t="n">
         <v>-36.50412532637074</v>
@@ -3076,13 +3076,13 @@
         <v>154.3034097035041</v>
       </c>
       <c r="C87" t="n">
-        <v>61.8192183449651</v>
+        <v>46.84570564984887</v>
       </c>
       <c r="D87" t="n">
-        <v>154.3034097035041</v>
+        <v>174.6743834231806</v>
       </c>
       <c r="E87" t="n">
-        <v>61.8192183449651</v>
+        <v>48.15817687747035</v>
       </c>
       <c r="F87" t="n">
         <v>-37.30501305483028</v>
@@ -3105,13 +3105,13 @@
         <v>154.1967553908356</v>
       </c>
       <c r="C88" t="n">
-        <v>61.85587686939182</v>
+        <v>46.72639008370146</v>
       </c>
       <c r="D88" t="n">
-        <v>154.1967553908356</v>
+        <v>174.5677291105121</v>
       </c>
       <c r="E88" t="n">
-        <v>61.85587686939182</v>
+        <v>48.03886131132295</v>
       </c>
       <c r="F88" t="n">
         <v>-38.10590078328983</v>
@@ -3134,13 +3134,13 @@
         <v>154.0901010781672</v>
       </c>
       <c r="C89" t="n">
-        <v>61.89253539381854</v>
+        <v>46.60707451755405</v>
       </c>
       <c r="D89" t="n">
-        <v>154.0901010781672</v>
+        <v>174.4610747978437</v>
       </c>
       <c r="E89" t="n">
-        <v>61.89253539381854</v>
+        <v>47.91954574517554</v>
       </c>
       <c r="F89" t="n">
         <v>-38.90678851174934</v>
@@ -3163,13 +3163,13 @@
         <v>153.9834467654987</v>
       </c>
       <c r="C90" t="n">
-        <v>61.92919391824526</v>
+        <v>46.48775895140665</v>
       </c>
       <c r="D90" t="n">
-        <v>153.9834467654987</v>
+        <v>174.3544204851752</v>
       </c>
       <c r="E90" t="n">
-        <v>61.92919391824526</v>
+        <v>47.80023017902813</v>
       </c>
       <c r="F90" t="n">
         <v>-39.70767624020888</v>
@@ -3192,13 +3192,13 @@
         <v>153.8767924528303</v>
       </c>
       <c r="C91" t="n">
-        <v>61.96585244267198</v>
+        <v>46.36844338525924</v>
       </c>
       <c r="D91" t="n">
-        <v>153.8767924528303</v>
+        <v>174.2477661725068</v>
       </c>
       <c r="E91" t="n">
-        <v>61.96585244267198</v>
+        <v>47.68091461288072</v>
       </c>
       <c r="F91" t="n">
         <v>-40.5085639686684</v>
@@ -3221,13 +3221,13 @@
         <v>153.7701381401618</v>
       </c>
       <c r="C92" t="n">
-        <v>62.0025109670987</v>
+        <v>46.24912781911183</v>
       </c>
       <c r="D92" t="n">
-        <v>153.7701381401618</v>
+        <v>174.1411118598383</v>
       </c>
       <c r="E92" t="n">
-        <v>62.0025109670987</v>
+        <v>47.56159904673331</v>
       </c>
       <c r="F92" t="n">
         <v>-41.30945169712794</v>
@@ -3250,13 +3250,13 @@
         <v>153.6634838274933</v>
       </c>
       <c r="C93" t="n">
-        <v>62.03916949152542</v>
+        <v>46.12981225296443</v>
       </c>
       <c r="D93" t="n">
-        <v>153.6634838274933</v>
+        <v>174.0344575471698</v>
       </c>
       <c r="E93" t="n">
-        <v>62.03916949152542</v>
+        <v>47.44228348058591</v>
       </c>
       <c r="F93" t="n">
         <v>-42.11033942558745</v>
@@ -3279,13 +3279,13 @@
         <v>153.5568295148249</v>
       </c>
       <c r="C94" t="n">
-        <v>62.07582801595214</v>
+        <v>46.01049668681701</v>
       </c>
       <c r="D94" t="n">
-        <v>153.5568295148249</v>
+        <v>173.9278032345014</v>
       </c>
       <c r="E94" t="n">
-        <v>62.07582801595214</v>
+        <v>47.3229679144385</v>
       </c>
       <c r="F94" t="n">
         <v>-42.911227154047</v>
@@ -3308,13 +3308,13 @@
         <v>153.4501752021564</v>
       </c>
       <c r="C95" t="n">
-        <v>62.11248654037886</v>
+        <v>45.89118112066961</v>
       </c>
       <c r="D95" t="n">
-        <v>153.4501752021564</v>
+        <v>173.8211489218329</v>
       </c>
       <c r="E95" t="n">
-        <v>62.11248654037886</v>
+        <v>47.20365234829109</v>
       </c>
       <c r="F95" t="n">
         <v>-43.71211488250651</v>
@@ -3337,13 +3337,13 @@
         <v>153.3435208894879</v>
       </c>
       <c r="C96" t="n">
-        <v>62.14914506480558</v>
+        <v>45.7718655545222</v>
       </c>
       <c r="D96" t="n">
-        <v>153.3435208894879</v>
+        <v>173.7144946091645</v>
       </c>
       <c r="E96" t="n">
-        <v>62.14914506480558</v>
+        <v>47.08433678214368</v>
       </c>
       <c r="F96" t="n">
         <v>-44.51300261096605</v>
@@ -3366,13 +3366,13 @@
         <v>153.2368665768195</v>
       </c>
       <c r="C97" t="n">
-        <v>62.1858035892323</v>
+        <v>45.65254998837479</v>
       </c>
       <c r="D97" t="n">
-        <v>153.2368665768195</v>
+        <v>173.607840296496</v>
       </c>
       <c r="E97" t="n">
-        <v>62.1858035892323</v>
+        <v>46.96502121599627</v>
       </c>
       <c r="F97" t="n">
         <v>-45.3138903394256</v>
@@ -3395,13 +3395,13 @@
         <v>153.130212264151</v>
       </c>
       <c r="C98" t="n">
-        <v>62.22246211365902</v>
+        <v>45.53323442222739</v>
       </c>
       <c r="D98" t="n">
-        <v>153.130212264151</v>
+        <v>173.5011859838275</v>
       </c>
       <c r="E98" t="n">
-        <v>62.22246211365902</v>
+        <v>46.84570564984887</v>
       </c>
       <c r="F98" t="n">
         <v>-46.11477806788511</v>
@@ -3424,13 +3424,13 @@
         <v>153.0235579514826</v>
       </c>
       <c r="C99" t="n">
-        <v>62.25912063808574</v>
+        <v>45.41391885607997</v>
       </c>
       <c r="D99" t="n">
-        <v>153.0235579514826</v>
+        <v>173.3945316711591</v>
       </c>
       <c r="E99" t="n">
-        <v>62.25912063808574</v>
+        <v>46.72639008370146</v>
       </c>
       <c r="F99" t="n">
         <v>-46.91566579634465</v>
@@ -3453,13 +3453,13 @@
         <v>152.9169036388141</v>
       </c>
       <c r="C100" t="n">
-        <v>62.29577916251246</v>
+        <v>45.29460328993257</v>
       </c>
       <c r="D100" t="n">
-        <v>152.9169036388141</v>
+        <v>173.2878773584906</v>
       </c>
       <c r="E100" t="n">
-        <v>62.29577916251246</v>
+        <v>46.60707451755405</v>
       </c>
       <c r="F100" t="n">
         <v>-47.71655352480417</v>
@@ -3482,13 +3482,13 @@
         <v>152.8102493261456</v>
       </c>
       <c r="C101" t="n">
-        <v>62.33243768693918</v>
+        <v>45.17528772378516</v>
       </c>
       <c r="D101" t="n">
-        <v>152.8102493261456</v>
+        <v>173.1812230458222</v>
       </c>
       <c r="E101" t="n">
-        <v>62.33243768693918</v>
+        <v>46.48775895140665</v>
       </c>
       <c r="F101" t="n">
         <v>-48.51744125326371</v>
@@ -3511,13 +3511,13 @@
         <v>152.7035950134772</v>
       </c>
       <c r="C102" t="n">
-        <v>62.3690962113659</v>
+        <v>45.05597215763775</v>
       </c>
       <c r="D102" t="n">
-        <v>152.7035950134772</v>
+        <v>173.0745687331537</v>
       </c>
       <c r="E102" t="n">
-        <v>62.3690962113659</v>
+        <v>46.36844338525924</v>
       </c>
       <c r="F102" t="n">
         <v>-49.31832898172323</v>
@@ -3540,13 +3540,13 @@
         <v>152.5969407008087</v>
       </c>
       <c r="C103" t="n">
-        <v>62.40575473579262</v>
+        <v>44.93665659149035</v>
       </c>
       <c r="D103" t="n">
-        <v>152.5969407008087</v>
+        <v>172.9679144204852</v>
       </c>
       <c r="E103" t="n">
-        <v>62.40575473579262</v>
+        <v>46.24912781911183</v>
       </c>
       <c r="F103" t="n">
         <v>-50.11921671018277</v>
@@ -3569,13 +3569,13 @@
         <v>152.4902863881402</v>
       </c>
       <c r="C104" t="n">
-        <v>62.44241326021934</v>
+        <v>44.81734102534294</v>
       </c>
       <c r="D104" t="n">
-        <v>152.4902863881402</v>
+        <v>172.8612601078167</v>
       </c>
       <c r="E104" t="n">
-        <v>62.44241326021934</v>
+        <v>46.12981225296443</v>
       </c>
       <c r="F104" t="n">
         <v>-50.92010443864228</v>
@@ -3598,13 +3598,13 @@
         <v>152.3836320754718</v>
       </c>
       <c r="C105" t="n">
-        <v>62.47907178464606</v>
+        <v>44.69802545919553</v>
       </c>
       <c r="D105" t="n">
-        <v>152.3836320754718</v>
+        <v>172.7546057951483</v>
       </c>
       <c r="E105" t="n">
-        <v>62.47907178464606</v>
+        <v>46.01049668681701</v>
       </c>
       <c r="F105" t="n">
         <v>-51.72099216710183</v>
@@ -3627,13 +3627,13 @@
         <v>152.2769777628033</v>
       </c>
       <c r="C106" t="n">
-        <v>62.51573030907278</v>
+        <v>44.57870989304813</v>
       </c>
       <c r="D106" t="n">
-        <v>152.2769777628033</v>
+        <v>172.6479514824798</v>
       </c>
       <c r="E106" t="n">
-        <v>62.51573030907278</v>
+        <v>45.89118112066961</v>
       </c>
       <c r="F106" t="n">
         <v>-52.52187989556134</v>
@@ -3656,13 +3656,13 @@
         <v>152.1703234501348</v>
       </c>
       <c r="C107" t="n">
-        <v>62.5523888334995</v>
+        <v>44.45939432690072</v>
       </c>
       <c r="D107" t="n">
-        <v>152.1703234501348</v>
+        <v>172.5412971698113</v>
       </c>
       <c r="E107" t="n">
-        <v>62.5523888334995</v>
+        <v>45.7718655545222</v>
       </c>
       <c r="F107" t="n">
         <v>-53.32276762402088</v>
@@ -3685,13 +3685,13 @@
         <v>152.0636691374664</v>
       </c>
       <c r="C108" t="n">
-        <v>62.58904735792622</v>
+        <v>44.34007876075331</v>
       </c>
       <c r="D108" t="n">
-        <v>152.0636691374664</v>
+        <v>172.4346428571429</v>
       </c>
       <c r="E108" t="n">
-        <v>62.58904735792622</v>
+        <v>45.65254998837479</v>
       </c>
       <c r="F108" t="n">
         <v>-54.12365535248043</v>
@@ -3714,13 +3714,13 @@
         <v>151.9570148247979</v>
       </c>
       <c r="C109" t="n">
-        <v>62.62570588235294</v>
+        <v>44.2207631946059</v>
       </c>
       <c r="D109" t="n">
-        <v>151.9570148247979</v>
+        <v>172.3279885444744</v>
       </c>
       <c r="E109" t="n">
-        <v>62.62570588235294</v>
+        <v>45.53323442222739</v>
       </c>
       <c r="F109" t="n">
         <v>-54.92454308093994</v>
@@ -3743,13 +3743,13 @@
         <v>151.8503605121295</v>
       </c>
       <c r="C110" t="n">
-        <v>62.66236440677966</v>
+        <v>44.10144762845849</v>
       </c>
       <c r="D110" t="n">
-        <v>151.8503605121295</v>
+        <v>172.221334231806</v>
       </c>
       <c r="E110" t="n">
-        <v>62.66236440677966</v>
+        <v>45.41391885607997</v>
       </c>
       <c r="F110" t="n">
         <v>-55.72543080939948</v>
@@ -3772,13 +3772,13 @@
         <v>151.743706199461</v>
       </c>
       <c r="C111" t="n">
-        <v>62.69902293120638</v>
+        <v>43.98213206231109</v>
       </c>
       <c r="D111" t="n">
-        <v>151.743706199461</v>
+        <v>172.1146799191375</v>
       </c>
       <c r="E111" t="n">
-        <v>62.69902293120638</v>
+        <v>45.29460328993257</v>
       </c>
       <c r="F111" t="n">
         <v>-56.526318537859</v>
@@ -3801,13 +3801,13 @@
         <v>151.6370518867925</v>
       </c>
       <c r="C112" t="n">
-        <v>62.7356814556331</v>
+        <v>43.86281649616368</v>
       </c>
       <c r="D112" t="n">
-        <v>151.6370518867925</v>
+        <v>172.008025606469</v>
       </c>
       <c r="E112" t="n">
-        <v>62.7356814556331</v>
+        <v>45.17528772378516</v>
       </c>
       <c r="F112" t="n">
         <v>-57.32720626631854</v>
@@ -3830,13 +3830,13 @@
         <v>151.5303975741241</v>
       </c>
       <c r="C113" t="n">
-        <v>62.77233998005982</v>
+        <v>43.74350093001627</v>
       </c>
       <c r="D113" t="n">
-        <v>151.5303975741241</v>
+        <v>171.9013712938006</v>
       </c>
       <c r="E113" t="n">
-        <v>62.77233998005982</v>
+        <v>45.05597215763775</v>
       </c>
       <c r="F113" t="n">
         <v>-58.12809399477806</v>
@@ -3859,13 +3859,13 @@
         <v>151.4237432614556</v>
       </c>
       <c r="C114" t="n">
-        <v>62.80899850448654</v>
+        <v>43.62418536386886</v>
       </c>
       <c r="D114" t="n">
-        <v>151.4237432614556</v>
+        <v>171.7947169811321</v>
       </c>
       <c r="E114" t="n">
-        <v>62.80899850448654</v>
+        <v>44.93665659149035</v>
       </c>
       <c r="F114" t="n">
         <v>-58.9289817232376</v>
@@ -3888,13 +3888,13 @@
         <v>151.3170889487872</v>
       </c>
       <c r="C115" t="n">
-        <v>62.84565702891326</v>
+        <v>43.50486979772145</v>
       </c>
       <c r="D115" t="n">
-        <v>151.3170889487872</v>
+        <v>171.6880626684637</v>
       </c>
       <c r="E115" t="n">
-        <v>62.84565702891326</v>
+        <v>44.81734102534294</v>
       </c>
       <c r="F115" t="n">
         <v>-59.72986945169711</v>
@@ -3917,13 +3917,13 @@
         <v>151.2104346361187</v>
       </c>
       <c r="C116" t="n">
-        <v>62.88231555333998</v>
+        <v>43.38555423157405</v>
       </c>
       <c r="D116" t="n">
-        <v>151.2104346361187</v>
+        <v>171.5814083557952</v>
       </c>
       <c r="E116" t="n">
-        <v>62.88231555333998</v>
+        <v>44.69802545919553</v>
       </c>
       <c r="F116" t="n">
         <v>-60.53075718015666</v>
@@ -3946,13 +3946,13 @@
         <v>151.1037803234502</v>
       </c>
       <c r="C117" t="n">
-        <v>62.9189740777667</v>
+        <v>43.26623866542664</v>
       </c>
       <c r="D117" t="n">
-        <v>151.1037803234502</v>
+        <v>171.4747540431267</v>
       </c>
       <c r="E117" t="n">
-        <v>62.9189740777667</v>
+        <v>44.57870989304813</v>
       </c>
       <c r="F117" t="n">
         <v>-61.3316449086162</v>
@@ -3975,13 +3975,13 @@
         <v>150.9971260107818</v>
       </c>
       <c r="C118" t="n">
-        <v>62.95563260219342</v>
+        <v>43.14692309927923</v>
       </c>
       <c r="D118" t="n">
-        <v>150.9971260107818</v>
+        <v>171.3680997304583</v>
       </c>
       <c r="E118" t="n">
-        <v>62.95563260219342</v>
+        <v>44.45939432690072</v>
       </c>
       <c r="F118" t="n">
         <v>-62.13253263707571</v>
@@ -4004,13 +4004,13 @@
         <v>150.8904716981133</v>
       </c>
       <c r="C119" t="n">
-        <v>62.99229112662014</v>
+        <v>43.02760753313183</v>
       </c>
       <c r="D119" t="n">
-        <v>150.8904716981133</v>
+        <v>171.2614454177898</v>
       </c>
       <c r="E119" t="n">
-        <v>62.99229112662014</v>
+        <v>44.34007876075331</v>
       </c>
       <c r="F119" t="n">
         <v>-62.93342036553526</v>
@@ -4033,13 +4033,13 @@
         <v>150.7838173854448</v>
       </c>
       <c r="C120" t="n">
-        <v>63.02894965104686</v>
+        <v>42.90829196698442</v>
       </c>
       <c r="D120" t="n">
-        <v>150.7838173854448</v>
+        <v>171.1547911051213</v>
       </c>
       <c r="E120" t="n">
-        <v>63.02894965104686</v>
+        <v>44.2207631946059</v>
       </c>
       <c r="F120" t="n">
         <v>-63.73430809399477</v>
@@ -4062,13 +4062,13 @@
         <v>150.6771630727764</v>
       </c>
       <c r="C121" t="n">
-        <v>63.06560817547358</v>
+        <v>42.78897640083702</v>
       </c>
       <c r="D121" t="n">
-        <v>150.6771630727764</v>
+        <v>171.0481367924529</v>
       </c>
       <c r="E121" t="n">
-        <v>63.06560817547358</v>
+        <v>44.10144762845849</v>
       </c>
       <c r="F121" t="n">
         <v>-64.53519582245431</v>
@@ -4091,13 +4091,13 @@
         <v>150.5705087601079</v>
       </c>
       <c r="C122" t="n">
-        <v>63.1022666999003</v>
+        <v>42.6696608346896</v>
       </c>
       <c r="D122" t="n">
-        <v>150.5705087601079</v>
+        <v>170.9414824797844</v>
       </c>
       <c r="E122" t="n">
-        <v>63.1022666999003</v>
+        <v>43.98213206231109</v>
       </c>
       <c r="F122" t="n">
         <v>-65.33608355091383</v>
@@ -4120,13 +4120,13 @@
         <v>150.4638544474394</v>
       </c>
       <c r="C123" t="n">
-        <v>63.13892522432702</v>
+        <v>42.55034526854219</v>
       </c>
       <c r="D123" t="n">
-        <v>150.4638544474394</v>
+        <v>170.8348281671159</v>
       </c>
       <c r="E123" t="n">
-        <v>63.13892522432702</v>
+        <v>43.86281649616368</v>
       </c>
       <c r="F123" t="n">
         <v>-66.13697127937337</v>
@@ -4149,13 +4149,13 @@
         <v>150.357200134771</v>
       </c>
       <c r="C124" t="n">
-        <v>63.17558374875374</v>
+        <v>42.43102970239479</v>
       </c>
       <c r="D124" t="n">
-        <v>150.357200134771</v>
+        <v>170.7281738544475</v>
       </c>
       <c r="E124" t="n">
-        <v>63.17558374875374</v>
+        <v>43.74350093001627</v>
       </c>
       <c r="F124" t="n">
         <v>-66.93785900783288</v>
@@ -4178,13 +4178,13 @@
         <v>150.2505458221025</v>
       </c>
       <c r="C125" t="n">
-        <v>63.21224227318045</v>
+        <v>42.31171413624738</v>
       </c>
       <c r="D125" t="n">
-        <v>150.2505458221025</v>
+        <v>170.621519541779</v>
       </c>
       <c r="E125" t="n">
-        <v>63.21224227318045</v>
+        <v>43.62418536386886</v>
       </c>
       <c r="F125" t="n">
         <v>-67.73874673629243</v>
@@ -4207,13 +4207,13 @@
         <v>150.143891509434</v>
       </c>
       <c r="C126" t="n">
-        <v>63.24890079760718</v>
+        <v>42.19239857009998</v>
       </c>
       <c r="D126" t="n">
-        <v>150.143891509434</v>
+        <v>170.5148652291105</v>
       </c>
       <c r="E126" t="n">
-        <v>63.24890079760718</v>
+        <v>43.50486979772145</v>
       </c>
       <c r="F126" t="n">
         <v>-68.53963446475194</v>
@@ -4236,13 +4236,13 @@
         <v>150.0372371967656</v>
       </c>
       <c r="C127" t="n">
-        <v>63.28555932203389</v>
+        <v>42.07308300395256</v>
       </c>
       <c r="D127" t="n">
-        <v>150.0372371967656</v>
+        <v>170.4082109164421</v>
       </c>
       <c r="E127" t="n">
-        <v>63.28555932203389</v>
+        <v>43.38555423157405</v>
       </c>
       <c r="F127" t="n">
         <v>-69.34052219321148</v>
@@ -4265,13 +4265,13 @@
         <v>149.9305828840971</v>
       </c>
       <c r="C128" t="n">
-        <v>63.32221784646062</v>
+        <v>41.95376743780515</v>
       </c>
       <c r="D128" t="n">
-        <v>149.9305828840971</v>
+        <v>170.3015566037736</v>
       </c>
       <c r="E128" t="n">
-        <v>63.32221784646062</v>
+        <v>43.26623866542664</v>
       </c>
       <c r="F128" t="n">
         <v>-70.14140992167103</v>
@@ -4294,13 +4294,13 @@
         <v>149.8239285714287</v>
       </c>
       <c r="C129" t="n">
-        <v>63.35887637088733</v>
+        <v>41.83445187165775</v>
       </c>
       <c r="D129" t="n">
-        <v>149.8239285714287</v>
+        <v>170.1949022911052</v>
       </c>
       <c r="E129" t="n">
-        <v>63.35887637088733</v>
+        <v>43.14692309927923</v>
       </c>
       <c r="F129" t="n">
         <v>-70.94229765013054</v>
@@ -4323,13 +4323,13 @@
         <v>149.7172742587602</v>
       </c>
       <c r="C130" t="n">
-        <v>63.39553489531406</v>
+        <v>41.71513630551034</v>
       </c>
       <c r="D130" t="n">
-        <v>149.7172742587602</v>
+        <v>170.0882479784367</v>
       </c>
       <c r="E130" t="n">
-        <v>63.39553489531406</v>
+        <v>43.02760753313183</v>
       </c>
       <c r="F130" t="n">
         <v>-71.74318537859008</v>
@@ -4352,13 +4352,13 @@
         <v>149.6106199460917</v>
       </c>
       <c r="C131" t="n">
-        <v>63.43219341974077</v>
+        <v>41.59582073936294</v>
       </c>
       <c r="D131" t="n">
-        <v>149.6106199460917</v>
+        <v>169.9815936657682</v>
       </c>
       <c r="E131" t="n">
-        <v>63.43219341974077</v>
+        <v>42.90829196698442</v>
       </c>
       <c r="F131" t="n">
         <v>-72.5440731070496</v>
@@ -4381,13 +4381,13 @@
         <v>149.5039656334233</v>
       </c>
       <c r="C132" t="n">
-        <v>63.4688519441675</v>
+        <v>41.47650517321553</v>
       </c>
       <c r="D132" t="n">
-        <v>149.5039656334233</v>
+        <v>169.8749393530998</v>
       </c>
       <c r="E132" t="n">
-        <v>63.4688519441675</v>
+        <v>42.78897640083702</v>
       </c>
       <c r="F132" t="n">
         <v>-73.34496083550914</v>
@@ -4410,13 +4410,13 @@
         <v>149.3973113207548</v>
       </c>
       <c r="C133" t="n">
-        <v>63.50551046859421</v>
+        <v>41.35718960706812</v>
       </c>
       <c r="D133" t="n">
-        <v>149.3973113207548</v>
+        <v>169.7682850404313</v>
       </c>
       <c r="E133" t="n">
-        <v>63.50551046859421</v>
+        <v>42.6696608346896</v>
       </c>
       <c r="F133" t="n">
         <v>-74.14584856396868</v>
@@ -4439,13 +4439,13 @@
         <v>149.2906570080863</v>
       </c>
       <c r="C134" t="n">
-        <v>63.54216899302094</v>
+        <v>41.23787404092072</v>
       </c>
       <c r="D134" t="n">
-        <v>149.2906570080863</v>
+        <v>169.6616307277629</v>
       </c>
       <c r="E134" t="n">
-        <v>63.54216899302094</v>
+        <v>42.55034526854219</v>
       </c>
       <c r="F134" t="n">
         <v>-74.94673629242817</v>
@@ -4468,13 +4468,13 @@
         <v>149.1840026954179</v>
       </c>
       <c r="C135" t="n">
-        <v>63.57882751744765</v>
+        <v>41.11855847477331</v>
       </c>
       <c r="D135" t="n">
-        <v>149.1840026954179</v>
+        <v>169.5549764150944</v>
       </c>
       <c r="E135" t="n">
-        <v>63.57882751744765</v>
+        <v>42.43102970239479</v>
       </c>
       <c r="F135" t="n">
         <v>-75.74762402088771</v>
@@ -4497,13 +4497,13 @@
         <v>149.0773483827494</v>
       </c>
       <c r="C136" t="n">
-        <v>63.61548604187438</v>
+        <v>40.9992429086259</v>
       </c>
       <c r="D136" t="n">
-        <v>149.0773483827494</v>
+        <v>169.4483221024259</v>
       </c>
       <c r="E136" t="n">
-        <v>63.61548604187438</v>
+        <v>42.31171413624738</v>
       </c>
       <c r="F136" t="n">
         <v>-76.54851174934726</v>
@@ -4526,13 +4526,13 @@
         <v>148.970694070081</v>
       </c>
       <c r="C137" t="n">
-        <v>63.65214456630109</v>
+        <v>40.87992734247849</v>
       </c>
       <c r="D137" t="n">
-        <v>148.970694070081</v>
+        <v>169.3416677897575</v>
       </c>
       <c r="E137" t="n">
-        <v>63.65214456630109</v>
+        <v>42.19239857009998</v>
       </c>
       <c r="F137" t="n">
         <v>-77.3493994778068</v>
@@ -4555,13 +4555,13 @@
         <v>148.8640397574125</v>
       </c>
       <c r="C138" t="n">
-        <v>63.68880309072781</v>
+        <v>40.76061177633108</v>
       </c>
       <c r="D138" t="n">
-        <v>148.8640397574125</v>
+        <v>169.235013477089</v>
       </c>
       <c r="E138" t="n">
-        <v>63.68880309072781</v>
+        <v>42.07308300395256</v>
       </c>
       <c r="F138" t="n">
         <v>-78.15028720626634</v>
@@ -4584,13 +4584,13 @@
         <v>148.757385444744</v>
       </c>
       <c r="C139" t="n">
-        <v>63.72546161515453</v>
+        <v>40.64129621018368</v>
       </c>
       <c r="D139" t="n">
-        <v>148.757385444744</v>
+        <v>169.1283591644205</v>
       </c>
       <c r="E139" t="n">
-        <v>63.72546161515453</v>
+        <v>41.95376743780515</v>
       </c>
       <c r="F139" t="n">
         <v>-78.95117493472583</v>
@@ -4613,13 +4613,13 @@
         <v>148.6507311320756</v>
       </c>
       <c r="C140" t="n">
-        <v>63.76212013958125</v>
+        <v>40.52198064403627</v>
       </c>
       <c r="D140" t="n">
-        <v>148.6507311320756</v>
+        <v>169.0217048517521</v>
       </c>
       <c r="E140" t="n">
-        <v>63.76212013958125</v>
+        <v>41.83445187165775</v>
       </c>
       <c r="F140" t="n">
         <v>-79.75206266318537</v>
@@ -4642,13 +4642,13 @@
         <v>148.5440768194071</v>
       </c>
       <c r="C141" t="n">
-        <v>63.79877866400797</v>
+        <v>40.40266507788886</v>
       </c>
       <c r="D141" t="n">
-        <v>148.5440768194071</v>
+        <v>168.9150505390836</v>
       </c>
       <c r="E141" t="n">
-        <v>63.79877866400797</v>
+        <v>41.71513630551034</v>
       </c>
       <c r="F141" t="n">
         <v>-80.55295039164491</v>
@@ -4671,13 +4671,13 @@
         <v>148.4374225067386</v>
       </c>
       <c r="C142" t="n">
-        <v>63.83543718843469</v>
+        <v>40.28334951174145</v>
       </c>
       <c r="D142" t="n">
-        <v>148.4374225067386</v>
+        <v>168.8083962264151</v>
       </c>
       <c r="E142" t="n">
-        <v>63.83543718843469</v>
+        <v>41.59582073936294</v>
       </c>
       <c r="F142" t="n">
         <v>-81.35383812010446</v>
@@ -4700,13 +4700,13 @@
         <v>148.3307681940702</v>
       </c>
       <c r="C143" t="n">
-        <v>63.87209571286141</v>
+        <v>40.16403394559404</v>
       </c>
       <c r="D143" t="n">
-        <v>148.3307681940702</v>
+        <v>168.7017419137467</v>
       </c>
       <c r="E143" t="n">
-        <v>63.87209571286141</v>
+        <v>41.47650517321553</v>
       </c>
       <c r="F143" t="n">
         <v>-82.15472584856394</v>
@@ -4729,13 +4729,13 @@
         <v>148.2241138814017</v>
       </c>
       <c r="C144" t="n">
-        <v>63.90875423728813</v>
+        <v>40.04471837944664</v>
       </c>
       <c r="D144" t="n">
-        <v>148.2241138814017</v>
+        <v>168.5950876010782</v>
       </c>
       <c r="E144" t="n">
-        <v>63.90875423728813</v>
+        <v>41.35718960706812</v>
       </c>
       <c r="F144" t="n">
         <v>-82.95561357702348</v>
@@ -4758,13 +4758,13 @@
         <v>148.1174595687332</v>
       </c>
       <c r="C145" t="n">
-        <v>63.94541276171485</v>
+        <v>39.92540281329923</v>
       </c>
       <c r="D145" t="n">
-        <v>148.1174595687332</v>
+        <v>168.4884332884097</v>
       </c>
       <c r="E145" t="n">
-        <v>63.94541276171485</v>
+        <v>41.23787404092072</v>
       </c>
       <c r="F145" t="n">
         <v>-83.75650130548303</v>
@@ -4787,13 +4787,13 @@
         <v>148.0108052560648</v>
       </c>
       <c r="C146" t="n">
-        <v>63.98207128614157</v>
+        <v>39.80608724715182</v>
       </c>
       <c r="D146" t="n">
-        <v>148.0108052560648</v>
+        <v>168.3817789757413</v>
       </c>
       <c r="E146" t="n">
-        <v>63.98207128614157</v>
+        <v>41.11855847477331</v>
       </c>
       <c r="F146" t="n">
         <v>-84.55738903394257</v>
@@ -4816,13 +4816,13 @@
         <v>147.9041509433963</v>
       </c>
       <c r="C147" t="n">
-        <v>64.01872981056829</v>
+        <v>39.68677168100442</v>
       </c>
       <c r="D147" t="n">
-        <v>147.9041509433963</v>
+        <v>168.2751246630728</v>
       </c>
       <c r="E147" t="n">
-        <v>64.01872981056829</v>
+        <v>40.9992429086259</v>
       </c>
       <c r="F147" t="n">
         <v>-85.35827676240211</v>
@@ -4845,13 +4845,13 @@
         <v>147.7974966307279</v>
       </c>
       <c r="C148" t="n">
-        <v>64.05538833499502</v>
+        <v>39.56745611485701</v>
       </c>
       <c r="D148" t="n">
-        <v>147.7974966307279</v>
+        <v>168.1684703504044</v>
       </c>
       <c r="E148" t="n">
-        <v>64.05538833499502</v>
+        <v>40.87992734247849</v>
       </c>
       <c r="F148" t="n">
         <v>-86.1591644908616</v>
@@ -4874,13 +4874,13 @@
         <v>147.6908423180594</v>
       </c>
       <c r="C149" t="n">
-        <v>64.09204685942173</v>
+        <v>39.4481405487096</v>
       </c>
       <c r="D149" t="n">
-        <v>147.6908423180594</v>
+        <v>168.0618160377359</v>
       </c>
       <c r="E149" t="n">
-        <v>64.09204685942173</v>
+        <v>40.76061177633108</v>
       </c>
       <c r="F149" t="n">
         <v>-86.96005221932114</v>
@@ -4903,13 +4903,13 @@
         <v>147.5841880053909</v>
       </c>
       <c r="C150" t="n">
-        <v>64.12870538384846</v>
+        <v>39.3288249825622</v>
       </c>
       <c r="D150" t="n">
-        <v>147.5841880053909</v>
+        <v>167.9551617250674</v>
       </c>
       <c r="E150" t="n">
-        <v>64.12870538384846</v>
+        <v>40.64129621018368</v>
       </c>
       <c r="F150" t="n">
         <v>-87.76093994778068</v>
@@ -4932,13 +4932,13 @@
         <v>147.4775336927225</v>
       </c>
       <c r="C151" t="n">
-        <v>64.16536390827517</v>
+        <v>39.20950941641478</v>
       </c>
       <c r="D151" t="n">
-        <v>147.4775336927225</v>
+        <v>167.848507412399</v>
       </c>
       <c r="E151" t="n">
-        <v>64.16536390827517</v>
+        <v>40.52198064403627</v>
       </c>
       <c r="F151" t="n">
         <v>-88.56182767624023</v>
@@ -4961,13 +4961,13 @@
         <v>147.370879380054</v>
       </c>
       <c r="C152" t="n">
-        <v>64.2020224327019</v>
+        <v>39.09019385026738</v>
       </c>
       <c r="D152" t="n">
-        <v>147.370879380054</v>
+        <v>167.7418530997305</v>
       </c>
       <c r="E152" t="n">
-        <v>64.2020224327019</v>
+        <v>40.40266507788886</v>
       </c>
       <c r="F152" t="n">
         <v>-89.36271540469971</v>
@@ -4990,13 +4990,13 @@
         <v>147.2642250673856</v>
       </c>
       <c r="C153" t="n">
-        <v>64.23868095712861</v>
+        <v>38.97087828411997</v>
       </c>
       <c r="D153" t="n">
-        <v>147.2642250673856</v>
+        <v>167.6351987870621</v>
       </c>
       <c r="E153" t="n">
-        <v>64.23868095712861</v>
+        <v>40.28334951174145</v>
       </c>
       <c r="F153" t="n">
         <v>-90.16360313315926</v>
@@ -5019,13 +5019,13 @@
         <v>147.1575707547171</v>
       </c>
       <c r="C154" t="n">
-        <v>64.27533948155533</v>
+        <v>38.85156271797256</v>
       </c>
       <c r="D154" t="n">
-        <v>147.1575707547171</v>
+        <v>167.5285444743936</v>
       </c>
       <c r="E154" t="n">
-        <v>64.27533948155533</v>
+        <v>40.16403394559404</v>
       </c>
       <c r="F154" t="n">
         <v>-90.9644908616188</v>
@@ -5048,13 +5048,13 @@
         <v>147.0509164420486</v>
       </c>
       <c r="C155" t="n">
-        <v>64.31199800598205</v>
+        <v>38.73224715182515</v>
       </c>
       <c r="D155" t="n">
-        <v>147.0509164420486</v>
+        <v>167.4218901617251</v>
       </c>
       <c r="E155" t="n">
-        <v>64.31199800598205</v>
+        <v>40.04471837944664</v>
       </c>
       <c r="F155" t="n">
         <v>-91.76537859007834</v>
@@ -5077,13 +5077,13 @@
         <v>146.9442621293801</v>
       </c>
       <c r="C156" t="n">
-        <v>64.34865653040877</v>
+        <v>38.61293158567774</v>
       </c>
       <c r="D156" t="n">
-        <v>146.9442621293801</v>
+        <v>167.3152358490566</v>
       </c>
       <c r="E156" t="n">
-        <v>64.34865653040877</v>
+        <v>39.92540281329923</v>
       </c>
       <c r="F156" t="n">
         <v>-92.56626631853788</v>
@@ -5106,13 +5106,13 @@
         <v>146.8376078167117</v>
       </c>
       <c r="C157" t="n">
-        <v>64.38531505483549</v>
+        <v>38.49361601953034</v>
       </c>
       <c r="D157" t="n">
-        <v>146.8376078167117</v>
+        <v>167.2085815363882</v>
       </c>
       <c r="E157" t="n">
-        <v>64.38531505483549</v>
+        <v>39.80608724715182</v>
       </c>
       <c r="F157" t="n">
         <v>-93.36715404699737</v>
@@ -5135,13 +5135,13 @@
         <v>146.7309535040432</v>
       </c>
       <c r="C158" t="n">
-        <v>64.42197357926221</v>
+        <v>38.37430045338293</v>
       </c>
       <c r="D158" t="n">
-        <v>146.7309535040432</v>
+        <v>167.1019272237197</v>
       </c>
       <c r="E158" t="n">
-        <v>64.42197357926221</v>
+        <v>39.68677168100442</v>
       </c>
       <c r="F158" t="n">
         <v>-94.16804177545691</v>
@@ -5164,13 +5164,13 @@
         <v>146.6242991913747</v>
       </c>
       <c r="C159" t="n">
-        <v>64.45863210368893</v>
+        <v>38.25498488723552</v>
       </c>
       <c r="D159" t="n">
-        <v>146.6242991913747</v>
+        <v>166.9952729110512</v>
       </c>
       <c r="E159" t="n">
-        <v>64.45863210368893</v>
+        <v>39.56745611485701</v>
       </c>
       <c r="F159" t="n">
         <v>-94.96892950391646</v>
@@ -5193,13 +5193,13 @@
         <v>146.5176448787063</v>
       </c>
       <c r="C160" t="n">
-        <v>64.49529062811565</v>
+        <v>38.13566932108812</v>
       </c>
       <c r="D160" t="n">
-        <v>146.5176448787063</v>
+        <v>166.8886185983828</v>
       </c>
       <c r="E160" t="n">
-        <v>64.49529062811565</v>
+        <v>39.4481405487096</v>
       </c>
       <c r="F160" t="n">
         <v>-95.769817232376</v>
@@ -5222,13 +5222,13 @@
         <v>146.4109905660378</v>
       </c>
       <c r="C161" t="n">
-        <v>64.53194915254237</v>
+        <v>38.01635375494071</v>
       </c>
       <c r="D161" t="n">
-        <v>146.4109905660378</v>
+        <v>166.7819642857143</v>
       </c>
       <c r="E161" t="n">
-        <v>64.53194915254237</v>
+        <v>39.3288249825622</v>
       </c>
       <c r="F161" t="n">
         <v>-96.57070496083549</v>
@@ -5251,13 +5251,13 @@
         <v>146.3043362533694</v>
       </c>
       <c r="C162" t="n">
-        <v>64.56860767696909</v>
+        <v>37.8970381887933</v>
       </c>
       <c r="D162" t="n">
-        <v>146.3043362533694</v>
+        <v>166.6753099730459</v>
       </c>
       <c r="E162" t="n">
-        <v>64.56860767696909</v>
+        <v>39.20950941641478</v>
       </c>
       <c r="F162" t="n">
         <v>-97.37159268929503</v>
@@ -5280,13 +5280,13 @@
         <v>146.1976819407009</v>
       </c>
       <c r="C163" t="n">
-        <v>64.60526620139581</v>
+        <v>37.7777226226459</v>
       </c>
       <c r="D163" t="n">
-        <v>146.1976819407009</v>
+        <v>166.5686556603774</v>
       </c>
       <c r="E163" t="n">
-        <v>64.60526620139581</v>
+        <v>39.09019385026738</v>
       </c>
       <c r="F163" t="n">
         <v>-98.17248041775457</v>
@@ -5309,13 +5309,13 @@
         <v>146.0910276280324</v>
       </c>
       <c r="C164" t="n">
-        <v>64.64192472582253</v>
+        <v>37.65840705649849</v>
       </c>
       <c r="D164" t="n">
-        <v>146.0910276280324</v>
+        <v>166.4620013477089</v>
       </c>
       <c r="E164" t="n">
-        <v>64.64192472582253</v>
+        <v>38.97087828411997</v>
       </c>
       <c r="F164" t="n">
         <v>-98.97336814621411</v>
@@ -5338,13 +5338,13 @@
         <v>145.984373315364</v>
       </c>
       <c r="C165" t="n">
-        <v>64.67858325024925</v>
+        <v>37.53909149035108</v>
       </c>
       <c r="D165" t="n">
-        <v>145.984373315364</v>
+        <v>166.3553470350405</v>
       </c>
       <c r="E165" t="n">
-        <v>64.67858325024925</v>
+        <v>38.85156271797256</v>
       </c>
       <c r="F165" t="n">
         <v>-99.7742558746736</v>
@@ -5367,13 +5367,13 @@
         <v>145.8777190026955</v>
       </c>
       <c r="C166" t="n">
-        <v>64.71524177467597</v>
+        <v>37.41977592420367</v>
       </c>
       <c r="D166" t="n">
-        <v>145.8777190026955</v>
+        <v>166.248692722372</v>
       </c>
       <c r="E166" t="n">
-        <v>64.71524177467597</v>
+        <v>38.73224715182515</v>
       </c>
       <c r="F166" t="n">
         <v>-100.5751436031331</v>
@@ -5396,13 +5396,13 @@
         <v>145.7710646900271</v>
       </c>
       <c r="C167" t="n">
-        <v>64.75190029910269</v>
+        <v>37.30046035805626</v>
       </c>
       <c r="D167" t="n">
-        <v>145.7710646900271</v>
+        <v>166.1420384097036</v>
       </c>
       <c r="E167" t="n">
-        <v>64.75190029910269</v>
+        <v>38.61293158567774</v>
       </c>
       <c r="F167" t="n">
         <v>-101.3760313315927</v>
@@ -5425,13 +5425,13 @@
         <v>145.6644103773586</v>
       </c>
       <c r="C168" t="n">
-        <v>64.78855882352941</v>
+        <v>37.18114479190886</v>
       </c>
       <c r="D168" t="n">
-        <v>145.6644103773586</v>
+        <v>166.0353840970351</v>
       </c>
       <c r="E168" t="n">
-        <v>64.78855882352941</v>
+        <v>38.49361601953034</v>
       </c>
       <c r="F168" t="n">
         <v>-102.1769190600522</v>
@@ -5454,13 +5454,13 @@
         <v>145.5577560646901</v>
       </c>
       <c r="C169" t="n">
-        <v>64.82521734795613</v>
+        <v>37.06182922576144</v>
       </c>
       <c r="D169" t="n">
-        <v>145.5577560646901</v>
+        <v>165.9287297843666</v>
       </c>
       <c r="E169" t="n">
-        <v>64.82521734795613</v>
+        <v>38.37430045338293</v>
       </c>
       <c r="F169" t="n">
         <v>-102.9778067885118</v>
@@ -5483,13 +5483,13 @@
         <v>145.4511017520217</v>
       </c>
       <c r="C170" t="n">
-        <v>64.86187587238285</v>
+        <v>36.94251365961404</v>
       </c>
       <c r="D170" t="n">
-        <v>145.4511017520217</v>
+        <v>165.8220754716982</v>
       </c>
       <c r="E170" t="n">
-        <v>64.86187587238285</v>
+        <v>38.25498488723552</v>
       </c>
       <c r="F170" t="n">
         <v>-103.7786945169713</v>
@@ -5512,13 +5512,13 @@
         <v>145.3444474393532</v>
       </c>
       <c r="C171" t="n">
-        <v>64.89853439680957</v>
+        <v>36.82319809346663</v>
       </c>
       <c r="D171" t="n">
-        <v>145.3444474393532</v>
+        <v>165.7154211590297</v>
       </c>
       <c r="E171" t="n">
-        <v>64.89853439680957</v>
+        <v>38.13566932108812</v>
       </c>
       <c r="F171" t="n">
         <v>-104.5795822454308</v>
@@ -5541,13 +5541,13 @@
         <v>145.2377931266847</v>
       </c>
       <c r="C172" t="n">
-        <v>64.93519292123628</v>
+        <v>36.70388252731922</v>
       </c>
       <c r="D172" t="n">
-        <v>145.2377931266847</v>
+        <v>165.6087668463612</v>
       </c>
       <c r="E172" t="n">
-        <v>64.93519292123628</v>
+        <v>38.01635375494071</v>
       </c>
       <c r="F172" t="n">
         <v>-105.3804699738903</v>
@@ -5570,13 +5570,13 @@
         <v>145.1311388140163</v>
       </c>
       <c r="C173" t="n">
-        <v>64.97185144566301</v>
+        <v>36.58456696117182</v>
       </c>
       <c r="D173" t="n">
-        <v>145.1311388140163</v>
+        <v>165.5021125336928</v>
       </c>
       <c r="E173" t="n">
-        <v>64.97185144566301</v>
+        <v>37.8970381887933</v>
       </c>
       <c r="F173" t="n">
         <v>-106.1813577023499</v>
@@ -5599,13 +5599,13 @@
         <v>145.0244845013478</v>
       </c>
       <c r="C174" t="n">
-        <v>65.00850997008973</v>
+        <v>36.46525139502441</v>
       </c>
       <c r="D174" t="n">
-        <v>145.0244845013478</v>
+        <v>165.3954582210243</v>
       </c>
       <c r="E174" t="n">
-        <v>65.00850997008973</v>
+        <v>37.7777226226459</v>
       </c>
       <c r="F174" t="n">
         <v>-106.9822454308094</v>
@@ -5628,13 +5628,13 @@
         <v>144.9178301886793</v>
       </c>
       <c r="C175" t="n">
-        <v>65.04516849451645</v>
+        <v>36.345935828877</v>
       </c>
       <c r="D175" t="n">
-        <v>144.9178301886793</v>
+        <v>165.2888039083558</v>
       </c>
       <c r="E175" t="n">
-        <v>65.04516849451645</v>
+        <v>37.65840705649849</v>
       </c>
       <c r="F175" t="n">
         <v>-107.7831331592689</v>
@@ -5657,13 +5657,13 @@
         <v>144.8111758760109</v>
       </c>
       <c r="C176" t="n">
-        <v>65.08182701894316</v>
+        <v>36.2266202627296</v>
       </c>
       <c r="D176" t="n">
-        <v>144.8111758760109</v>
+        <v>165.1821495956874</v>
       </c>
       <c r="E176" t="n">
-        <v>65.08182701894316</v>
+        <v>37.53909149035108</v>
       </c>
       <c r="F176" t="n">
         <v>-108.5840208877285</v>
@@ -5686,13 +5686,13 @@
         <v>144.7045215633424</v>
       </c>
       <c r="C177" t="n">
-        <v>65.11848554336989</v>
+        <v>36.10730469658219</v>
       </c>
       <c r="D177" t="n">
-        <v>144.7045215633424</v>
+        <v>165.0754952830189</v>
       </c>
       <c r="E177" t="n">
-        <v>65.11848554336989</v>
+        <v>37.41977592420367</v>
       </c>
       <c r="F177" t="n">
         <v>-109.384908616188</v>
@@ -5715,13 +5715,13 @@
         <v>144.5978672506739</v>
       </c>
       <c r="C178" t="n">
-        <v>65.15514406779661</v>
+        <v>35.98798913043478</v>
       </c>
       <c r="D178" t="n">
-        <v>144.5978672506739</v>
+        <v>164.9688409703505</v>
       </c>
       <c r="E178" t="n">
-        <v>65.15514406779661</v>
+        <v>37.30046035805626</v>
       </c>
       <c r="F178" t="n">
         <v>-110.1857963446475</v>
@@ -5744,13 +5744,13 @@
         <v>144.4912129380055</v>
       </c>
       <c r="C179" t="n">
-        <v>65.19180259222333</v>
+        <v>35.86867356428737</v>
       </c>
       <c r="D179" t="n">
-        <v>144.4912129380055</v>
+        <v>164.862186657682</v>
       </c>
       <c r="E179" t="n">
-        <v>65.19180259222333</v>
+        <v>37.18114479190886</v>
       </c>
       <c r="F179" t="n">
         <v>-110.986684073107</v>
@@ -5773,13 +5773,13 @@
         <v>144.384558625337</v>
       </c>
       <c r="C180" t="n">
-        <v>65.22846111665004</v>
+        <v>35.74935799813996</v>
       </c>
       <c r="D180" t="n">
-        <v>144.384558625337</v>
+        <v>164.7555323450135</v>
       </c>
       <c r="E180" t="n">
-        <v>65.22846111665004</v>
+        <v>37.06182922576144</v>
       </c>
       <c r="F180" t="n">
         <v>-111.7875718015666</v>
@@ -5802,13 +5802,13 @@
         <v>144.2779043126686</v>
       </c>
       <c r="C181" t="n">
-        <v>65.26511964107677</v>
+        <v>35.63004243199256</v>
       </c>
       <c r="D181" t="n">
-        <v>144.2779043126686</v>
+        <v>164.6488780323451</v>
       </c>
       <c r="E181" t="n">
-        <v>65.26511964107677</v>
+        <v>36.94251365961404</v>
       </c>
       <c r="F181" t="n">
         <v>-112.5884595300261</v>
@@ -5831,13 +5831,13 @@
         <v>144.1712500000001</v>
       </c>
       <c r="C182" t="n">
-        <v>65.30177816550349</v>
+        <v>35.51072686584515</v>
       </c>
       <c r="D182" t="n">
-        <v>144.1712500000001</v>
+        <v>164.5422237196766</v>
       </c>
       <c r="E182" t="n">
-        <v>65.30177816550349</v>
+        <v>36.82319809346663</v>
       </c>
       <c r="F182" t="n">
         <v>-113.3893472584857</v>
@@ -5860,13 +5860,13 @@
         <v>144.0645956873316</v>
       </c>
       <c r="C183" t="n">
-        <v>65.33843668993021</v>
+        <v>35.39141129969774</v>
       </c>
       <c r="D183" t="n">
-        <v>144.0645956873316</v>
+        <v>164.4355694070081</v>
       </c>
       <c r="E183" t="n">
-        <v>65.33843668993021</v>
+        <v>36.70388252731922</v>
       </c>
       <c r="F183" t="n">
         <v>-114.1902349869451</v>
@@ -5889,13 +5889,13 @@
         <v>143.9579413746632</v>
       </c>
       <c r="C184" t="n">
-        <v>65.37509521435692</v>
+        <v>35.27209573355033</v>
       </c>
       <c r="D184" t="n">
-        <v>143.9579413746632</v>
+        <v>164.3289150943397</v>
       </c>
       <c r="E184" t="n">
-        <v>65.37509521435692</v>
+        <v>36.58456696117182</v>
       </c>
       <c r="F184" t="n">
         <v>-114.9911227154047</v>
@@ -5918,13 +5918,13 @@
         <v>143.8512870619947</v>
       </c>
       <c r="C185" t="n">
-        <v>65.41175373878364</v>
+        <v>35.15278016740292</v>
       </c>
       <c r="D185" t="n">
-        <v>143.8512870619947</v>
+        <v>164.2222607816712</v>
       </c>
       <c r="E185" t="n">
-        <v>65.41175373878364</v>
+        <v>36.46525139502441</v>
       </c>
       <c r="F185" t="n">
         <v>-115.7920104438642</v>
@@ -5947,13 +5947,13 @@
         <v>143.7446327493262</v>
       </c>
       <c r="C186" t="n">
-        <v>65.44841226321036</v>
+        <v>35.03346460125552</v>
       </c>
       <c r="D186" t="n">
-        <v>143.7446327493262</v>
+        <v>164.1156064690028</v>
       </c>
       <c r="E186" t="n">
-        <v>65.44841226321036</v>
+        <v>36.345935828877</v>
       </c>
       <c r="F186" t="n">
         <v>-116.5928981723238</v>
@@ -5976,13 +5976,13 @@
         <v>143.6379784366578</v>
       </c>
       <c r="C187" t="n">
-        <v>65.48507078763708</v>
+        <v>34.91414903510811</v>
       </c>
       <c r="D187" t="n">
-        <v>143.6379784366578</v>
+        <v>164.0089521563343</v>
       </c>
       <c r="E187" t="n">
-        <v>65.48507078763708</v>
+        <v>36.2266202627296</v>
       </c>
       <c r="F187" t="n">
         <v>-117.3937859007833</v>
@@ -6005,13 +6005,13 @@
         <v>143.5313241239893</v>
       </c>
       <c r="C188" t="n">
-        <v>65.5217293120638</v>
+        <v>34.7948334689607</v>
       </c>
       <c r="D188" t="n">
-        <v>143.5313241239893</v>
+        <v>163.9022978436658</v>
       </c>
       <c r="E188" t="n">
-        <v>65.5217293120638</v>
+        <v>36.10730469658219</v>
       </c>
       <c r="F188" t="n">
         <v>-118.1946736292428</v>
@@ -6034,13 +6034,13 @@
         <v>143.4246698113209</v>
       </c>
       <c r="C189" t="n">
-        <v>65.55838783649052</v>
+        <v>34.6755179028133</v>
       </c>
       <c r="D189" t="n">
-        <v>143.4246698113209</v>
+        <v>163.7956435309974</v>
       </c>
       <c r="E189" t="n">
-        <v>65.55838783649052</v>
+        <v>35.98798913043478</v>
       </c>
       <c r="F189" t="n">
         <v>-118.9955613577023</v>
@@ -6063,13 +6063,13 @@
         <v>143.3180154986524</v>
       </c>
       <c r="C190" t="n">
-        <v>65.59504636091724</v>
+        <v>34.55620233666589</v>
       </c>
       <c r="D190" t="n">
-        <v>143.3180154986524</v>
+        <v>163.6889892183289</v>
       </c>
       <c r="E190" t="n">
-        <v>65.59504636091724</v>
+        <v>35.86867356428737</v>
       </c>
       <c r="F190" t="n">
         <v>-119.7964490861619</v>
@@ -6092,13 +6092,13 @@
         <v>143.2113611859839</v>
       </c>
       <c r="C191" t="n">
-        <v>65.63170488534396</v>
+        <v>34.43688677051848</v>
       </c>
       <c r="D191" t="n">
-        <v>143.2113611859839</v>
+        <v>163.5823349056604</v>
       </c>
       <c r="E191" t="n">
-        <v>65.63170488534396</v>
+        <v>35.74935799813996</v>
       </c>
       <c r="F191" t="n">
         <v>-120.5973368146214</v>
@@ -6121,13 +6121,13 @@
         <v>143.1047068733155</v>
       </c>
       <c r="C192" t="n">
-        <v>65.66836340977068</v>
+        <v>34.31757120437108</v>
       </c>
       <c r="D192" t="n">
-        <v>143.1047068733155</v>
+        <v>163.475680592992</v>
       </c>
       <c r="E192" t="n">
-        <v>65.66836340977068</v>
+        <v>35.63004243199256</v>
       </c>
       <c r="F192" t="n">
         <v>-121.3982245430809</v>
@@ -6150,13 +6150,13 @@
         <v>142.998052560647</v>
       </c>
       <c r="C193" t="n">
-        <v>65.7050219341974</v>
+        <v>34.19825563822366</v>
       </c>
       <c r="D193" t="n">
-        <v>142.998052560647</v>
+        <v>163.3690262803235</v>
       </c>
       <c r="E193" t="n">
-        <v>65.7050219341974</v>
+        <v>35.51072686584515</v>
       </c>
       <c r="F193" t="n">
         <v>-122.1991122715405</v>
@@ -6179,13 +6179,13 @@
         <v>142.8913982479785</v>
       </c>
       <c r="C194" t="n">
-        <v>65.74168045862412</v>
+        <v>34.07894007207626</v>
       </c>
       <c r="D194" t="n">
-        <v>142.8913982479785</v>
+        <v>163.262371967655</v>
       </c>
       <c r="E194" t="n">
-        <v>65.74168045862412</v>
+        <v>35.39141129969774</v>
       </c>
       <c r="F194" t="n">
         <v>-123</v>
@@ -6208,13 +6208,13 @@
         <v>142.7847439353101</v>
       </c>
       <c r="C195" t="n">
-        <v>65.77833898305084</v>
+        <v>33.95962450592885</v>
       </c>
       <c r="D195" t="n">
-        <v>142.7847439353101</v>
+        <v>163.1557176549866</v>
       </c>
       <c r="E195" t="n">
-        <v>65.77833898305084</v>
+        <v>35.27209573355033</v>
       </c>
       <c r="F195" t="n">
         <v>-123</v>
@@ -6237,13 +6237,13 @@
         <v>142.6780896226416</v>
       </c>
       <c r="C196" t="n">
-        <v>65.81499750747756</v>
+        <v>33.84030893978144</v>
       </c>
       <c r="D196" t="n">
-        <v>142.6780896226416</v>
+        <v>163.0490633423181</v>
       </c>
       <c r="E196" t="n">
-        <v>65.81499750747756</v>
+        <v>35.15278016740292</v>
       </c>
       <c r="F196" t="n">
         <v>-123</v>
@@ -6266,13 +6266,13 @@
         <v>142.5714353099731</v>
       </c>
       <c r="C197" t="n">
-        <v>65.85165603190428</v>
+        <v>33.72099337363403</v>
       </c>
       <c r="D197" t="n">
-        <v>142.5714353099731</v>
+        <v>162.9424090296496</v>
       </c>
       <c r="E197" t="n">
-        <v>65.85165603190428</v>
+        <v>35.03346460125552</v>
       </c>
       <c r="F197" t="n">
         <v>-123</v>
@@ -6295,13 +6295,13 @@
         <v>142.4647809973047</v>
       </c>
       <c r="C198" t="n">
-        <v>65.888314556331</v>
+        <v>33.60167780748662</v>
       </c>
       <c r="D198" t="n">
-        <v>142.4647809973047</v>
+        <v>162.8357547169812</v>
       </c>
       <c r="E198" t="n">
-        <v>65.888314556331</v>
+        <v>34.91414903510811</v>
       </c>
       <c r="F198" t="n">
         <v>-123</v>
@@ -6324,13 +6324,13 @@
         <v>142.3581266846362</v>
       </c>
       <c r="C199" t="n">
-        <v>65.92497308075772</v>
+        <v>33.48236224133922</v>
       </c>
       <c r="D199" t="n">
-        <v>142.3581266846362</v>
+        <v>162.7291004043127</v>
       </c>
       <c r="E199" t="n">
-        <v>65.92497308075772</v>
+        <v>34.7948334689607</v>
       </c>
       <c r="F199" t="n">
         <v>-123</v>
@@ -6353,13 +6353,13 @@
         <v>142.2514723719678</v>
       </c>
       <c r="C200" t="n">
-        <v>65.96163160518444</v>
+        <v>33.36304667519181</v>
       </c>
       <c r="D200" t="n">
-        <v>142.2514723719678</v>
+        <v>162.6224460916443</v>
       </c>
       <c r="E200" t="n">
-        <v>65.96163160518444</v>
+        <v>34.6755179028133</v>
       </c>
       <c r="F200" t="n">
         <v>-123</v>
@@ -6382,13 +6382,13 @@
         <v>142.1448180592993</v>
       </c>
       <c r="C201" t="n">
-        <v>65.99829012961116</v>
+        <v>33.2437311090444</v>
       </c>
       <c r="D201" t="n">
-        <v>142.1448180592993</v>
+        <v>162.5157917789758</v>
       </c>
       <c r="E201" t="n">
-        <v>65.99829012961116</v>
+        <v>34.55620233666589</v>
       </c>
       <c r="F201" t="n">
         <v>-123</v>
@@ -6411,13 +6411,13 @@
         <v>142.0381637466308</v>
       </c>
       <c r="C202" t="n">
-        <v>66.03494865403788</v>
+        <v>33.124415542897</v>
       </c>
       <c r="D202" t="n">
-        <v>142.0381637466308</v>
+        <v>162.4091374663073</v>
       </c>
       <c r="E202" t="n">
-        <v>66.03494865403788</v>
+        <v>34.43688677051848</v>
       </c>
       <c r="F202" t="n">
         <v>-123</v>
@@ -6440,13 +6440,13 @@
         <v>141.9315094339624</v>
       </c>
       <c r="C203" t="n">
-        <v>66.0716071784646</v>
+        <v>33.00509997674959</v>
       </c>
       <c r="D203" t="n">
-        <v>141.9315094339624</v>
+        <v>162.3024831536389</v>
       </c>
       <c r="E203" t="n">
-        <v>66.0716071784646</v>
+        <v>34.31757120437108</v>
       </c>
       <c r="F203" t="n">
         <v>-123</v>
@@ -6469,13 +6469,13 @@
         <v>141.8248551212939</v>
       </c>
       <c r="C204" t="n">
-        <v>66.10826570289132</v>
+        <v>32.88578441060218</v>
       </c>
       <c r="D204" t="n">
-        <v>141.8248551212939</v>
+        <v>162.1958288409704</v>
       </c>
       <c r="E204" t="n">
-        <v>66.10826570289132</v>
+        <v>34.19825563822366</v>
       </c>
       <c r="F204" t="n">
         <v>-123</v>
@@ -6498,13 +6498,13 @@
         <v>141.7182008086255</v>
       </c>
       <c r="C205" t="n">
-        <v>66.14492422731804</v>
+        <v>32.76646884445478</v>
       </c>
       <c r="D205" t="n">
-        <v>141.7182008086255</v>
+        <v>162.089174528302</v>
       </c>
       <c r="E205" t="n">
-        <v>66.14492422731804</v>
+        <v>34.07894007207626</v>
       </c>
       <c r="F205" t="n">
         <v>-123</v>
@@ -6527,13 +6527,13 @@
         <v>141.611546495957</v>
       </c>
       <c r="C206" t="n">
-        <v>66.18158275174476</v>
+        <v>32.64715327830737</v>
       </c>
       <c r="D206" t="n">
-        <v>141.611546495957</v>
+        <v>161.9825202156335</v>
       </c>
       <c r="E206" t="n">
-        <v>66.18158275174476</v>
+        <v>33.95962450592885</v>
       </c>
       <c r="F206" t="n">
         <v>-123</v>
@@ -6556,13 +6556,13 @@
         <v>141.5048921832885</v>
       </c>
       <c r="C207" t="n">
-        <v>66.21824127617148</v>
+        <v>32.52783771215996</v>
       </c>
       <c r="D207" t="n">
-        <v>141.5048921832885</v>
+        <v>161.875865902965</v>
       </c>
       <c r="E207" t="n">
-        <v>66.21824127617148</v>
+        <v>33.84030893978144</v>
       </c>
       <c r="F207" t="n">
         <v>-123</v>
@@ -6585,13 +6585,13 @@
         <v>141.3982378706201</v>
       </c>
       <c r="C208" t="n">
-        <v>66.2548998005982</v>
+        <v>32.40852214601255</v>
       </c>
       <c r="D208" t="n">
-        <v>141.3982378706201</v>
+        <v>161.7692115902965</v>
       </c>
       <c r="E208" t="n">
-        <v>66.2548998005982</v>
+        <v>33.72099337363403</v>
       </c>
       <c r="F208" t="n">
         <v>-123</v>
@@ -6614,13 +6614,13 @@
         <v>141.2915835579516</v>
       </c>
       <c r="C209" t="n">
-        <v>66.29155832502492</v>
+        <v>32.28920657986514</v>
       </c>
       <c r="D209" t="n">
-        <v>141.2915835579516</v>
+        <v>161.6625572776281</v>
       </c>
       <c r="E209" t="n">
-        <v>66.29155832502492</v>
+        <v>33.60167780748662</v>
       </c>
       <c r="F209" t="n">
         <v>-123</v>
@@ -6643,13 +6643,13 @@
         <v>141.1849292452831</v>
       </c>
       <c r="C210" t="n">
-        <v>66.32821684945164</v>
+        <v>32.16989101371774</v>
       </c>
       <c r="D210" t="n">
-        <v>141.1849292452831</v>
+        <v>161.5559029649596</v>
       </c>
       <c r="E210" t="n">
-        <v>66.32821684945164</v>
+        <v>33.48236224133922</v>
       </c>
       <c r="F210" t="n">
         <v>-123</v>
@@ -6672,13 +6672,13 @@
         <v>141.0782749326146</v>
       </c>
       <c r="C211" t="n">
-        <v>66.36487537387836</v>
+        <v>32.05057544757032</v>
       </c>
       <c r="D211" t="n">
-        <v>141.0782749326146</v>
+        <v>161.4492486522912</v>
       </c>
       <c r="E211" t="n">
-        <v>66.36487537387836</v>
+        <v>33.36304667519181</v>
       </c>
       <c r="F211" t="n">
         <v>-123</v>
@@ -6701,13 +6701,13 @@
         <v>140.9716206199462</v>
       </c>
       <c r="C212" t="n">
-        <v>66.40153389830508</v>
+        <v>31.93125988142292</v>
       </c>
       <c r="D212" t="n">
-        <v>140.9716206199462</v>
+        <v>161.3425943396227</v>
       </c>
       <c r="E212" t="n">
-        <v>66.40153389830508</v>
+        <v>33.2437311090444</v>
       </c>
       <c r="F212" t="n">
         <v>-123</v>
@@ -6730,13 +6730,13 @@
         <v>140.8649663072777</v>
       </c>
       <c r="C213" t="n">
-        <v>66.4381924227318</v>
+        <v>31.81194431527551</v>
       </c>
       <c r="D213" t="n">
-        <v>140.8649663072777</v>
+        <v>161.2359400269542</v>
       </c>
       <c r="E213" t="n">
-        <v>66.4381924227318</v>
+        <v>33.124415542897</v>
       </c>
       <c r="F213" t="n">
         <v>-123</v>
@@ -6759,13 +6759,13 @@
         <v>140.7583119946093</v>
       </c>
       <c r="C214" t="n">
-        <v>66.47485094715852</v>
+        <v>31.6926287491281</v>
       </c>
       <c r="D214" t="n">
-        <v>140.7583119946093</v>
+        <v>161.1292857142858</v>
       </c>
       <c r="E214" t="n">
-        <v>66.47485094715852</v>
+        <v>33.00509997674959</v>
       </c>
       <c r="F214" t="n">
         <v>-123</v>
@@ -6788,13 +6788,13 @@
         <v>140.6516576819408</v>
       </c>
       <c r="C215" t="n">
-        <v>66.51150947158524</v>
+        <v>31.5733131829807</v>
       </c>
       <c r="D215" t="n">
-        <v>140.6516576819408</v>
+        <v>161.0226314016173</v>
       </c>
       <c r="E215" t="n">
-        <v>66.51150947158524</v>
+        <v>32.88578441060218</v>
       </c>
       <c r="F215" t="n">
         <v>-123</v>
@@ -6817,13 +6817,13 @@
         <v>140.5450033692723</v>
       </c>
       <c r="C216" t="n">
-        <v>66.54816799601195</v>
+        <v>31.45399761683329</v>
       </c>
       <c r="D216" t="n">
-        <v>140.5450033692723</v>
+        <v>160.9159770889489</v>
       </c>
       <c r="E216" t="n">
-        <v>66.54816799601195</v>
+        <v>32.76646884445478</v>
       </c>
       <c r="F216" t="n">
         <v>-123</v>
@@ -6846,13 +6846,13 @@
         <v>140.4383490566039</v>
       </c>
       <c r="C217" t="n">
-        <v>66.58482652043868</v>
+        <v>31.33468205068588</v>
       </c>
       <c r="D217" t="n">
-        <v>140.4383490566039</v>
+        <v>160.8093227762804</v>
       </c>
       <c r="E217" t="n">
-        <v>66.58482652043868</v>
+        <v>32.64715327830737</v>
       </c>
       <c r="F217" t="n">
         <v>-123</v>
@@ -6875,13 +6875,13 @@
         <v>140.3316947439354</v>
       </c>
       <c r="C218" t="n">
-        <v>66.62148504486539</v>
+        <v>31.21536648453847</v>
       </c>
       <c r="D218" t="n">
-        <v>140.3316947439354</v>
+        <v>160.7026684636119</v>
       </c>
       <c r="E218" t="n">
-        <v>66.62148504486539</v>
+        <v>32.52783771215996</v>
       </c>
       <c r="F218" t="n">
         <v>-123</v>
@@ -6904,13 +6904,13 @@
         <v>140.225040431267</v>
       </c>
       <c r="C219" t="n">
-        <v>66.65814356929212</v>
+        <v>31.09605091839107</v>
       </c>
       <c r="D219" t="n">
-        <v>140.225040431267</v>
+        <v>160.5960141509435</v>
       </c>
       <c r="E219" t="n">
-        <v>66.65814356929212</v>
+        <v>32.40852214601255</v>
       </c>
       <c r="F219" t="n">
         <v>-123</v>
@@ -6933,13 +6933,13 @@
         <v>140.1183861185985</v>
       </c>
       <c r="C220" t="n">
-        <v>66.69480209371883</v>
+        <v>30.97673535224366</v>
       </c>
       <c r="D220" t="n">
-        <v>140.1183861185985</v>
+        <v>160.489359838275</v>
       </c>
       <c r="E220" t="n">
-        <v>66.69480209371883</v>
+        <v>32.28920657986514</v>
       </c>
       <c r="F220" t="n">
         <v>-123</v>
@@ -6962,13 +6962,13 @@
         <v>140.01173180593</v>
       </c>
       <c r="C221" t="n">
-        <v>66.73146061814556</v>
+        <v>30.85741978609625</v>
       </c>
       <c r="D221" t="n">
-        <v>140.01173180593</v>
+        <v>160.3827055256065</v>
       </c>
       <c r="E221" t="n">
-        <v>66.73146061814556</v>
+        <v>32.16989101371774</v>
       </c>
       <c r="F221" t="n">
         <v>-123</v>
@@ -6991,13 +6991,13 @@
         <v>139.9050774932616</v>
       </c>
       <c r="C222" t="n">
-        <v>66.76811914257227</v>
+        <v>30.73810421994884</v>
       </c>
       <c r="D222" t="n">
-        <v>139.9050774932616</v>
+        <v>160.2760512129381</v>
       </c>
       <c r="E222" t="n">
-        <v>66.76811914257227</v>
+        <v>32.05057544757032</v>
       </c>
       <c r="F222" t="n">
         <v>-123</v>
@@ -7020,13 +7020,13 @@
         <v>139.7984231805931</v>
       </c>
       <c r="C223" t="n">
-        <v>66.804777666999</v>
+        <v>30.61878865380144</v>
       </c>
       <c r="D223" t="n">
-        <v>139.7984231805931</v>
+        <v>160.1693969002696</v>
       </c>
       <c r="E223" t="n">
-        <v>66.804777666999</v>
+        <v>31.93125988142292</v>
       </c>
       <c r="F223" t="n">
         <v>-123</v>
@@ -7049,13 +7049,13 @@
         <v>139.6917688679246</v>
       </c>
       <c r="C224" t="n">
-        <v>66.84143619142571</v>
+        <v>30.49947308765403</v>
       </c>
       <c r="D224" t="n">
-        <v>139.6917688679246</v>
+        <v>160.0627425876012</v>
       </c>
       <c r="E224" t="n">
-        <v>66.84143619142571</v>
+        <v>31.81194431527551</v>
       </c>
       <c r="F224" t="n">
         <v>-123</v>
@@ -7078,13 +7078,13 @@
         <v>139.5851145552562</v>
       </c>
       <c r="C225" t="n">
-        <v>66.87809471585244</v>
+        <v>30.38015752150662</v>
       </c>
       <c r="D225" t="n">
-        <v>139.5851145552562</v>
+        <v>159.9560882749327</v>
       </c>
       <c r="E225" t="n">
-        <v>66.87809471585244</v>
+        <v>31.6926287491281</v>
       </c>
       <c r="F225" t="n">
         <v>-123</v>
@@ -7107,13 +7107,13 @@
         <v>139.4784602425877</v>
       </c>
       <c r="C226" t="n">
-        <v>66.91475324027915</v>
+        <v>30.26084195535921</v>
       </c>
       <c r="D226" t="n">
-        <v>139.4784602425877</v>
+        <v>159.8494339622642</v>
       </c>
       <c r="E226" t="n">
-        <v>66.91475324027915</v>
+        <v>31.5733131829807</v>
       </c>
       <c r="F226" t="n">
         <v>-123</v>
@@ -7136,13 +7136,13 @@
         <v>139.3718059299192</v>
       </c>
       <c r="C227" t="n">
-        <v>66.95141176470588</v>
+        <v>30.14152638921181</v>
       </c>
       <c r="D227" t="n">
-        <v>139.3718059299192</v>
+        <v>159.7427796495957</v>
       </c>
       <c r="E227" t="n">
-        <v>66.95141176470588</v>
+        <v>31.45399761683329</v>
       </c>
       <c r="F227" t="n">
         <v>-123</v>
@@ -7165,13 +7165,13 @@
         <v>139.2651516172508</v>
       </c>
       <c r="C228" t="n">
-        <v>66.98807028913259</v>
+        <v>30.0222108230644</v>
       </c>
       <c r="D228" t="n">
-        <v>139.2651516172508</v>
+        <v>159.6361253369273</v>
       </c>
       <c r="E228" t="n">
-        <v>66.98807028913259</v>
+        <v>31.33468205068588</v>
       </c>
       <c r="F228" t="n">
         <v>-123</v>
@@ -7194,13 +7194,13 @@
         <v>139.1584973045823</v>
       </c>
       <c r="C229" t="n">
-        <v>67.02472881355932</v>
+        <v>29.90289525691699</v>
       </c>
       <c r="D229" t="n">
-        <v>139.1584973045823</v>
+        <v>159.5294710242588</v>
       </c>
       <c r="E229" t="n">
-        <v>67.02472881355932</v>
+        <v>31.21536648453847</v>
       </c>
       <c r="F229" t="n">
         <v>-123</v>
@@ -7223,13 +7223,13 @@
         <v>139.0518429919139</v>
       </c>
       <c r="C230" t="n">
-        <v>67.06138733798603</v>
+        <v>29.78357969076959</v>
       </c>
       <c r="D230" t="n">
-        <v>139.0518429919139</v>
+        <v>159.4228167115904</v>
       </c>
       <c r="E230" t="n">
-        <v>67.06138733798603</v>
+        <v>31.09605091839107</v>
       </c>
       <c r="F230" t="n">
         <v>-123</v>
@@ -7252,13 +7252,13 @@
         <v>138.9451886792454</v>
       </c>
       <c r="C231" t="n">
-        <v>67.09804586241276</v>
+        <v>29.66426412462218</v>
       </c>
       <c r="D231" t="n">
-        <v>138.9451886792454</v>
+        <v>159.3161623989219</v>
       </c>
       <c r="E231" t="n">
-        <v>67.09804586241276</v>
+        <v>30.97673535224366</v>
       </c>
       <c r="F231" t="n">
         <v>-123</v>
@@ -7281,13 +7281,13 @@
         <v>138.8385343665769</v>
       </c>
       <c r="C232" t="n">
-        <v>67.13470438683947</v>
+        <v>29.54494855847477</v>
       </c>
       <c r="D232" t="n">
-        <v>138.8385343665769</v>
+        <v>159.2095080862534</v>
       </c>
       <c r="E232" t="n">
-        <v>67.13470438683947</v>
+        <v>30.85741978609625</v>
       </c>
       <c r="F232" t="n">
         <v>-123</v>
@@ -7310,13 +7310,13 @@
         <v>138.7318800539085</v>
       </c>
       <c r="C233" t="n">
-        <v>67.1713629112662</v>
+        <v>29.42563299232736</v>
       </c>
       <c r="D233" t="n">
-        <v>138.7318800539085</v>
+        <v>159.102853773585</v>
       </c>
       <c r="E233" t="n">
-        <v>67.1713629112662</v>
+        <v>30.73810421994884</v>
       </c>
       <c r="F233" t="n">
         <v>-123</v>
@@ -7339,13 +7339,13 @@
         <v>138.62522574124</v>
       </c>
       <c r="C234" t="n">
-        <v>67.20802143569291</v>
+        <v>29.30631742617996</v>
       </c>
       <c r="D234" t="n">
-        <v>138.62522574124</v>
+        <v>158.9961994609165</v>
       </c>
       <c r="E234" t="n">
-        <v>67.20802143569291</v>
+        <v>30.61878865380144</v>
       </c>
       <c r="F234" t="n">
         <v>-123</v>
@@ -7368,13 +7368,13 @@
         <v>138.5185714285715</v>
       </c>
       <c r="C235" t="n">
-        <v>67.24467996011964</v>
+        <v>29.18700186003255</v>
       </c>
       <c r="D235" t="n">
-        <v>138.5185714285715</v>
+        <v>158.889545148248</v>
       </c>
       <c r="E235" t="n">
-        <v>67.24467996011964</v>
+        <v>30.49947308765403</v>
       </c>
       <c r="F235" t="n">
         <v>-123</v>
@@ -7397,13 +7397,13 @@
         <v>138.4119171159031</v>
       </c>
       <c r="C236" t="n">
-        <v>67.28133848454635</v>
+        <v>29.06768629388514</v>
       </c>
       <c r="D236" t="n">
-        <v>138.4119171159031</v>
+        <v>158.7828908355796</v>
       </c>
       <c r="E236" t="n">
-        <v>67.28133848454635</v>
+        <v>30.38015752150662</v>
       </c>
       <c r="F236" t="n">
         <v>-123</v>
@@ -7426,13 +7426,13 @@
         <v>138.3052628032346</v>
       </c>
       <c r="C237" t="n">
-        <v>67.31799700897308</v>
+        <v>28.94837072773773</v>
       </c>
       <c r="D237" t="n">
-        <v>138.3052628032346</v>
+        <v>158.6762365229111</v>
       </c>
       <c r="E237" t="n">
-        <v>67.31799700897308</v>
+        <v>30.26084195535921</v>
       </c>
       <c r="F237" t="n">
         <v>-123</v>
@@ -7455,13 +7455,13 @@
         <v>138.1986084905662</v>
       </c>
       <c r="C238" t="n">
-        <v>67.35465553339979</v>
+        <v>28.82905516159033</v>
       </c>
       <c r="D238" t="n">
-        <v>138.1986084905662</v>
+        <v>158.5695822102427</v>
       </c>
       <c r="E238" t="n">
-        <v>67.35465553339979</v>
+        <v>30.14152638921181</v>
       </c>
       <c r="F238" t="n">
         <v>-123</v>
@@ -7484,13 +7484,13 @@
         <v>138.0919541778977</v>
       </c>
       <c r="C239" t="n">
-        <v>67.39131405782652</v>
+        <v>28.70973959544292</v>
       </c>
       <c r="D239" t="n">
-        <v>138.0919541778977</v>
+        <v>158.4629278975742</v>
       </c>
       <c r="E239" t="n">
-        <v>67.39131405782652</v>
+        <v>30.0222108230644</v>
       </c>
       <c r="F239" t="n">
         <v>-123</v>
@@ -7513,13 +7513,13 @@
         <v>137.9852998652292</v>
       </c>
       <c r="C240" t="n">
-        <v>67.42797258225323</v>
+        <v>28.59042402929551</v>
       </c>
       <c r="D240" t="n">
-        <v>137.9852998652292</v>
+        <v>158.3562735849057</v>
       </c>
       <c r="E240" t="n">
-        <v>67.42797258225323</v>
+        <v>29.90289525691699</v>
       </c>
       <c r="F240" t="n">
         <v>-123</v>
@@ -7542,13 +7542,13 @@
         <v>137.8786455525608</v>
       </c>
       <c r="C241" t="n">
-        <v>67.46463110667996</v>
+        <v>28.4711084631481</v>
       </c>
       <c r="D241" t="n">
-        <v>137.8786455525608</v>
+        <v>158.2496192722373</v>
       </c>
       <c r="E241" t="n">
-        <v>67.46463110667996</v>
+        <v>29.78357969076959</v>
       </c>
       <c r="F241" t="n">
         <v>-123</v>
@@ -7571,13 +7571,13 @@
         <v>137.7719912398923</v>
       </c>
       <c r="C242" t="n">
-        <v>67.50128963110667</v>
+        <v>28.35179289700069</v>
       </c>
       <c r="D242" t="n">
-        <v>137.7719912398923</v>
+        <v>158.1429649595688</v>
       </c>
       <c r="E242" t="n">
-        <v>67.50128963110667</v>
+        <v>29.66426412462218</v>
       </c>
       <c r="F242" t="n">
         <v>-123</v>
@@ -7600,13 +7600,13 @@
         <v>137.6653369272238</v>
       </c>
       <c r="C243" t="n">
-        <v>67.5379481555334</v>
+        <v>28.23247733085329</v>
       </c>
       <c r="D243" t="n">
-        <v>137.6653369272238</v>
+        <v>158.0363106469003</v>
       </c>
       <c r="E243" t="n">
-        <v>67.5379481555334</v>
+        <v>29.54494855847477</v>
       </c>
       <c r="F243" t="n">
         <v>-123</v>
@@ -7629,13 +7629,13 @@
         <v>137.5586826145554</v>
       </c>
       <c r="C244" t="n">
-        <v>67.57460667996011</v>
+        <v>28.11316176470588</v>
       </c>
       <c r="D244" t="n">
-        <v>137.5586826145554</v>
+        <v>157.9296563342319</v>
       </c>
       <c r="E244" t="n">
-        <v>67.57460667996011</v>
+        <v>29.42563299232736</v>
       </c>
       <c r="F244" t="n">
         <v>-123</v>
@@ -7658,13 +7658,13 @@
         <v>137.4520283018869</v>
       </c>
       <c r="C245" t="n">
-        <v>67.61126520438684</v>
+        <v>27.99384619855847</v>
       </c>
       <c r="D245" t="n">
-        <v>137.4520283018869</v>
+        <v>157.8230020215634</v>
       </c>
       <c r="E245" t="n">
-        <v>67.61126520438684</v>
+        <v>29.30631742617996</v>
       </c>
       <c r="F245" t="n">
         <v>-123</v>
@@ -7687,13 +7687,13 @@
         <v>137.3453739892184</v>
       </c>
       <c r="C246" t="n">
-        <v>67.64792372881355</v>
+        <v>27.87453063241106</v>
       </c>
       <c r="D246" t="n">
-        <v>137.3453739892184</v>
+        <v>157.7163477088949</v>
       </c>
       <c r="E246" t="n">
-        <v>67.64792372881355</v>
+        <v>29.18700186003255</v>
       </c>
       <c r="F246" t="n">
         <v>-123</v>
@@ -7716,13 +7716,13 @@
         <v>137.23871967655</v>
       </c>
       <c r="C247" t="n">
-        <v>67.68458225324028</v>
+        <v>27.75521506626366</v>
       </c>
       <c r="D247" t="n">
-        <v>137.23871967655</v>
+        <v>157.6096933962265</v>
       </c>
       <c r="E247" t="n">
-        <v>67.68458225324028</v>
+        <v>29.06768629388514</v>
       </c>
       <c r="F247" t="n">
         <v>-123</v>
@@ -7745,13 +7745,13 @@
         <v>137.1320653638815</v>
       </c>
       <c r="C248" t="n">
-        <v>67.72124077766699</v>
+        <v>27.63589950011625</v>
       </c>
       <c r="D248" t="n">
-        <v>137.1320653638815</v>
+        <v>157.503039083558</v>
       </c>
       <c r="E248" t="n">
-        <v>67.72124077766699</v>
+        <v>28.94837072773773</v>
       </c>
       <c r="F248" t="n">
         <v>-123</v>
@@ -7774,13 +7774,13 @@
         <v>137.025411051213</v>
       </c>
       <c r="C249" t="n">
-        <v>67.75789930209372</v>
+        <v>27.51658393396884</v>
       </c>
       <c r="D249" t="n">
-        <v>137.025411051213</v>
+        <v>157.3963847708896</v>
       </c>
       <c r="E249" t="n">
-        <v>67.75789930209372</v>
+        <v>28.82905516159033</v>
       </c>
       <c r="F249" t="n">
         <v>-123</v>
@@ -7803,13 +7803,13 @@
         <v>136.9187567385446</v>
       </c>
       <c r="C250" t="n">
-        <v>67.79455782652043</v>
+        <v>27.39726836782143</v>
       </c>
       <c r="D250" t="n">
-        <v>136.9187567385446</v>
+        <v>157.2897304582211</v>
       </c>
       <c r="E250" t="n">
-        <v>67.79455782652043</v>
+        <v>28.70973959544292</v>
       </c>
       <c r="F250" t="n">
         <v>-123</v>
@@ -7832,13 +7832,13 @@
         <v>136.8121024258761</v>
       </c>
       <c r="C251" t="n">
-        <v>67.83121635094716</v>
+        <v>27.27795280167403</v>
       </c>
       <c r="D251" t="n">
-        <v>136.8121024258761</v>
+        <v>157.1830761455526</v>
       </c>
       <c r="E251" t="n">
-        <v>67.83121635094716</v>
+        <v>28.59042402929551</v>
       </c>
       <c r="F251" t="n">
         <v>-123</v>
@@ -7861,13 +7861,13 @@
         <v>136.7054481132077</v>
       </c>
       <c r="C252" t="n">
-        <v>67.86787487537387</v>
+        <v>27.15863723552662</v>
       </c>
       <c r="D252" t="n">
-        <v>136.7054481132077</v>
+        <v>157.0764218328842</v>
       </c>
       <c r="E252" t="n">
-        <v>67.86787487537387</v>
+        <v>28.4711084631481</v>
       </c>
       <c r="F252" t="n">
         <v>-123</v>
@@ -7890,13 +7890,13 @@
         <v>136.5987938005392</v>
       </c>
       <c r="C253" t="n">
-        <v>67.9045333998006</v>
+        <v>27.03932166937921</v>
       </c>
       <c r="D253" t="n">
-        <v>136.5987938005392</v>
+        <v>156.9697675202157</v>
       </c>
       <c r="E253" t="n">
-        <v>67.9045333998006</v>
+        <v>28.35179289700069</v>
       </c>
       <c r="F253" t="n">
         <v>-123</v>
@@ -7919,13 +7919,13 @@
         <v>136.4921394878707</v>
       </c>
       <c r="C254" t="n">
-        <v>67.94119192422731</v>
+        <v>26.9200061032318</v>
       </c>
       <c r="D254" t="n">
-        <v>136.4921394878707</v>
+        <v>156.8631132075472</v>
       </c>
       <c r="E254" t="n">
-        <v>67.94119192422731</v>
+        <v>28.23247733085329</v>
       </c>
       <c r="F254" t="n">
         <v>-123</v>
@@ -7948,13 +7948,13 @@
         <v>136.3854851752023</v>
       </c>
       <c r="C255" t="n">
-        <v>67.97785044865404</v>
+        <v>26.8006905370844</v>
       </c>
       <c r="D255" t="n">
-        <v>136.3854851752023</v>
+        <v>156.7564588948788</v>
       </c>
       <c r="E255" t="n">
-        <v>67.97785044865404</v>
+        <v>28.11316176470588</v>
       </c>
       <c r="F255" t="n">
         <v>-123</v>
@@ -7977,13 +7977,13 @@
         <v>136.2788308625338</v>
       </c>
       <c r="C256" t="n">
-        <v>68.01450897308075</v>
+        <v>26.68137497093699</v>
       </c>
       <c r="D256" t="n">
-        <v>136.2788308625338</v>
+        <v>156.6498045822103</v>
       </c>
       <c r="E256" t="n">
-        <v>68.01450897308075</v>
+        <v>27.99384619855847</v>
       </c>
       <c r="F256" t="n">
         <v>-123</v>
@@ -8006,13 +8006,13 @@
         <v>136.1721765498654</v>
       </c>
       <c r="C257" t="n">
-        <v>68.05116749750748</v>
+        <v>26.56205940478958</v>
       </c>
       <c r="D257" t="n">
-        <v>136.1721765498654</v>
+        <v>156.5431502695419</v>
       </c>
       <c r="E257" t="n">
-        <v>68.05116749750748</v>
+        <v>27.87453063241106</v>
       </c>
       <c r="F257" t="n">
         <v>-123</v>
@@ -8035,13 +8035,13 @@
         <v>136.0655222371969</v>
       </c>
       <c r="C258" t="n">
-        <v>68.08782602193419</v>
+        <v>26.44274383864217</v>
       </c>
       <c r="D258" t="n">
-        <v>136.0655222371969</v>
+        <v>156.4364959568734</v>
       </c>
       <c r="E258" t="n">
-        <v>68.08782602193419</v>
+        <v>27.75521506626366</v>
       </c>
       <c r="F258" t="n">
         <v>-123</v>
@@ -8064,13 +8064,13 @@
         <v>135.9588679245284</v>
       </c>
       <c r="C259" t="n">
-        <v>68.12448454636092</v>
+        <v>26.32342827249477</v>
       </c>
       <c r="D259" t="n">
-        <v>135.9588679245284</v>
+        <v>156.3298416442049</v>
       </c>
       <c r="E259" t="n">
-        <v>68.12448454636092</v>
+        <v>27.63589950011625</v>
       </c>
       <c r="F259" t="n">
         <v>-123</v>
@@ -8093,13 +8093,13 @@
         <v>135.85221361186</v>
       </c>
       <c r="C260" t="n">
-        <v>68.16114307078763</v>
+        <v>26.20411270634736</v>
       </c>
       <c r="D260" t="n">
-        <v>135.85221361186</v>
+        <v>156.2231873315365</v>
       </c>
       <c r="E260" t="n">
-        <v>68.16114307078763</v>
+        <v>27.51658393396884</v>
       </c>
       <c r="F260" t="n">
         <v>-123</v>
@@ -8122,13 +8122,13 @@
         <v>135.7455592991915</v>
       </c>
       <c r="C261" t="n">
-        <v>68.19780159521434</v>
+        <v>26.08479714019995</v>
       </c>
       <c r="D261" t="n">
-        <v>135.7455592991915</v>
+        <v>156.116533018868</v>
       </c>
       <c r="E261" t="n">
-        <v>68.19780159521434</v>
+        <v>27.39726836782143</v>
       </c>
       <c r="F261" t="n">
         <v>-123</v>
@@ -8151,13 +8151,13 @@
         <v>135.638904986523</v>
       </c>
       <c r="C262" t="n">
-        <v>68.23446011964107</v>
+        <v>25.96548157405254</v>
       </c>
       <c r="D262" t="n">
-        <v>135.638904986523</v>
+        <v>156.0098787061995</v>
       </c>
       <c r="E262" t="n">
-        <v>68.23446011964107</v>
+        <v>27.27795280167403</v>
       </c>
       <c r="F262" t="n">
         <v>-123</v>
@@ -8180,13 +8180,13 @@
         <v>135.5322506738545</v>
       </c>
       <c r="C263" t="n">
-        <v>68.2711186440678</v>
+        <v>25.84616600790513</v>
       </c>
       <c r="D263" t="n">
-        <v>135.5322506738545</v>
+        <v>155.9032243935311</v>
       </c>
       <c r="E263" t="n">
-        <v>68.2711186440678</v>
+        <v>27.15863723552662</v>
       </c>
       <c r="F263" t="n">
         <v>-123</v>
@@ -8209,13 +8209,13 @@
         <v>135.4255963611861</v>
       </c>
       <c r="C264" t="n">
-        <v>68.30777716849451</v>
+        <v>25.72685044175773</v>
       </c>
       <c r="D264" t="n">
-        <v>135.4255963611861</v>
+        <v>155.7965700808626</v>
       </c>
       <c r="E264" t="n">
-        <v>68.30777716849451</v>
+        <v>27.03932166937921</v>
       </c>
       <c r="F264" t="n">
         <v>-123</v>
@@ -8238,13 +8238,13 @@
         <v>135.3189420485176</v>
       </c>
       <c r="C265" t="n">
-        <v>68.34443569292122</v>
+        <v>25.60753487561032</v>
       </c>
       <c r="D265" t="n">
-        <v>135.3189420485176</v>
+        <v>155.6899157681941</v>
       </c>
       <c r="E265" t="n">
-        <v>68.34443569292122</v>
+        <v>26.9200061032318</v>
       </c>
       <c r="F265" t="n">
         <v>-123</v>
@@ -8267,13 +8267,13 @@
         <v>135.2122877358492</v>
       </c>
       <c r="C266" t="n">
-        <v>68.38109421734795</v>
+        <v>25.48821930946291</v>
       </c>
       <c r="D266" t="n">
-        <v>135.2122877358492</v>
+        <v>155.5832614555257</v>
       </c>
       <c r="E266" t="n">
-        <v>68.38109421734795</v>
+        <v>26.8006905370844</v>
       </c>
       <c r="F266" t="n">
         <v>-123</v>
@@ -8296,13 +8296,13 @@
         <v>135.1056334231807</v>
       </c>
       <c r="C267" t="n">
-        <v>68.41775274177468</v>
+        <v>25.36890374331551</v>
       </c>
       <c r="D267" t="n">
-        <v>135.1056334231807</v>
+        <v>155.4766071428572</v>
       </c>
       <c r="E267" t="n">
-        <v>68.41775274177468</v>
+        <v>26.68137497093699</v>
       </c>
       <c r="F267" t="n">
         <v>-123</v>
@@ -8325,13 +8325,13 @@
         <v>134.9989791105123</v>
       </c>
       <c r="C268" t="n">
-        <v>68.45441126620139</v>
+        <v>25.2495881771681</v>
       </c>
       <c r="D268" t="n">
-        <v>134.9989791105123</v>
+        <v>155.3699528301888</v>
       </c>
       <c r="E268" t="n">
-        <v>68.45441126620139</v>
+        <v>26.56205940478958</v>
       </c>
       <c r="F268" t="n">
         <v>-123</v>
@@ -8354,13 +8354,13 @@
         <v>134.8923247978438</v>
       </c>
       <c r="C269" t="n">
-        <v>68.4910697906281</v>
+        <v>25.13027261102069</v>
       </c>
       <c r="D269" t="n">
-        <v>134.8923247978438</v>
+        <v>155.2632985175203</v>
       </c>
       <c r="E269" t="n">
-        <v>68.4910697906281</v>
+        <v>26.44274383864217</v>
       </c>
       <c r="F269" t="n">
         <v>-123</v>
@@ -8383,13 +8383,13 @@
         <v>134.7856704851753</v>
       </c>
       <c r="C270" t="n">
-        <v>68.52772831505483</v>
+        <v>25.01095704487328</v>
       </c>
       <c r="D270" t="n">
-        <v>134.7856704851753</v>
+        <v>155.1566442048518</v>
       </c>
       <c r="E270" t="n">
-        <v>68.52772831505483</v>
+        <v>26.32342827249477</v>
       </c>
       <c r="F270" t="n">
         <v>-123</v>
@@ -8412,13 +8412,13 @@
         <v>134.6790161725069</v>
       </c>
       <c r="C271" t="n">
-        <v>68.56438683948156</v>
+        <v>24.89164147872587</v>
       </c>
       <c r="D271" t="n">
-        <v>134.6790161725069</v>
+        <v>155.0499898921834</v>
       </c>
       <c r="E271" t="n">
-        <v>68.56438683948156</v>
+        <v>26.20411270634736</v>
       </c>
       <c r="F271" t="n">
         <v>-123</v>
@@ -8441,13 +8441,13 @@
         <v>134.5723618598384</v>
       </c>
       <c r="C272" t="n">
-        <v>68.60104536390827</v>
+        <v>24.77232591257847</v>
       </c>
       <c r="D272" t="n">
-        <v>134.5723618598384</v>
+        <v>154.9433355795149</v>
       </c>
       <c r="E272" t="n">
-        <v>68.60104536390827</v>
+        <v>26.08479714019995</v>
       </c>
       <c r="F272" t="n">
         <v>-123</v>
@@ -8470,13 +8470,13 @@
         <v>134.4657075471699</v>
       </c>
       <c r="C273" t="n">
-        <v>68.63770388833498</v>
+        <v>24.65301034643106</v>
       </c>
       <c r="D273" t="n">
-        <v>134.4657075471699</v>
+        <v>154.8366812668464</v>
       </c>
       <c r="E273" t="n">
-        <v>68.63770388833498</v>
+        <v>25.96548157405254</v>
       </c>
       <c r="F273" t="n">
         <v>-123</v>
@@ -8499,13 +8499,13 @@
         <v>134.3590532345015</v>
       </c>
       <c r="C274" t="n">
-        <v>68.67436241276171</v>
+        <v>24.53369478028365</v>
       </c>
       <c r="D274" t="n">
-        <v>134.3590532345015</v>
+        <v>154.730026954178</v>
       </c>
       <c r="E274" t="n">
-        <v>68.67436241276171</v>
+        <v>25.84616600790513</v>
       </c>
       <c r="F274" t="n">
         <v>-123</v>
@@ -8528,13 +8528,13 @@
         <v>134.252398921833</v>
       </c>
       <c r="C275" t="n">
-        <v>68.71102093718844</v>
+        <v>24.41437921413625</v>
       </c>
       <c r="D275" t="n">
-        <v>134.252398921833</v>
+        <v>154.6233726415095</v>
       </c>
       <c r="E275" t="n">
-        <v>68.71102093718844</v>
+        <v>25.72685044175773</v>
       </c>
       <c r="F275" t="n">
         <v>-123</v>
@@ -8557,13 +8557,13 @@
         <v>134.1457446091646</v>
       </c>
       <c r="C276" t="n">
-        <v>68.74767946161515</v>
+        <v>24.29506364798883</v>
       </c>
       <c r="D276" t="n">
-        <v>134.1457446091646</v>
+        <v>154.5167183288411</v>
       </c>
       <c r="E276" t="n">
-        <v>68.74767946161515</v>
+        <v>25.60753487561032</v>
       </c>
       <c r="F276" t="n">
         <v>-123</v>
@@ -8586,13 +8586,13 @@
         <v>134.0390902964961</v>
       </c>
       <c r="C277" t="n">
-        <v>68.78433798604186</v>
+        <v>24.17574808184143</v>
       </c>
       <c r="D277" t="n">
-        <v>134.0390902964961</v>
+        <v>154.4100640161726</v>
       </c>
       <c r="E277" t="n">
-        <v>68.78433798604186</v>
+        <v>25.48821930946291</v>
       </c>
       <c r="F277" t="n">
         <v>-123</v>
@@ -8615,13 +8615,13 @@
         <v>133.9324359838276</v>
       </c>
       <c r="C278" t="n">
-        <v>68.82099651046859</v>
+        <v>24.05643251569402</v>
       </c>
       <c r="D278" t="n">
-        <v>133.9324359838276</v>
+        <v>154.3034097035041</v>
       </c>
       <c r="E278" t="n">
-        <v>68.82099651046859</v>
+        <v>25.36890374331551</v>
       </c>
       <c r="F278" t="n">
         <v>-123</v>
@@ -8644,13 +8644,13 @@
         <v>133.8257816711591</v>
       </c>
       <c r="C279" t="n">
-        <v>68.85765503489532</v>
+        <v>23.93711694954661</v>
       </c>
       <c r="D279" t="n">
-        <v>133.8257816711591</v>
+        <v>154.1967553908356</v>
       </c>
       <c r="E279" t="n">
-        <v>68.85765503489532</v>
+        <v>25.2495881771681</v>
       </c>
       <c r="F279" t="n">
         <v>-123</v>
@@ -8673,13 +8673,13 @@
         <v>133.7191273584907</v>
       </c>
       <c r="C280" t="n">
-        <v>68.89431355932203</v>
+        <v>23.81780138339921</v>
       </c>
       <c r="D280" t="n">
-        <v>133.7191273584907</v>
+        <v>154.0901010781672</v>
       </c>
       <c r="E280" t="n">
-        <v>68.89431355932203</v>
+        <v>25.13027261102069</v>
       </c>
       <c r="F280" t="n">
         <v>-123</v>
@@ -8702,13 +8702,13 @@
         <v>133.6124730458222</v>
       </c>
       <c r="C281" t="n">
-        <v>68.93097208374874</v>
+        <v>23.6984858172518</v>
       </c>
       <c r="D281" t="n">
-        <v>133.6124730458222</v>
+        <v>153.9834467654987</v>
       </c>
       <c r="E281" t="n">
-        <v>68.93097208374874</v>
+        <v>25.01095704487328</v>
       </c>
       <c r="F281" t="n">
         <v>-123</v>
@@ -8731,13 +8731,13 @@
         <v>133.5058187331538</v>
       </c>
       <c r="C282" t="n">
-        <v>68.96763060817547</v>
+        <v>23.57917025110439</v>
       </c>
       <c r="D282" t="n">
-        <v>133.5058187331538</v>
+        <v>153.8767924528303</v>
       </c>
       <c r="E282" t="n">
-        <v>68.96763060817547</v>
+        <v>24.89164147872587</v>
       </c>
       <c r="F282" t="n">
         <v>-123</v>
@@ -8760,13 +8760,13 @@
         <v>133.3991644204853</v>
       </c>
       <c r="C283" t="n">
-        <v>69.00428913260218</v>
+        <v>23.45985468495698</v>
       </c>
       <c r="D283" t="n">
-        <v>133.3991644204853</v>
+        <v>153.7701381401618</v>
       </c>
       <c r="E283" t="n">
-        <v>69.00428913260218</v>
+        <v>24.77232591257847</v>
       </c>
       <c r="F283" t="n">
         <v>-123</v>
@@ -8789,13 +8789,13 @@
         <v>133.2925101078168</v>
       </c>
       <c r="C284" t="n">
-        <v>69.04094765702891</v>
+        <v>23.34053911880957</v>
       </c>
       <c r="D284" t="n">
-        <v>133.2925101078168</v>
+        <v>153.6634838274933</v>
       </c>
       <c r="E284" t="n">
-        <v>69.04094765702891</v>
+        <v>24.65301034643106</v>
       </c>
       <c r="F284" t="n">
         <v>-123</v>
@@ -8818,13 +8818,13 @@
         <v>133.1858557951484</v>
       </c>
       <c r="C285" t="n">
-        <v>69.07760618145562</v>
+        <v>23.22122355266217</v>
       </c>
       <c r="D285" t="n">
-        <v>133.1858557951484</v>
+        <v>153.5568295148249</v>
       </c>
       <c r="E285" t="n">
-        <v>69.07760618145562</v>
+        <v>24.53369478028365</v>
       </c>
       <c r="F285" t="n">
         <v>-123</v>
@@ -8847,13 +8847,13 @@
         <v>133.0792014824799</v>
       </c>
       <c r="C286" t="n">
-        <v>69.11426470588235</v>
+        <v>23.10190798651476</v>
       </c>
       <c r="D286" t="n">
-        <v>133.0792014824799</v>
+        <v>153.4501752021564</v>
       </c>
       <c r="E286" t="n">
-        <v>69.11426470588235</v>
+        <v>24.41437921413625</v>
       </c>
       <c r="F286" t="n">
         <v>-123</v>
@@ -8876,13 +8876,13 @@
         <v>132.9725471698114</v>
       </c>
       <c r="C287" t="n">
-        <v>69.15092323030906</v>
+        <v>22.98259242036735</v>
       </c>
       <c r="D287" t="n">
-        <v>132.9725471698114</v>
+        <v>153.3435208894879</v>
       </c>
       <c r="E287" t="n">
-        <v>69.15092323030906</v>
+        <v>24.29506364798883</v>
       </c>
       <c r="F287" t="n">
         <v>-123</v>
@@ -8905,13 +8905,13 @@
         <v>132.865892857143</v>
       </c>
       <c r="C288" t="n">
-        <v>69.18758175473579</v>
+        <v>22.86327685421995</v>
       </c>
       <c r="D288" t="n">
-        <v>132.865892857143</v>
+        <v>153.2368665768195</v>
       </c>
       <c r="E288" t="n">
-        <v>69.18758175473579</v>
+        <v>24.17574808184143</v>
       </c>
       <c r="F288" t="n">
         <v>-123</v>
@@ -8934,13 +8934,13 @@
         <v>132.7592385444745</v>
       </c>
       <c r="C289" t="n">
-        <v>69.2242402791625</v>
+        <v>22.74396128807254</v>
       </c>
       <c r="D289" t="n">
-        <v>132.7592385444745</v>
+        <v>153.130212264151</v>
       </c>
       <c r="E289" t="n">
-        <v>69.2242402791625</v>
+        <v>24.05643251569402</v>
       </c>
       <c r="F289" t="n">
         <v>-123</v>
@@ -8963,13 +8963,13 @@
         <v>132.6525842318061</v>
       </c>
       <c r="C290" t="n">
-        <v>69.26089880358923</v>
+        <v>22.62464572192513</v>
       </c>
       <c r="D290" t="n">
-        <v>132.6525842318061</v>
+        <v>153.0235579514826</v>
       </c>
       <c r="E290" t="n">
-        <v>69.26089880358923</v>
+        <v>23.93711694954661</v>
       </c>
       <c r="F290" t="n">
         <v>-123</v>
@@ -8992,13 +8992,13 @@
         <v>132.5459299191376</v>
       </c>
       <c r="C291" t="n">
-        <v>69.29755732801594</v>
+        <v>22.50533015577772</v>
       </c>
       <c r="D291" t="n">
-        <v>132.5459299191376</v>
+        <v>152.9169036388141</v>
       </c>
       <c r="E291" t="n">
-        <v>69.29755732801594</v>
+        <v>23.81780138339921</v>
       </c>
       <c r="F291" t="n">
         <v>-123</v>
@@ -9021,13 +9021,13 @@
         <v>132.4392756064691</v>
       </c>
       <c r="C292" t="n">
-        <v>69.33421585244267</v>
+        <v>22.38601458963031</v>
       </c>
       <c r="D292" t="n">
-        <v>132.4392756064691</v>
+        <v>152.8102493261456</v>
       </c>
       <c r="E292" t="n">
-        <v>69.33421585244267</v>
+        <v>23.6984858172518</v>
       </c>
       <c r="F292" t="n">
         <v>-123</v>
@@ -9050,13 +9050,13 @@
         <v>132.3326212938007</v>
       </c>
       <c r="C293" t="n">
-        <v>69.37087437686938</v>
+        <v>22.26669902348291</v>
       </c>
       <c r="D293" t="n">
-        <v>132.3326212938007</v>
+        <v>152.7035950134772</v>
       </c>
       <c r="E293" t="n">
-        <v>69.37087437686938</v>
+        <v>23.57917025110439</v>
       </c>
       <c r="F293" t="n">
         <v>-123</v>
@@ -9079,13 +9079,13 @@
         <v>132.2259669811322</v>
       </c>
       <c r="C294" t="n">
-        <v>69.40753290129611</v>
+        <v>22.1473834573355</v>
       </c>
       <c r="D294" t="n">
-        <v>132.2259669811322</v>
+        <v>152.5969407008087</v>
       </c>
       <c r="E294" t="n">
-        <v>69.40753290129611</v>
+        <v>23.45985468495698</v>
       </c>
       <c r="F294" t="n">
         <v>-123</v>
@@ -9108,13 +9108,13 @@
         <v>132.1193126684637</v>
       </c>
       <c r="C295" t="n">
-        <v>69.44419142572282</v>
+        <v>22.02806789118809</v>
       </c>
       <c r="D295" t="n">
-        <v>132.1193126684637</v>
+        <v>152.4902863881402</v>
       </c>
       <c r="E295" t="n">
-        <v>69.44419142572282</v>
+        <v>23.34053911880957</v>
       </c>
       <c r="F295" t="n">
         <v>-123</v>
@@ -9137,13 +9137,13 @@
         <v>132.0126583557953</v>
       </c>
       <c r="C296" t="n">
-        <v>69.48084995014955</v>
+        <v>21.90875232504069</v>
       </c>
       <c r="D296" t="n">
-        <v>132.0126583557953</v>
+        <v>152.3836320754718</v>
       </c>
       <c r="E296" t="n">
-        <v>69.48084995014955</v>
+        <v>23.22122355266217</v>
       </c>
       <c r="F296" t="n">
         <v>-123</v>
@@ -9166,13 +9166,13 @@
         <v>131.9060040431268</v>
       </c>
       <c r="C297" t="n">
-        <v>69.51750847457626</v>
+        <v>21.78943675889327</v>
       </c>
       <c r="D297" t="n">
-        <v>132.0066666666667</v>
+        <v>152.2769777628033</v>
       </c>
       <c r="E297" t="n">
-        <v>69.51750847457626</v>
+        <v>23.10190798651476</v>
       </c>
       <c r="F297" t="n">
         <v>-123</v>
@@ -9195,13 +9195,13 @@
         <v>131.7993497304583</v>
       </c>
       <c r="C298" t="n">
-        <v>69.55416699900299</v>
+        <v>21.67012119274587</v>
       </c>
       <c r="D298" t="n">
-        <v>132.0066666666667</v>
+        <v>152.1703234501348</v>
       </c>
       <c r="E298" t="n">
-        <v>69.55416699900299</v>
+        <v>22.98259242036735</v>
       </c>
       <c r="F298" t="n">
         <v>-123</v>
@@ -9224,13 +9224,13 @@
         <v>131.6926954177899</v>
       </c>
       <c r="C299" t="n">
-        <v>69.5908255234297</v>
+        <v>21.55080562659846</v>
       </c>
       <c r="D299" t="n">
-        <v>132.0066666666667</v>
+        <v>152.0636691374664</v>
       </c>
       <c r="E299" t="n">
-        <v>69.5908255234297</v>
+        <v>22.86327685421995</v>
       </c>
       <c r="F299" t="n">
         <v>-123</v>
@@ -9253,13 +9253,13 @@
         <v>131.5860411051214</v>
       </c>
       <c r="C300" t="n">
-        <v>69.62748404785643</v>
+        <v>21.43149006045105</v>
       </c>
       <c r="D300" t="n">
-        <v>132.0066666666667</v>
+        <v>151.9570148247979</v>
       </c>
       <c r="E300" t="n">
-        <v>69.62748404785643</v>
+        <v>22.74396128807254</v>
       </c>
       <c r="F300" t="n">
         <v>-123</v>
@@ -9282,13 +9282,13 @@
         <v>131.4793867924529</v>
       </c>
       <c r="C301" t="n">
-        <v>69.66414257228314</v>
+        <v>21.31217449430365</v>
       </c>
       <c r="D301" t="n">
-        <v>132.0066666666667</v>
+        <v>151.8503605121295</v>
       </c>
       <c r="E301" t="n">
-        <v>69.66414257228314</v>
+        <v>22.62464572192513</v>
       </c>
       <c r="F301" t="n">
         <v>-123</v>
@@ -9311,13 +9311,13 @@
         <v>131.3727324797845</v>
       </c>
       <c r="C302" t="n">
-        <v>69.70080109670987</v>
+        <v>21.19285892815624</v>
       </c>
       <c r="D302" t="n">
-        <v>132.0066666666667</v>
+        <v>151.743706199461</v>
       </c>
       <c r="E302" t="n">
-        <v>69.70080109670987</v>
+        <v>22.50533015577772</v>
       </c>
       <c r="F302" t="n">
         <v>-123</v>
@@ -9340,13 +9340,13 @@
         <v>131.266078167116</v>
       </c>
       <c r="C303" t="n">
-        <v>69.73745962113658</v>
+        <v>21.07354336200883</v>
       </c>
       <c r="D303" t="n">
-        <v>132.0066666666667</v>
+        <v>151.6370518867925</v>
       </c>
       <c r="E303" t="n">
-        <v>69.73745962113658</v>
+        <v>22.38601458963031</v>
       </c>
       <c r="F303" t="n">
         <v>-123</v>
@@ -9369,13 +9369,13 @@
         <v>131.1594238544476</v>
       </c>
       <c r="C304" t="n">
-        <v>69.77411814556331</v>
+        <v>20.95422779586142</v>
       </c>
       <c r="D304" t="n">
-        <v>132.0066666666667</v>
+        <v>151.5303975741241</v>
       </c>
       <c r="E304" t="n">
-        <v>69.77411814556331</v>
+        <v>22.26669902348291</v>
       </c>
       <c r="F304" t="n">
         <v>-123</v>
@@ -9398,13 +9398,13 @@
         <v>131.0527695417791</v>
       </c>
       <c r="C305" t="n">
-        <v>69.81077666999002</v>
+        <v>20.83491222971401</v>
       </c>
       <c r="D305" t="n">
-        <v>132.0066666666667</v>
+        <v>151.4237432614556</v>
       </c>
       <c r="E305" t="n">
-        <v>69.81077666999002</v>
+        <v>22.1473834573355</v>
       </c>
       <c r="F305" t="n">
         <v>-123</v>
@@ -9427,13 +9427,13 @@
         <v>130.9461152291106</v>
       </c>
       <c r="C306" t="n">
-        <v>69.84743519441675</v>
+        <v>20.71559666356661</v>
       </c>
       <c r="D306" t="n">
-        <v>132.0066666666667</v>
+        <v>151.3170889487872</v>
       </c>
       <c r="E306" t="n">
-        <v>69.84743519441675</v>
+        <v>22.02806789118809</v>
       </c>
       <c r="F306" t="n">
         <v>-123</v>
@@ -9456,13 +9456,13 @@
         <v>130.8394609164422</v>
       </c>
       <c r="C307" t="n">
-        <v>69.88409371884346</v>
+        <v>20.5962810974192</v>
       </c>
       <c r="D307" t="n">
-        <v>132.0066666666667</v>
+        <v>151.2104346361187</v>
       </c>
       <c r="E307" t="n">
-        <v>69.88409371884346</v>
+        <v>21.90875232504069</v>
       </c>
       <c r="F307" t="n">
         <v>-123</v>
@@ -9485,13 +9485,13 @@
         <v>130.7328066037737</v>
       </c>
       <c r="C308" t="n">
-        <v>69.92075224327019</v>
+        <v>20.47696553127179</v>
       </c>
       <c r="D308" t="n">
-        <v>132.0066666666667</v>
+        <v>151.1037803234502</v>
       </c>
       <c r="E308" t="n">
-        <v>69.92075224327019</v>
+        <v>21.78943675889327</v>
       </c>
       <c r="F308" t="n">
         <v>-123</v>
@@ -9514,13 +9514,13 @@
         <v>130.6261522911053</v>
       </c>
       <c r="C309" t="n">
-        <v>69.9574107676969</v>
+        <v>20.35764996512439</v>
       </c>
       <c r="D309" t="n">
-        <v>132.0066666666667</v>
+        <v>150.9971260107818</v>
       </c>
       <c r="E309" t="n">
-        <v>69.9574107676969</v>
+        <v>21.67012119274587</v>
       </c>
       <c r="F309" t="n">
         <v>-123</v>
@@ -9543,13 +9543,13 @@
         <v>130.5194979784368</v>
       </c>
       <c r="C310" t="n">
-        <v>69.99406929212363</v>
+        <v>20.23833439897698</v>
       </c>
       <c r="D310" t="n">
-        <v>132.0066666666667</v>
+        <v>150.8904716981133</v>
       </c>
       <c r="E310" t="n">
-        <v>69.99406929212363</v>
+        <v>21.55080562659846</v>
       </c>
       <c r="F310" t="n">
         <v>-123</v>
@@ -9572,13 +9572,13 @@
         <v>130.4128436657683</v>
       </c>
       <c r="C311" t="n">
-        <v>70.03072781655034</v>
+        <v>20.11901883282957</v>
       </c>
       <c r="D311" t="n">
-        <v>132.0066666666667</v>
+        <v>150.7838173854448</v>
       </c>
       <c r="E311" t="n">
-        <v>70.03072781655034</v>
+        <v>21.43149006045105</v>
       </c>
       <c r="F311" t="n">
         <v>-123</v>
@@ -9601,13 +9601,13 @@
         <v>130.3061893530999</v>
       </c>
       <c r="C312" t="n">
-        <v>70.06738634097707</v>
+        <v>19.99970326668216</v>
       </c>
       <c r="D312" t="n">
-        <v>132.0066666666667</v>
+        <v>150.6771630727764</v>
       </c>
       <c r="E312" t="n">
-        <v>70.06738634097707</v>
+        <v>21.31217449430365</v>
       </c>
       <c r="F312" t="n">
         <v>-123</v>
@@ -9630,13 +9630,13 @@
         <v>130.1995350404314</v>
       </c>
       <c r="C313" t="n">
-        <v>70.10404486540378</v>
+        <v>19.88038770053475</v>
       </c>
       <c r="D313" t="n">
-        <v>132.0066666666667</v>
+        <v>150.5705087601079</v>
       </c>
       <c r="E313" t="n">
-        <v>70.10404486540378</v>
+        <v>21.19285892815624</v>
       </c>
       <c r="F313" t="n">
         <v>-123</v>
@@ -9659,13 +9659,13 @@
         <v>130.0928807277629</v>
       </c>
       <c r="C314" t="n">
-        <v>70.14070338983051</v>
+        <v>19.76107213438735</v>
       </c>
       <c r="D314" t="n">
-        <v>132.0066666666667</v>
+        <v>150.4638544474394</v>
       </c>
       <c r="E314" t="n">
-        <v>70.14070338983051</v>
+        <v>21.07354336200883</v>
       </c>
       <c r="F314" t="n">
         <v>-123</v>
@@ -9688,13 +9688,13 @@
         <v>129.9862264150945</v>
       </c>
       <c r="C315" t="n">
-        <v>70.17736191425722</v>
+        <v>19.64175656823994</v>
       </c>
       <c r="D315" t="n">
-        <v>132.0066666666667</v>
+        <v>150.357200134771</v>
       </c>
       <c r="E315" t="n">
-        <v>70.17736191425722</v>
+        <v>20.95422779586142</v>
       </c>
       <c r="F315" t="n">
         <v>-123</v>
@@ -9717,13 +9717,13 @@
         <v>129.879572102426</v>
       </c>
       <c r="C316" t="n">
-        <v>70.21402043868395</v>
+        <v>19.52244100209253</v>
       </c>
       <c r="D316" t="n">
-        <v>132.0066666666667</v>
+        <v>150.2505458221025</v>
       </c>
       <c r="E316" t="n">
-        <v>70.21402043868395</v>
+        <v>20.83491222971401</v>
       </c>
       <c r="F316" t="n">
         <v>-123</v>
@@ -9746,13 +9746,13 @@
         <v>129.7729177897575</v>
       </c>
       <c r="C317" t="n">
-        <v>70.25067896311066</v>
+        <v>19.40312543594513</v>
       </c>
       <c r="D317" t="n">
-        <v>132.0066666666667</v>
+        <v>150.143891509434</v>
       </c>
       <c r="E317" t="n">
-        <v>70.25067896311066</v>
+        <v>20.71559666356661</v>
       </c>
       <c r="F317" t="n">
         <v>-123</v>
@@ -9775,13 +9775,13 @@
         <v>129.6662634770891</v>
       </c>
       <c r="C318" t="n">
-        <v>70.28733748753739</v>
+        <v>19.28380986979771</v>
       </c>
       <c r="D318" t="n">
-        <v>132.0066666666667</v>
+        <v>150.0372371967656</v>
       </c>
       <c r="E318" t="n">
-        <v>70.28733748753739</v>
+        <v>20.5962810974192</v>
       </c>
       <c r="F318" t="n">
         <v>-123</v>
@@ -9804,13 +9804,13 @@
         <v>129.5596091644206</v>
       </c>
       <c r="C319" t="n">
-        <v>70.3239960119641</v>
+        <v>19.16449430365031</v>
       </c>
       <c r="D319" t="n">
-        <v>132.0066666666667</v>
+        <v>149.9305828840971</v>
       </c>
       <c r="E319" t="n">
-        <v>70.3239960119641</v>
+        <v>20.47696553127179</v>
       </c>
       <c r="F319" t="n">
         <v>-123</v>
@@ -9833,13 +9833,13 @@
         <v>129.4529548517522</v>
       </c>
       <c r="C320" t="n">
-        <v>70.36065453639083</v>
+        <v>19.0451787375029</v>
       </c>
       <c r="D320" t="n">
-        <v>132.0066666666667</v>
+        <v>149.8239285714287</v>
       </c>
       <c r="E320" t="n">
-        <v>70.36065453639083</v>
+        <v>20.35764996512439</v>
       </c>
       <c r="F320" t="n">
         <v>-123</v>
@@ -9862,13 +9862,13 @@
         <v>129.3463005390837</v>
       </c>
       <c r="C321" t="n">
-        <v>70.39731306081754</v>
+        <v>18.92586317135549</v>
       </c>
       <c r="D321" t="n">
-        <v>132.0066666666667</v>
+        <v>149.7172742587602</v>
       </c>
       <c r="E321" t="n">
-        <v>70.39731306081754</v>
+        <v>20.23833439897698</v>
       </c>
       <c r="F321" t="n">
         <v>-123</v>
@@ -9891,13 +9891,13 @@
         <v>129.2396462264152</v>
       </c>
       <c r="C322" t="n">
-        <v>70.43397158524427</v>
+        <v>18.80654760520809</v>
       </c>
       <c r="D322" t="n">
-        <v>132.0066666666667</v>
+        <v>149.6106199460917</v>
       </c>
       <c r="E322" t="n">
-        <v>70.43397158524427</v>
+        <v>20.11901883282957</v>
       </c>
       <c r="F322" t="n">
         <v>-123</v>
@@ -9920,13 +9920,13 @@
         <v>129.1329919137468</v>
       </c>
       <c r="C323" t="n">
-        <v>70.47063010967098</v>
+        <v>18.68723203906068</v>
       </c>
       <c r="D323" t="n">
-        <v>132.0066666666667</v>
+        <v>149.5039656334233</v>
       </c>
       <c r="E323" t="n">
-        <v>70.47063010967098</v>
+        <v>19.99970326668216</v>
       </c>
       <c r="F323" t="n">
         <v>-123</v>
@@ -9949,13 +9949,13 @@
         <v>129.0263376010783</v>
       </c>
       <c r="C324" t="n">
-        <v>70.5072886340977</v>
+        <v>18.56791647291328</v>
       </c>
       <c r="D324" t="n">
-        <v>132.0066666666667</v>
+        <v>149.3973113207548</v>
       </c>
       <c r="E324" t="n">
-        <v>70.5072886340977</v>
+        <v>19.88038770053475</v>
       </c>
       <c r="F324" t="n">
         <v>-123</v>
@@ -9978,13 +9978,13 @@
         <v>128.9196832884098</v>
       </c>
       <c r="C325" t="n">
-        <v>70.54394715852442</v>
+        <v>18.44860090676586</v>
       </c>
       <c r="D325" t="n">
-        <v>132.0066666666667</v>
+        <v>149.2906570080863</v>
       </c>
       <c r="E325" t="n">
-        <v>70.54394715852442</v>
+        <v>19.76107213438735</v>
       </c>
       <c r="F325" t="n">
         <v>-123</v>
@@ -10007,13 +10007,13 @@
         <v>128.8130289757414</v>
       </c>
       <c r="C326" t="n">
-        <v>70.58060568295114</v>
+        <v>18.32928534061845</v>
       </c>
       <c r="D326" t="n">
-        <v>132.0066666666667</v>
+        <v>149.1840026954179</v>
       </c>
       <c r="E326" t="n">
-        <v>70.58060568295114</v>
+        <v>19.64175656823994</v>
       </c>
       <c r="F326" t="n">
         <v>-123</v>
@@ -10036,13 +10036,13 @@
         <v>128.7063746630729</v>
       </c>
       <c r="C327" t="n">
-        <v>70.61726420737786</v>
+        <v>18.20996977447105</v>
       </c>
       <c r="D327" t="n">
-        <v>132.0066666666667</v>
+        <v>149.0773483827494</v>
       </c>
       <c r="E327" t="n">
-        <v>70.61726420737786</v>
+        <v>19.52244100209253</v>
       </c>
       <c r="F327" t="n">
         <v>-123</v>
@@ -10065,13 +10065,13 @@
         <v>128.5997203504045</v>
       </c>
       <c r="C328" t="n">
-        <v>70.65392273180458</v>
+        <v>18.09065420832364</v>
       </c>
       <c r="D328" t="n">
-        <v>132.0066666666667</v>
+        <v>148.970694070081</v>
       </c>
       <c r="E328" t="n">
-        <v>70.65392273180458</v>
+        <v>19.40312543594513</v>
       </c>
       <c r="F328" t="n">
         <v>-123</v>
@@ -10094,13 +10094,13 @@
         <v>128.493066037736</v>
       </c>
       <c r="C329" t="n">
-        <v>70.6905812562313</v>
+        <v>17.97133864217624</v>
       </c>
       <c r="D329" t="n">
-        <v>132.0066666666667</v>
+        <v>148.8640397574125</v>
       </c>
       <c r="E329" t="n">
-        <v>70.6905812562313</v>
+        <v>19.28380986979771</v>
       </c>
       <c r="F329" t="n">
         <v>-123</v>
@@ -10123,13 +10123,13 @@
         <v>128.3864117250675</v>
       </c>
       <c r="C330" t="n">
-        <v>70.72723978065802</v>
+        <v>17.85202307602883</v>
       </c>
       <c r="D330" t="n">
-        <v>132.0066666666667</v>
+        <v>148.757385444744</v>
       </c>
       <c r="E330" t="n">
-        <v>70.72723978065802</v>
+        <v>19.16449430365031</v>
       </c>
       <c r="F330" t="n">
         <v>-123</v>
@@ -10152,13 +10152,13 @@
         <v>128.2797574123991</v>
       </c>
       <c r="C331" t="n">
-        <v>70.76389830508474</v>
+        <v>17.73270750988142</v>
       </c>
       <c r="D331" t="n">
-        <v>132.0066666666667</v>
+        <v>148.6507311320756</v>
       </c>
       <c r="E331" t="n">
-        <v>70.76389830508474</v>
+        <v>19.0451787375029</v>
       </c>
       <c r="F331" t="n">
         <v>-123</v>
@@ -10181,13 +10181,13 @@
         <v>128.1731030997306</v>
       </c>
       <c r="C332" t="n">
-        <v>70.80055682951146</v>
+        <v>17.61339194373401</v>
       </c>
       <c r="D332" t="n">
-        <v>132.0066666666667</v>
+        <v>148.5440768194071</v>
       </c>
       <c r="E332" t="n">
-        <v>70.80055682951146</v>
+        <v>18.92586317135549</v>
       </c>
       <c r="F332" t="n">
         <v>-123</v>
@@ -10210,13 +10210,13 @@
         <v>128.0664487870621</v>
       </c>
       <c r="C333" t="n">
-        <v>70.83721535393818</v>
+        <v>17.4940763775866</v>
       </c>
       <c r="D333" t="n">
-        <v>132.0066666666667</v>
+        <v>148.4374225067386</v>
       </c>
       <c r="E333" t="n">
-        <v>70.83721535393818</v>
+        <v>18.80654760520809</v>
       </c>
       <c r="F333" t="n">
         <v>-123</v>
@@ -10239,13 +10239,13 @@
         <v>127.9597944743937</v>
       </c>
       <c r="C334" t="n">
-        <v>70.8738738783649</v>
+        <v>17.3747608114392</v>
       </c>
       <c r="D334" t="n">
-        <v>132.0066666666667</v>
+        <v>148.3307681940702</v>
       </c>
       <c r="E334" t="n">
-        <v>70.8738738783649</v>
+        <v>18.68723203906068</v>
       </c>
       <c r="F334" t="n">
         <v>-123</v>
@@ -10268,13 +10268,13 @@
         <v>127.8531401617252</v>
       </c>
       <c r="C335" t="n">
-        <v>70.91053240279162</v>
+        <v>17.25544524529179</v>
       </c>
       <c r="D335" t="n">
-        <v>132.0066666666667</v>
+        <v>148.2241138814017</v>
       </c>
       <c r="E335" t="n">
-        <v>70.91053240279162</v>
+        <v>18.56791647291328</v>
       </c>
       <c r="F335" t="n">
         <v>-123</v>
@@ -10297,13 +10297,13 @@
         <v>127.7464858490567</v>
       </c>
       <c r="C336" t="n">
-        <v>70.94719092721834</v>
+        <v>17.13612967914438</v>
       </c>
       <c r="D336" t="n">
-        <v>132.0066666666667</v>
+        <v>148.1174595687332</v>
       </c>
       <c r="E336" t="n">
-        <v>70.94719092721834</v>
+        <v>18.44860090676586</v>
       </c>
       <c r="F336" t="n">
         <v>-123</v>
@@ -10326,13 +10326,13 @@
         <v>127.6398315363883</v>
       </c>
       <c r="C337" t="n">
-        <v>70.98384945164506</v>
+        <v>17.01681411299698</v>
       </c>
       <c r="D337" t="n">
-        <v>132.0066666666667</v>
+        <v>148.0108052560648</v>
       </c>
       <c r="E337" t="n">
-        <v>70.98384945164506</v>
+        <v>18.32928534061845</v>
       </c>
       <c r="F337" t="n">
         <v>-123</v>
@@ -10355,13 +10355,13 @@
         <v>127.5331772237198</v>
       </c>
       <c r="C338" t="n">
-        <v>71.02050797607178</v>
+        <v>16.89749854684957</v>
       </c>
       <c r="D338" t="n">
-        <v>132.0066666666667</v>
+        <v>147.9041509433963</v>
       </c>
       <c r="E338" t="n">
-        <v>71.02050797607178</v>
+        <v>18.20996977447105</v>
       </c>
       <c r="F338" t="n">
         <v>-123</v>
@@ -10384,13 +10384,13 @@
         <v>127.4265229110514</v>
       </c>
       <c r="C339" t="n">
-        <v>71.0571665004985</v>
+        <v>16.77818298070216</v>
       </c>
       <c r="D339" t="n">
-        <v>132.0066666666667</v>
+        <v>147.7974966307279</v>
       </c>
       <c r="E339" t="n">
-        <v>71.0571665004985</v>
+        <v>18.09065420832364</v>
       </c>
       <c r="F339" t="n">
         <v>-123</v>
@@ -10413,13 +10413,13 @@
         <v>127.3198685983829</v>
       </c>
       <c r="C340" t="n">
-        <v>71.09382502492522</v>
+        <v>16.65886741455475</v>
       </c>
       <c r="D340" t="n">
-        <v>132.0066666666667</v>
+        <v>147.6908423180594</v>
       </c>
       <c r="E340" t="n">
-        <v>71.09382502492522</v>
+        <v>17.97133864217624</v>
       </c>
       <c r="F340" t="n">
         <v>-123</v>
@@ -10442,13 +10442,13 @@
         <v>127.2132142857144</v>
       </c>
       <c r="C341" t="n">
-        <v>71.13048354935194</v>
+        <v>16.53955184840734</v>
       </c>
       <c r="D341" t="n">
-        <v>132.0066666666667</v>
+        <v>147.5841880053909</v>
       </c>
       <c r="E341" t="n">
-        <v>71.13048354935194</v>
+        <v>17.85202307602883</v>
       </c>
       <c r="F341" t="n">
         <v>-123</v>
@@ -10471,13 +10471,13 @@
         <v>127.106559973046</v>
       </c>
       <c r="C342" t="n">
-        <v>71.16714207377866</v>
+        <v>16.42023628225994</v>
       </c>
       <c r="D342" t="n">
-        <v>132.0066666666667</v>
+        <v>147.4775336927225</v>
       </c>
       <c r="E342" t="n">
-        <v>71.16714207377866</v>
+        <v>17.73270750988142</v>
       </c>
       <c r="F342" t="n">
         <v>-123</v>
@@ -10500,13 +10500,13 @@
         <v>126.9999056603775</v>
       </c>
       <c r="C343" t="n">
-        <v>71.20380059820538</v>
+        <v>16.30092071611253</v>
       </c>
       <c r="D343" t="n">
-        <v>132.0066666666667</v>
+        <v>147.370879380054</v>
       </c>
       <c r="E343" t="n">
-        <v>71.20380059820538</v>
+        <v>17.61339194373401</v>
       </c>
       <c r="F343" t="n">
         <v>-123</v>
@@ -10529,13 +10529,13 @@
         <v>126.893251347709</v>
       </c>
       <c r="C344" t="n">
-        <v>71.2404591226321</v>
+        <v>16.18160514996512</v>
       </c>
       <c r="D344" t="n">
-        <v>132.0066666666667</v>
+        <v>147.2642250673856</v>
       </c>
       <c r="E344" t="n">
-        <v>71.2404591226321</v>
+        <v>17.4940763775866</v>
       </c>
       <c r="F344" t="n">
         <v>-123</v>
@@ -10558,13 +10558,13 @@
         <v>126.7865970350406</v>
       </c>
       <c r="C345" t="n">
-        <v>71.27711764705882</v>
+        <v>16.06228958381772</v>
       </c>
       <c r="D345" t="n">
-        <v>132.0066666666667</v>
+        <v>147.1575707547171</v>
       </c>
       <c r="E345" t="n">
-        <v>71.27711764705882</v>
+        <v>17.3747608114392</v>
       </c>
       <c r="F345" t="n">
         <v>-123</v>
@@ -10587,13 +10587,13 @@
         <v>126.6799427223721</v>
       </c>
       <c r="C346" t="n">
-        <v>71.31377617148554</v>
+        <v>15.9429740176703</v>
       </c>
       <c r="D346" t="n">
-        <v>132.0066666666667</v>
+        <v>147.0509164420486</v>
       </c>
       <c r="E346" t="n">
-        <v>71.31377617148554</v>
+        <v>17.25544524529179</v>
       </c>
       <c r="F346" t="n">
         <v>-123</v>
@@ -10616,13 +10616,13 @@
         <v>126.5732884097037</v>
       </c>
       <c r="C347" t="n">
-        <v>71.35043469591226</v>
+        <v>15.8236584515229</v>
       </c>
       <c r="D347" t="n">
-        <v>132.0066666666667</v>
+        <v>146.9442621293801</v>
       </c>
       <c r="E347" t="n">
-        <v>71.35043469591226</v>
+        <v>17.13612967914438</v>
       </c>
       <c r="F347" t="n">
         <v>-123</v>
@@ -10645,13 +10645,13 @@
         <v>126.4666340970352</v>
       </c>
       <c r="C348" t="n">
-        <v>71.38709322033898</v>
+        <v>15.70434288537549</v>
       </c>
       <c r="D348" t="n">
-        <v>132.0066666666667</v>
+        <v>146.8376078167117</v>
       </c>
       <c r="E348" t="n">
-        <v>71.38709322033898</v>
+        <v>17.01681411299698</v>
       </c>
       <c r="F348" t="n">
         <v>-123</v>
@@ -10674,13 +10674,13 @@
         <v>126.3599797843667</v>
       </c>
       <c r="C349" t="n">
-        <v>71.4237517447657</v>
+        <v>15.58502731922808</v>
       </c>
       <c r="D349" t="n">
-        <v>132.0066666666667</v>
+        <v>146.7309535040432</v>
       </c>
       <c r="E349" t="n">
-        <v>71.4237517447657</v>
+        <v>16.89749854684957</v>
       </c>
       <c r="F349" t="n">
         <v>-123</v>
@@ -10703,13 +10703,13 @@
         <v>126.2533254716982</v>
       </c>
       <c r="C350" t="n">
-        <v>71.46041026919242</v>
+        <v>15.46571175308068</v>
       </c>
       <c r="D350" t="n">
-        <v>132.0066666666667</v>
+        <v>146.6242991913747</v>
       </c>
       <c r="E350" t="n">
-        <v>71.46041026919242</v>
+        <v>16.77818298070216</v>
       </c>
       <c r="F350" t="n">
         <v>-123</v>
@@ -10732,13 +10732,13 @@
         <v>126.1466711590298</v>
       </c>
       <c r="C351" t="n">
-        <v>71.49706879361914</v>
+        <v>15.34639618693327</v>
       </c>
       <c r="D351" t="n">
-        <v>132.0066666666667</v>
+        <v>146.5176448787063</v>
       </c>
       <c r="E351" t="n">
-        <v>71.49706879361914</v>
+        <v>16.65886741455475</v>
       </c>
       <c r="F351" t="n">
         <v>-123</v>
@@ -10761,13 +10761,13 @@
         <v>126.0400168463613</v>
       </c>
       <c r="C352" t="n">
-        <v>71.53372731804586</v>
+        <v>15.22708062078586</v>
       </c>
       <c r="D352" t="n">
-        <v>132.0066666666667</v>
+        <v>146.4109905660378</v>
       </c>
       <c r="E352" t="n">
-        <v>71.53372731804586</v>
+        <v>16.53955184840734</v>
       </c>
       <c r="F352" t="n">
         <v>-123</v>
@@ -10790,13 +10790,13 @@
         <v>125.9333625336929</v>
       </c>
       <c r="C353" t="n">
-        <v>71.57038584247258</v>
+        <v>15.10776505463845</v>
       </c>
       <c r="D353" t="n">
-        <v>132.0066666666667</v>
+        <v>146.3043362533694</v>
       </c>
       <c r="E353" t="n">
-        <v>71.57038584247258</v>
+        <v>16.42023628225994</v>
       </c>
       <c r="F353" t="n">
         <v>-123</v>
@@ -10819,13 +10819,13 @@
         <v>125.8267082210244</v>
       </c>
       <c r="C354" t="n">
-        <v>71.60704436689929</v>
+        <v>14.98844948849104</v>
       </c>
       <c r="D354" t="n">
-        <v>132.0066666666667</v>
+        <v>146.1976819407009</v>
       </c>
       <c r="E354" t="n">
-        <v>71.60704436689929</v>
+        <v>16.30092071611253</v>
       </c>
       <c r="F354" t="n">
         <v>-123</v>
@@ -10848,13 +10848,13 @@
         <v>125.7200539083559</v>
       </c>
       <c r="C355" t="n">
-        <v>71.64370289132601</v>
+        <v>14.86913392234364</v>
       </c>
       <c r="D355" t="n">
-        <v>132.0066666666667</v>
+        <v>146.0910276280324</v>
       </c>
       <c r="E355" t="n">
-        <v>71.64370289132601</v>
+        <v>16.18160514996512</v>
       </c>
       <c r="F355" t="n">
         <v>-123</v>
@@ -10877,13 +10877,13 @@
         <v>125.6133995956875</v>
       </c>
       <c r="C356" t="n">
-        <v>71.68036141575274</v>
+        <v>14.74981835619623</v>
       </c>
       <c r="D356" t="n">
-        <v>132.0066666666667</v>
+        <v>145.984373315364</v>
       </c>
       <c r="E356" t="n">
-        <v>71.68036141575274</v>
+        <v>16.06228958381772</v>
       </c>
       <c r="F356" t="n">
         <v>-123</v>
@@ -10906,13 +10906,13 @@
         <v>125.506745283019</v>
       </c>
       <c r="C357" t="n">
-        <v>71.71701994017945</v>
+        <v>14.63050279004882</v>
       </c>
       <c r="D357" t="n">
-        <v>132.0066666666667</v>
+        <v>145.8777190026955</v>
       </c>
       <c r="E357" t="n">
-        <v>71.71701994017945</v>
+        <v>15.9429740176703</v>
       </c>
       <c r="F357" t="n">
         <v>-123</v>
@@ -10935,13 +10935,13 @@
         <v>125.4000909703505</v>
       </c>
       <c r="C358" t="n">
-        <v>71.75367846460617</v>
+        <v>14.51118722390142</v>
       </c>
       <c r="D358" t="n">
-        <v>132.0066666666667</v>
+        <v>145.7710646900271</v>
       </c>
       <c r="E358" t="n">
-        <v>71.75367846460617</v>
+        <v>15.8236584515229</v>
       </c>
       <c r="F358" t="n">
         <v>-123</v>
@@ -10964,13 +10964,13 @@
         <v>125.2934366576821</v>
       </c>
       <c r="C359" t="n">
-        <v>71.79033698903289</v>
+        <v>14.39187165775401</v>
       </c>
       <c r="D359" t="n">
-        <v>132.0066666666667</v>
+        <v>145.6644103773586</v>
       </c>
       <c r="E359" t="n">
-        <v>71.79033698903289</v>
+        <v>15.70434288537549</v>
       </c>
       <c r="F359" t="n">
         <v>-123</v>
@@ -10993,13 +10993,13 @@
         <v>125.1867823450136</v>
       </c>
       <c r="C360" t="n">
-        <v>71.82699551345962</v>
+        <v>14.2725560916066</v>
       </c>
       <c r="D360" t="n">
-        <v>132.0066666666667</v>
+        <v>145.5577560646901</v>
       </c>
       <c r="E360" t="n">
-        <v>71.82699551345962</v>
+        <v>15.58502731922808</v>
       </c>
       <c r="F360" t="n">
         <v>-123</v>
@@ -11022,13 +11022,13 @@
         <v>125.0801280323452</v>
       </c>
       <c r="C361" t="n">
-        <v>71.86365403788633</v>
+        <v>14.15324052545919</v>
       </c>
       <c r="D361" t="n">
-        <v>132.0066666666667</v>
+        <v>145.4511017520217</v>
       </c>
       <c r="E361" t="n">
-        <v>71.86365403788633</v>
+        <v>15.46571175308068</v>
       </c>
       <c r="F361" t="n">
         <v>-123</v>
@@ -11051,13 +11051,13 @@
         <v>124.9734737196767</v>
       </c>
       <c r="C362" t="n">
-        <v>71.90031256231305</v>
+        <v>14.03392495931178</v>
       </c>
       <c r="D362" t="n">
-        <v>132.0066666666667</v>
+        <v>145.3444474393532</v>
       </c>
       <c r="E362" t="n">
-        <v>71.90031256231305</v>
+        <v>15.34639618693327</v>
       </c>
       <c r="F362" t="n">
         <v>-123</v>
@@ -11080,13 +11080,13 @@
         <v>124.8668194070082</v>
       </c>
       <c r="C363" t="n">
-        <v>71.93697108673977</v>
+        <v>13.91460939316438</v>
       </c>
       <c r="D363" t="n">
-        <v>132.0066666666667</v>
+        <v>145.2377931266847</v>
       </c>
       <c r="E363" t="n">
-        <v>71.93697108673977</v>
+        <v>15.22708062078586</v>
       </c>
       <c r="F363" t="n">
         <v>-123</v>
@@ -11109,13 +11109,13 @@
         <v>124.7601650943398</v>
       </c>
       <c r="C364" t="n">
-        <v>71.9736296111665</v>
+        <v>13.79529382701697</v>
       </c>
       <c r="D364" t="n">
-        <v>132.0066666666667</v>
+        <v>145.1311388140163</v>
       </c>
       <c r="E364" t="n">
-        <v>71.9736296111665</v>
+        <v>15.10776505463845</v>
       </c>
       <c r="F364" t="n">
         <v>-123</v>
@@ -11138,13 +11138,13 @@
         <v>124.6535107816713</v>
       </c>
       <c r="C365" t="n">
-        <v>72.01028813559321</v>
+        <v>13.67597826086956</v>
       </c>
       <c r="D365" t="n">
-        <v>132.0066666666667</v>
+        <v>145.0244845013478</v>
       </c>
       <c r="E365" t="n">
-        <v>72.01028813559321</v>
+        <v>14.98844948849104</v>
       </c>
       <c r="F365" t="n">
         <v>-123</v>
@@ -11167,13 +11167,13 @@
         <v>124.5468564690028</v>
       </c>
       <c r="C366" t="n">
-        <v>72.04694666001993</v>
+        <v>13.55666269472216</v>
       </c>
       <c r="D366" t="n">
-        <v>132.0066666666667</v>
+        <v>144.9178301886793</v>
       </c>
       <c r="E366" t="n">
-        <v>72.04694666001993</v>
+        <v>14.86913392234364</v>
       </c>
       <c r="F366" t="n">
         <v>-123</v>
@@ -11196,13 +11196,13 @@
         <v>124.4402021563344</v>
       </c>
       <c r="C367" t="n">
-        <v>72.08360518444665</v>
+        <v>13.43734712857474</v>
       </c>
       <c r="D367" t="n">
-        <v>132.0066666666667</v>
+        <v>144.8111758760109</v>
       </c>
       <c r="E367" t="n">
-        <v>72.08360518444665</v>
+        <v>14.74981835619623</v>
       </c>
       <c r="F367" t="n">
         <v>-123</v>
@@ -11225,13 +11225,13 @@
         <v>124.3335478436659</v>
       </c>
       <c r="C368" t="n">
-        <v>72.12026370887338</v>
+        <v>13.31803156242734</v>
       </c>
       <c r="D368" t="n">
-        <v>132.0066666666667</v>
+        <v>144.7045215633424</v>
       </c>
       <c r="E368" t="n">
-        <v>72.12026370887338</v>
+        <v>14.63050279004882</v>
       </c>
       <c r="F368" t="n">
         <v>-123</v>
@@ -11254,13 +11254,13 @@
         <v>124.2268935309974</v>
       </c>
       <c r="C369" t="n">
-        <v>72.15692223330009</v>
+        <v>13.19871599627993</v>
       </c>
       <c r="D369" t="n">
-        <v>132.0066666666667</v>
+        <v>144.5978672506739</v>
       </c>
       <c r="E369" t="n">
-        <v>72.15692223330009</v>
+        <v>14.51118722390142</v>
       </c>
       <c r="F369" t="n">
         <v>-123</v>
@@ -11283,13 +11283,13 @@
         <v>124.120239218329</v>
       </c>
       <c r="C370" t="n">
-        <v>72.19358075772681</v>
+        <v>13.07940043013252</v>
       </c>
       <c r="D370" t="n">
-        <v>132.0066666666667</v>
+        <v>144.4912129380055</v>
       </c>
       <c r="E370" t="n">
-        <v>72.19358075772681</v>
+        <v>14.39187165775401</v>
       </c>
       <c r="F370" t="n">
         <v>-123</v>
@@ -11312,13 +11312,13 @@
         <v>124.0135849056605</v>
       </c>
       <c r="C371" t="n">
-        <v>72.23023928215353</v>
+        <v>12.96008486398512</v>
       </c>
       <c r="D371" t="n">
-        <v>132.0066666666667</v>
+        <v>144.384558625337</v>
       </c>
       <c r="E371" t="n">
-        <v>72.23023928215353</v>
+        <v>14.2725560916066</v>
       </c>
       <c r="F371" t="n">
         <v>-123</v>
@@ -11341,13 +11341,13 @@
         <v>123.9069305929921</v>
       </c>
       <c r="C372" t="n">
-        <v>72.26689780658026</v>
+        <v>12.84076929783771</v>
       </c>
       <c r="D372" t="n">
-        <v>132.0066666666667</v>
+        <v>144.2779043126686</v>
       </c>
       <c r="E372" t="n">
-        <v>72.26689780658026</v>
+        <v>14.15324052545919</v>
       </c>
       <c r="F372" t="n">
         <v>-123</v>
@@ -11370,13 +11370,13 @@
         <v>123.8002762803236</v>
       </c>
       <c r="C373" t="n">
-        <v>72.30355633100697</v>
+        <v>12.7214537316903</v>
       </c>
       <c r="D373" t="n">
-        <v>132.0066666666667</v>
+        <v>144.1712500000001</v>
       </c>
       <c r="E373" t="n">
-        <v>72.30355633100697</v>
+        <v>14.03392495931178</v>
       </c>
       <c r="F373" t="n">
         <v>-123</v>
@@ -11399,13 +11399,13 @@
         <v>123.6936219676551</v>
       </c>
       <c r="C374" t="n">
-        <v>72.34021485543369</v>
+        <v>12.60213816554289</v>
       </c>
       <c r="D374" t="n">
-        <v>132.0066666666667</v>
+        <v>144.0645956873316</v>
       </c>
       <c r="E374" t="n">
-        <v>72.34021485543369</v>
+        <v>13.91460939316438</v>
       </c>
       <c r="F374" t="n">
         <v>-123</v>
@@ -11428,13 +11428,13 @@
         <v>123.5869676549867</v>
       </c>
       <c r="C375" t="n">
-        <v>72.37687337986041</v>
+        <v>12.48282259939548</v>
       </c>
       <c r="D375" t="n">
-        <v>132.0066666666667</v>
+        <v>143.9579413746632</v>
       </c>
       <c r="E375" t="n">
-        <v>72.37687337986041</v>
+        <v>13.79529382701697</v>
       </c>
       <c r="F375" t="n">
         <v>-123</v>
@@ -11457,13 +11457,13 @@
         <v>123.4803133423182</v>
       </c>
       <c r="C376" t="n">
-        <v>72.41353190428713</v>
+        <v>12.36350703324808</v>
       </c>
       <c r="D376" t="n">
-        <v>132.0066666666667</v>
+        <v>143.8512870619947</v>
       </c>
       <c r="E376" t="n">
-        <v>72.41353190428713</v>
+        <v>13.67597826086956</v>
       </c>
       <c r="F376" t="n">
         <v>-123</v>
@@ -11486,13 +11486,13 @@
         <v>123.3736590296497</v>
       </c>
       <c r="C377" t="n">
-        <v>72.45019042871385</v>
+        <v>12.24419146710067</v>
       </c>
       <c r="D377" t="n">
-        <v>132.0066666666667</v>
+        <v>143.7446327493262</v>
       </c>
       <c r="E377" t="n">
-        <v>72.45019042871385</v>
+        <v>13.55666269472216</v>
       </c>
       <c r="F377" t="n">
         <v>-123</v>
@@ -11515,13 +11515,13 @@
         <v>123.2670047169813</v>
       </c>
       <c r="C378" t="n">
-        <v>72.48684895314057</v>
+        <v>12.12487590095326</v>
       </c>
       <c r="D378" t="n">
-        <v>132.0066666666667</v>
+        <v>143.6379784366578</v>
       </c>
       <c r="E378" t="n">
-        <v>72.48684895314057</v>
+        <v>13.43734712857474</v>
       </c>
       <c r="F378" t="n">
         <v>-123</v>
@@ -11544,13 +11544,13 @@
         <v>123.1603504043128</v>
       </c>
       <c r="C379" t="n">
-        <v>72.52350747756729</v>
+        <v>12.00556033480586</v>
       </c>
       <c r="D379" t="n">
-        <v>132.0066666666667</v>
+        <v>143.5313241239893</v>
       </c>
       <c r="E379" t="n">
-        <v>72.52350747756729</v>
+        <v>13.31803156242734</v>
       </c>
       <c r="F379" t="n">
         <v>-123</v>
@@ -11573,13 +11573,13 @@
         <v>123.0536960916444</v>
       </c>
       <c r="C380" t="n">
-        <v>72.56016600199401</v>
+        <v>11.88624476865845</v>
       </c>
       <c r="D380" t="n">
-        <v>132.0066666666667</v>
+        <v>143.4246698113209</v>
       </c>
       <c r="E380" t="n">
-        <v>72.56016600199401</v>
+        <v>13.19871599627993</v>
       </c>
       <c r="F380" t="n">
         <v>-123</v>
@@ -11602,13 +11602,13 @@
         <v>122.9470417789759</v>
       </c>
       <c r="C381" t="n">
-        <v>72.59682452642073</v>
+        <v>11.76692920251104</v>
       </c>
       <c r="D381" t="n">
-        <v>132.0066666666667</v>
+        <v>143.3180154986524</v>
       </c>
       <c r="E381" t="n">
-        <v>72.59682452642073</v>
+        <v>13.07940043013252</v>
       </c>
       <c r="F381" t="n">
         <v>-123</v>
@@ -11631,13 +11631,13 @@
         <v>122.8403874663074</v>
       </c>
       <c r="C382" t="n">
-        <v>72.63348305084745</v>
+        <v>11.64761363636363</v>
       </c>
       <c r="D382" t="n">
-        <v>132.0066666666667</v>
+        <v>143.2113611859839</v>
       </c>
       <c r="E382" t="n">
-        <v>72.63348305084745</v>
+        <v>12.96008486398512</v>
       </c>
       <c r="F382" t="n">
         <v>-123</v>
@@ -11660,13 +11660,13 @@
         <v>122.733733153639</v>
       </c>
       <c r="C383" t="n">
-        <v>72.67014157527417</v>
+        <v>11.52829807021622</v>
       </c>
       <c r="D383" t="n">
-        <v>132.0066666666667</v>
+        <v>143.1047068733155</v>
       </c>
       <c r="E383" t="n">
-        <v>72.67014157527417</v>
+        <v>12.84076929783771</v>
       </c>
       <c r="F383" t="n">
         <v>-123</v>
@@ -11689,13 +11689,13 @@
         <v>122.6270788409705</v>
       </c>
       <c r="C384" t="n">
-        <v>72.70680009970089</v>
+        <v>11.40898250406882</v>
       </c>
       <c r="D384" t="n">
-        <v>132.0066666666667</v>
+        <v>142.998052560647</v>
       </c>
       <c r="E384" t="n">
-        <v>72.70680009970089</v>
+        <v>12.7214537316903</v>
       </c>
       <c r="F384" t="n">
         <v>-123</v>
@@ -11718,13 +11718,13 @@
         <v>122.520424528302</v>
       </c>
       <c r="C385" t="n">
-        <v>72.74345862412761</v>
+        <v>11.28966693792141</v>
       </c>
       <c r="D385" t="n">
-        <v>132.0066666666667</v>
+        <v>142.8913982479785</v>
       </c>
       <c r="E385" t="n">
-        <v>72.74345862412761</v>
+        <v>12.60213816554289</v>
       </c>
       <c r="F385" t="n">
         <v>-123</v>
@@ -11747,13 +11747,13 @@
         <v>122.4137702156336</v>
       </c>
       <c r="C386" t="n">
-        <v>72.78011714855433</v>
+        <v>11.170351371774</v>
       </c>
       <c r="D386" t="n">
-        <v>132.0066666666667</v>
+        <v>142.7847439353101</v>
       </c>
       <c r="E386" t="n">
-        <v>72.78011714855433</v>
+        <v>12.48282259939548</v>
       </c>
       <c r="F386" t="n">
         <v>-123</v>
@@ -11776,13 +11776,13 @@
         <v>122.3071159029651</v>
       </c>
       <c r="C387" t="n">
-        <v>72.81677567298105</v>
+        <v>11.0510358056266</v>
       </c>
       <c r="D387" t="n">
-        <v>132.0066666666667</v>
+        <v>142.6780896226416</v>
       </c>
       <c r="E387" t="n">
-        <v>72.81677567298105</v>
+        <v>12.36350703324808</v>
       </c>
       <c r="F387" t="n">
         <v>-123</v>
@@ -11805,13 +11805,13 @@
         <v>122.2004615902966</v>
       </c>
       <c r="C388" t="n">
-        <v>72.85343419740776</v>
+        <v>10.93172023947918</v>
       </c>
       <c r="D388" t="n">
-        <v>132.0066666666667</v>
+        <v>142.5714353099731</v>
       </c>
       <c r="E388" t="n">
-        <v>72.85343419740776</v>
+        <v>12.24419146710067</v>
       </c>
       <c r="F388" t="n">
         <v>-123</v>
@@ -11834,13 +11834,13 @@
         <v>122.0938072776282</v>
       </c>
       <c r="C389" t="n">
-        <v>72.89009272183449</v>
+        <v>10.81240467333178</v>
       </c>
       <c r="D389" t="n">
-        <v>132.0066666666667</v>
+        <v>142.4647809973047</v>
       </c>
       <c r="E389" t="n">
-        <v>72.89009272183449</v>
+        <v>12.12487590095326</v>
       </c>
       <c r="F389" t="n">
         <v>-123</v>
@@ -11863,13 +11863,13 @@
         <v>121.9871529649597</v>
       </c>
       <c r="C390" t="n">
-        <v>72.9267512462612</v>
+        <v>10.69308910718437</v>
       </c>
       <c r="D390" t="n">
-        <v>132.0066666666667</v>
+        <v>142.3581266846362</v>
       </c>
       <c r="E390" t="n">
-        <v>72.9267512462612</v>
+        <v>12.00556033480586</v>
       </c>
       <c r="F390" t="n">
         <v>-123</v>
@@ -11892,13 +11892,13 @@
         <v>121.8804986522913</v>
       </c>
       <c r="C391" t="n">
-        <v>72.96340977068793</v>
+        <v>10.57377354103696</v>
       </c>
       <c r="D391" t="n">
-        <v>132.0066666666667</v>
+        <v>142.2514723719678</v>
       </c>
       <c r="E391" t="n">
-        <v>72.96340977068793</v>
+        <v>11.88624476865845</v>
       </c>
       <c r="F391" t="n">
         <v>-123</v>
@@ -11921,13 +11921,13 @@
         <v>121.7738443396228</v>
       </c>
       <c r="C392" t="n">
-        <v>73.00006829511464</v>
+        <v>10.45445797488956</v>
       </c>
       <c r="D392" t="n">
-        <v>132.0066666666667</v>
+        <v>142.1448180592993</v>
       </c>
       <c r="E392" t="n">
-        <v>73.00006829511464</v>
+        <v>11.76692920251104</v>
       </c>
       <c r="F392" t="n">
         <v>-123</v>
@@ -11950,13 +11950,13 @@
         <v>121.6671900269543</v>
       </c>
       <c r="C393" t="n">
-        <v>73.03672681954137</v>
+        <v>10.33514240874215</v>
       </c>
       <c r="D393" t="n">
-        <v>132.0066666666667</v>
+        <v>142.0381637466308</v>
       </c>
       <c r="E393" t="n">
-        <v>73.03672681954137</v>
+        <v>11.64761363636363</v>
       </c>
       <c r="F393" t="n">
         <v>-123</v>
@@ -11979,13 +11979,13 @@
         <v>121.5605357142859</v>
       </c>
       <c r="C394" t="n">
-        <v>73.07338534396808</v>
+        <v>10.21582684259474</v>
       </c>
       <c r="D394" t="n">
-        <v>132.0066666666667</v>
+        <v>141.9315094339624</v>
       </c>
       <c r="E394" t="n">
-        <v>73.07338534396808</v>
+        <v>11.52829807021622</v>
       </c>
       <c r="F394" t="n">
         <v>-123</v>
@@ -12008,13 +12008,13 @@
         <v>121.4538814016174</v>
       </c>
       <c r="C395" t="n">
-        <v>73.11004386839481</v>
+        <v>10.09651127644733</v>
       </c>
       <c r="D395" t="n">
-        <v>132.0066666666667</v>
+        <v>141.8248551212939</v>
       </c>
       <c r="E395" t="n">
-        <v>73.11004386839481</v>
+        <v>11.40898250406882</v>
       </c>
       <c r="F395" t="n">
         <v>-123</v>
@@ -12037,13 +12037,13 @@
         <v>121.3472270889489</v>
       </c>
       <c r="C396" t="n">
-        <v>73.14670239282152</v>
+        <v>9.977195710299924</v>
       </c>
       <c r="D396" t="n">
-        <v>132.0066666666667</v>
+        <v>141.7182008086255</v>
       </c>
       <c r="E396" t="n">
-        <v>73.14670239282152</v>
+        <v>11.28966693792141</v>
       </c>
       <c r="F396" t="n">
         <v>-123</v>
@@ -12066,13 +12066,13 @@
         <v>121.2405727762805</v>
       </c>
       <c r="C397" t="n">
-        <v>73.18336091724825</v>
+        <v>9.857880144152517</v>
       </c>
       <c r="D397" t="n">
-        <v>132.0066666666667</v>
+        <v>141.611546495957</v>
       </c>
       <c r="E397" t="n">
-        <v>73.18336091724825</v>
+        <v>11.170351371774</v>
       </c>
       <c r="F397" t="n">
         <v>-123</v>
@@ -12095,13 +12095,13 @@
         <v>121.133918463612</v>
       </c>
       <c r="C398" t="n">
-        <v>73.22001944167496</v>
+        <v>9.738564578005111</v>
       </c>
       <c r="D398" t="n">
-        <v>132.0066666666667</v>
+        <v>141.5048921832885</v>
       </c>
       <c r="E398" t="n">
-        <v>73.22001944167496</v>
+        <v>11.0510358056266</v>
       </c>
       <c r="F398" t="n">
         <v>-123</v>
@@ -12124,13 +12124,13 @@
         <v>121.0272641509436</v>
       </c>
       <c r="C399" t="n">
-        <v>73.25667796610169</v>
+        <v>9.619249011857704</v>
       </c>
       <c r="D399" t="n">
-        <v>132.0066666666667</v>
+        <v>141.3982378706201</v>
       </c>
       <c r="E399" t="n">
-        <v>73.25667796610169</v>
+        <v>10.93172023947918</v>
       </c>
       <c r="F399" t="n">
         <v>-123</v>
@@ -12153,13 +12153,13 @@
         <v>120.9206098382751</v>
       </c>
       <c r="C400" t="n">
-        <v>73.2933364905284</v>
+        <v>9.499933445710298</v>
       </c>
       <c r="D400" t="n">
-        <v>132.0066666666667</v>
+        <v>141.2915835579516</v>
       </c>
       <c r="E400" t="n">
-        <v>73.2933364905284</v>
+        <v>10.81240467333178</v>
       </c>
       <c r="F400" t="n">
         <v>-123</v>
@@ -12182,13 +12182,13 @@
         <v>120.8139555256066</v>
       </c>
       <c r="C401" t="n">
-        <v>73.32999501495513</v>
+        <v>9.380617879562891</v>
       </c>
       <c r="D401" t="n">
-        <v>132.0066666666667</v>
+        <v>141.1849292452831</v>
       </c>
       <c r="E401" t="n">
-        <v>73.32999501495513</v>
+        <v>10.69308910718437</v>
       </c>
       <c r="F401" t="n">
         <v>-123</v>
@@ -12211,13 +12211,13 @@
         <v>120.7073012129381</v>
       </c>
       <c r="C402" t="n">
-        <v>73.36665353938184</v>
+        <v>9.261302313415477</v>
       </c>
       <c r="D402" t="n">
-        <v>132.0066666666667</v>
+        <v>141.0782749326146</v>
       </c>
       <c r="E402" t="n">
-        <v>73.36665353938184</v>
+        <v>10.57377354103696</v>
       </c>
       <c r="F402" t="n">
         <v>-123</v>
@@ -12240,13 +12240,13 @@
         <v>120.6006469002697</v>
       </c>
       <c r="C403" t="n">
-        <v>73.40331206380857</v>
+        <v>9.141986747268071</v>
       </c>
       <c r="D403" t="n">
-        <v>132.0066666666667</v>
+        <v>140.9716206199462</v>
       </c>
       <c r="E403" t="n">
-        <v>73.40331206380857</v>
+        <v>10.45445797488956</v>
       </c>
       <c r="F403" t="n">
         <v>-123</v>
@@ -12269,13 +12269,13 @@
         <v>120.4939925876012</v>
       </c>
       <c r="C404" t="n">
-        <v>73.43997058823528</v>
+        <v>9.022671181120664</v>
       </c>
       <c r="D404" t="n">
-        <v>132.0066666666667</v>
+        <v>140.8649663072777</v>
       </c>
       <c r="E404" t="n">
-        <v>73.43997058823528</v>
+        <v>10.33514240874215</v>
       </c>
       <c r="F404" t="n">
         <v>-123</v>
@@ -12298,13 +12298,13 @@
         <v>120.3873382749328</v>
       </c>
       <c r="C405" t="n">
-        <v>73.47662911266201</v>
+        <v>8.903355614973258</v>
       </c>
       <c r="D405" t="n">
-        <v>132.0066666666667</v>
+        <v>140.7583119946093</v>
       </c>
       <c r="E405" t="n">
-        <v>73.47662911266201</v>
+        <v>10.21582684259474</v>
       </c>
       <c r="F405" t="n">
         <v>-123</v>
@@ -12327,13 +12327,13 @@
         <v>120.2806839622643</v>
       </c>
       <c r="C406" t="n">
-        <v>73.51328763708872</v>
+        <v>8.784040048825851</v>
       </c>
       <c r="D406" t="n">
-        <v>132.0066666666667</v>
+        <v>140.6516576819408</v>
       </c>
       <c r="E406" t="n">
-        <v>73.51328763708872</v>
+        <v>10.09651127644733</v>
       </c>
       <c r="F406" t="n">
         <v>-123</v>
@@ -12356,13 +12356,13 @@
         <v>120.1740296495958</v>
       </c>
       <c r="C407" t="n">
-        <v>73.54994616151545</v>
+        <v>8.664724482678444</v>
       </c>
       <c r="D407" t="n">
-        <v>132.0066666666667</v>
+        <v>140.5450033692723</v>
       </c>
       <c r="E407" t="n">
-        <v>73.54994616151545</v>
+        <v>9.977195710299924</v>
       </c>
       <c r="F407" t="n">
         <v>-123</v>
@@ -12385,13 +12385,13 @@
         <v>120.0673753369274</v>
       </c>
       <c r="C408" t="n">
-        <v>73.58660468594216</v>
+        <v>8.545408916531038</v>
       </c>
       <c r="D408" t="n">
-        <v>132.0066666666667</v>
+        <v>140.4383490566039</v>
       </c>
       <c r="E408" t="n">
-        <v>73.58660468594216</v>
+        <v>9.857880144152517</v>
       </c>
       <c r="F408" t="n">
         <v>-123</v>
@@ -12414,13 +12414,13 @@
         <v>119.9607210242589</v>
       </c>
       <c r="C409" t="n">
-        <v>73.62326321036889</v>
+        <v>8.426093350383624</v>
       </c>
       <c r="D409" t="n">
-        <v>132.0066666666667</v>
+        <v>140.3316947439354</v>
       </c>
       <c r="E409" t="n">
-        <v>73.62326321036889</v>
+        <v>9.738564578005111</v>
       </c>
       <c r="F409" t="n">
         <v>-123</v>
@@ -12443,13 +12443,13 @@
         <v>119.8540667115904</v>
       </c>
       <c r="C410" t="n">
-        <v>73.6599217347956</v>
+        <v>8.306777784236218</v>
       </c>
       <c r="D410" t="n">
-        <v>132.0066666666667</v>
+        <v>140.225040431267</v>
       </c>
       <c r="E410" t="n">
-        <v>73.6599217347956</v>
+        <v>9.619249011857704</v>
       </c>
       <c r="F410" t="n">
         <v>-123</v>
@@ -12472,13 +12472,13 @@
         <v>119.747412398922</v>
       </c>
       <c r="C411" t="n">
-        <v>73.69658025922233</v>
+        <v>8.187462218088811</v>
       </c>
       <c r="D411" t="n">
-        <v>132.0066666666667</v>
+        <v>140.1183861185985</v>
       </c>
       <c r="E411" t="n">
-        <v>73.69658025922233</v>
+        <v>9.499933445710298</v>
       </c>
       <c r="F411" t="n">
         <v>-123</v>
@@ -12501,13 +12501,13 @@
         <v>119.6407580862535</v>
       </c>
       <c r="C412" t="n">
-        <v>73.73323878364904</v>
+        <v>8.068146651941404</v>
       </c>
       <c r="D412" t="n">
-        <v>132.0066666666667</v>
+        <v>140.01173180593</v>
       </c>
       <c r="E412" t="n">
-        <v>73.73323878364904</v>
+        <v>9.380617879562891</v>
       </c>
       <c r="F412" t="n">
         <v>-123</v>
@@ -12530,13 +12530,13 @@
         <v>119.5341037735851</v>
       </c>
       <c r="C413" t="n">
-        <v>73.76989730807577</v>
+        <v>7.948831085793998</v>
       </c>
       <c r="D413" t="n">
-        <v>132.0066666666667</v>
+        <v>139.9050774932616</v>
       </c>
       <c r="E413" t="n">
-        <v>73.76989730807577</v>
+        <v>9.261302313415477</v>
       </c>
       <c r="F413" t="n">
         <v>-123</v>
@@ -12559,13 +12559,13 @@
         <v>119.4274494609166</v>
       </c>
       <c r="C414" t="n">
-        <v>73.80655583250248</v>
+        <v>7.829515519646591</v>
       </c>
       <c r="D414" t="n">
-        <v>132.0066666666667</v>
+        <v>139.7984231805931</v>
       </c>
       <c r="E414" t="n">
-        <v>73.80655583250248</v>
+        <v>9.141986747268071</v>
       </c>
       <c r="F414" t="n">
         <v>-123</v>
@@ -12588,13 +12588,13 @@
         <v>119.3207951482481</v>
       </c>
       <c r="C415" t="n">
-        <v>73.84321435692921</v>
+        <v>7.710199953499185</v>
       </c>
       <c r="D415" t="n">
-        <v>132.0066666666667</v>
+        <v>139.6917688679246</v>
       </c>
       <c r="E415" t="n">
-        <v>73.84321435692921</v>
+        <v>9.022671181120664</v>
       </c>
       <c r="F415" t="n">
         <v>-123</v>
@@ -12617,13 +12617,13 @@
         <v>119.2141408355797</v>
       </c>
       <c r="C416" t="n">
-        <v>73.87987288135592</v>
+        <v>7.590884387351771</v>
       </c>
       <c r="D416" t="n">
-        <v>132.0066666666667</v>
+        <v>139.5851145552562</v>
       </c>
       <c r="E416" t="n">
-        <v>73.87987288135592</v>
+        <v>8.903355614973258</v>
       </c>
       <c r="F416" t="n">
         <v>-123</v>
@@ -12646,13 +12646,13 @@
         <v>119.1074865229112</v>
       </c>
       <c r="C417" t="n">
-        <v>73.91653140578265</v>
+        <v>7.471568821204364</v>
       </c>
       <c r="D417" t="n">
-        <v>132.0066666666667</v>
+        <v>139.4784602425877</v>
       </c>
       <c r="E417" t="n">
-        <v>73.91653140578265</v>
+        <v>8.784040048825851</v>
       </c>
       <c r="F417" t="n">
         <v>-123</v>
@@ -12675,13 +12675,13 @@
         <v>119.0008322102427</v>
       </c>
       <c r="C418" t="n">
-        <v>73.95318993020936</v>
+        <v>7.352253255056958</v>
       </c>
       <c r="D418" t="n">
-        <v>132.0066666666667</v>
+        <v>139.3718059299192</v>
       </c>
       <c r="E418" t="n">
-        <v>73.95318993020936</v>
+        <v>8.664724482678444</v>
       </c>
       <c r="F418" t="n">
         <v>-123</v>
@@ -12704,13 +12704,13 @@
         <v>118.8941778975743</v>
       </c>
       <c r="C419" t="n">
-        <v>73.98984845463609</v>
+        <v>7.232937688909551</v>
       </c>
       <c r="D419" t="n">
-        <v>132.0066666666667</v>
+        <v>139.2651516172508</v>
       </c>
       <c r="E419" t="n">
-        <v>73.98984845463609</v>
+        <v>8.545408916531038</v>
       </c>
       <c r="F419" t="n">
         <v>-123</v>
@@ -12733,13 +12733,13 @@
         <v>118.7875235849058</v>
       </c>
       <c r="C420" t="n">
-        <v>74.0265069790628</v>
+        <v>7.113622122762145</v>
       </c>
       <c r="D420" t="n">
-        <v>132.0066666666667</v>
+        <v>139.1584973045823</v>
       </c>
       <c r="E420" t="n">
-        <v>74.0265069790628</v>
+        <v>8.426093350383624</v>
       </c>
       <c r="F420" t="n">
         <v>-123</v>
@@ -12762,13 +12762,13 @@
         <v>118.6808692722374</v>
       </c>
       <c r="C421" t="n">
-        <v>74.06316550348953</v>
+        <v>6.994306556614738</v>
       </c>
       <c r="D421" t="n">
-        <v>132.0066666666667</v>
+        <v>139.0518429919139</v>
       </c>
       <c r="E421" t="n">
-        <v>74.06316550348953</v>
+        <v>8.306777784236218</v>
       </c>
       <c r="F421" t="n">
         <v>-123</v>
@@ -12791,13 +12791,13 @@
         <v>118.5742149595689</v>
       </c>
       <c r="C422" t="n">
-        <v>74.09982402791624</v>
+        <v>6.874990990467332</v>
       </c>
       <c r="D422" t="n">
-        <v>132.0066666666667</v>
+        <v>138.9451886792454</v>
       </c>
       <c r="E422" t="n">
-        <v>74.09982402791624</v>
+        <v>8.187462218088811</v>
       </c>
       <c r="F422" t="n">
         <v>-123</v>
@@ -12820,13 +12820,13 @@
         <v>118.4675606469004</v>
       </c>
       <c r="C423" t="n">
-        <v>74.13648255234297</v>
+        <v>6.755675424319918</v>
       </c>
       <c r="D423" t="n">
-        <v>132.0066666666667</v>
+        <v>138.8385343665769</v>
       </c>
       <c r="E423" t="n">
-        <v>74.13648255234297</v>
+        <v>8.068146651941404</v>
       </c>
       <c r="F423" t="n">
         <v>-123</v>
@@ -12849,13 +12849,13 @@
         <v>118.360906334232</v>
       </c>
       <c r="C424" t="n">
-        <v>74.17314107676968</v>
+        <v>6.636359858172511</v>
       </c>
       <c r="D424" t="n">
-        <v>132.0066666666667</v>
+        <v>138.7318800539085</v>
       </c>
       <c r="E424" t="n">
-        <v>74.17314107676968</v>
+        <v>7.948831085793998</v>
       </c>
       <c r="F424" t="n">
         <v>-123</v>
@@ -12878,13 +12878,13 @@
         <v>118.2542520215635</v>
       </c>
       <c r="C425" t="n">
-        <v>74.20979960119641</v>
+        <v>6.517044292025105</v>
       </c>
       <c r="D425" t="n">
-        <v>132.0066666666667</v>
+        <v>138.62522574124</v>
       </c>
       <c r="E425" t="n">
-        <v>74.20979960119641</v>
+        <v>7.829515519646591</v>
       </c>
       <c r="F425" t="n">
         <v>-123</v>
@@ -12907,13 +12907,13 @@
         <v>118.147597708895</v>
       </c>
       <c r="C426" t="n">
-        <v>74.24645812562312</v>
+        <v>6.397728725877698</v>
       </c>
       <c r="D426" t="n">
-        <v>132.0066666666667</v>
+        <v>138.5185714285715</v>
       </c>
       <c r="E426" t="n">
-        <v>74.24645812562312</v>
+        <v>7.710199953499185</v>
       </c>
       <c r="F426" t="n">
         <v>-123</v>
@@ -12936,13 +12936,13 @@
         <v>118.0409433962266</v>
       </c>
       <c r="C427" t="n">
-        <v>74.28311665004985</v>
+        <v>6.278413159730292</v>
       </c>
       <c r="D427" t="n">
-        <v>132.0066666666667</v>
+        <v>138.4119171159031</v>
       </c>
       <c r="E427" t="n">
-        <v>74.28311665004985</v>
+        <v>7.590884387351771</v>
       </c>
       <c r="F427" t="n">
         <v>-123</v>
@@ -12965,13 +12965,13 @@
         <v>117.9342890835581</v>
       </c>
       <c r="C428" t="n">
-        <v>74.31977517447656</v>
+        <v>6.159097593582885</v>
       </c>
       <c r="D428" t="n">
-        <v>132.0066666666667</v>
+        <v>138.3052628032346</v>
       </c>
       <c r="E428" t="n">
-        <v>74.31977517447656</v>
+        <v>7.471568821204364</v>
       </c>
       <c r="F428" t="n">
         <v>-123</v>
@@ -12994,13 +12994,13 @@
         <v>117.8276347708896</v>
       </c>
       <c r="C429" t="n">
-        <v>74.35643369890329</v>
+        <v>6.039782027435479</v>
       </c>
       <c r="D429" t="n">
-        <v>132.0066666666667</v>
+        <v>138.1986084905662</v>
       </c>
       <c r="E429" t="n">
-        <v>74.35643369890329</v>
+        <v>7.352253255056958</v>
       </c>
       <c r="F429" t="n">
         <v>-123</v>
@@ -13023,13 +13023,13 @@
         <v>117.7209804582212</v>
       </c>
       <c r="C430" t="n">
-        <v>74.39309222333</v>
+        <v>5.920466461288065</v>
       </c>
       <c r="D430" t="n">
-        <v>132.0066666666667</v>
+        <v>138.0919541778977</v>
       </c>
       <c r="E430" t="n">
-        <v>74.39309222333</v>
+        <v>7.232937688909551</v>
       </c>
       <c r="F430" t="n">
         <v>-123</v>
@@ -13052,13 +13052,13 @@
         <v>117.6143261455527</v>
       </c>
       <c r="C431" t="n">
-        <v>74.42975074775673</v>
+        <v>5.801150895140658</v>
       </c>
       <c r="D431" t="n">
-        <v>132.0066666666667</v>
+        <v>137.9852998652292</v>
       </c>
       <c r="E431" t="n">
-        <v>74.42975074775673</v>
+        <v>7.113622122762145</v>
       </c>
       <c r="F431" t="n">
         <v>-123</v>
@@ -13081,13 +13081,13 @@
         <v>117.5076718328843</v>
       </c>
       <c r="C432" t="n">
-        <v>74.46640927218344</v>
+        <v>5.681835328993252</v>
       </c>
       <c r="D432" t="n">
-        <v>132.0066666666667</v>
+        <v>137.8786455525608</v>
       </c>
       <c r="E432" t="n">
-        <v>74.46640927218344</v>
+        <v>6.994306556614738</v>
       </c>
       <c r="F432" t="n">
         <v>-123</v>
@@ -13110,13 +13110,13 @@
         <v>117.4010175202158</v>
       </c>
       <c r="C433" t="n">
-        <v>74.50306779661017</v>
+        <v>5.562519762845845</v>
       </c>
       <c r="D433" t="n">
-        <v>132.0066666666667</v>
+        <v>137.7719912398923</v>
       </c>
       <c r="E433" t="n">
-        <v>74.50306779661017</v>
+        <v>6.874990990467332</v>
       </c>
       <c r="F433" t="n">
         <v>-123</v>
@@ -13139,13 +13139,13 @@
         <v>117.2943632075473</v>
       </c>
       <c r="C434" t="n">
-        <v>74.53972632103688</v>
+        <v>5.443204196698439</v>
       </c>
       <c r="D434" t="n">
-        <v>132.0066666666667</v>
+        <v>137.6653369272238</v>
       </c>
       <c r="E434" t="n">
-        <v>74.53972632103688</v>
+        <v>6.755675424319918</v>
       </c>
       <c r="F434" t="n">
         <v>-123</v>
@@ -13168,13 +13168,13 @@
         <v>117.1877088948789</v>
       </c>
       <c r="C435" t="n">
-        <v>74.57638484546359</v>
+        <v>5.323888630551032</v>
       </c>
       <c r="D435" t="n">
-        <v>132.0066666666667</v>
+        <v>137.5586826145554</v>
       </c>
       <c r="E435" t="n">
-        <v>74.57638484546359</v>
+        <v>6.636359858172511</v>
       </c>
       <c r="F435" t="n">
         <v>-123</v>
@@ -13197,13 +13197,13 @@
         <v>117.0810545822104</v>
       </c>
       <c r="C436" t="n">
-        <v>74.61304336989032</v>
+        <v>5.204573064403625</v>
       </c>
       <c r="D436" t="n">
-        <v>132.0066666666667</v>
+        <v>137.4520283018869</v>
       </c>
       <c r="E436" t="n">
-        <v>74.61304336989032</v>
+        <v>6.517044292025105</v>
       </c>
       <c r="F436" t="n">
         <v>-123</v>
@@ -13226,13 +13226,13 @@
         <v>116.9744002695419</v>
       </c>
       <c r="C437" t="n">
-        <v>74.64970189431705</v>
+        <v>5.085257498256212</v>
       </c>
       <c r="D437" t="n">
-        <v>132.0066666666667</v>
+        <v>137.3453739892184</v>
       </c>
       <c r="E437" t="n">
-        <v>74.64970189431705</v>
+        <v>6.397728725877698</v>
       </c>
       <c r="F437" t="n">
         <v>-123</v>
@@ -13255,13 +13255,13 @@
         <v>116.8677459568735</v>
       </c>
       <c r="C438" t="n">
-        <v>74.68636041874376</v>
+        <v>4.965941932108805</v>
       </c>
       <c r="D438" t="n">
-        <v>132.0066666666667</v>
+        <v>137.23871967655</v>
       </c>
       <c r="E438" t="n">
-        <v>74.68636041874376</v>
+        <v>6.278413159730292</v>
       </c>
       <c r="F438" t="n">
         <v>-123</v>
@@ -13284,13 +13284,13 @@
         <v>116.761091644205</v>
       </c>
       <c r="C439" t="n">
-        <v>74.72301894317047</v>
+        <v>4.846626365961399</v>
       </c>
       <c r="D439" t="n">
-        <v>132.0066666666667</v>
+        <v>137.1320653638815</v>
       </c>
       <c r="E439" t="n">
-        <v>74.72301894317047</v>
+        <v>6.159097593582885</v>
       </c>
       <c r="F439" t="n">
         <v>-123</v>
@@ -13313,13 +13313,13 @@
         <v>116.6544373315366</v>
       </c>
       <c r="C440" t="n">
-        <v>74.7596774675972</v>
+        <v>4.727310799813992</v>
       </c>
       <c r="D440" t="n">
-        <v>132.0066666666667</v>
+        <v>137.025411051213</v>
       </c>
       <c r="E440" t="n">
-        <v>74.7596774675972</v>
+        <v>6.039782027435479</v>
       </c>
       <c r="F440" t="n">
         <v>-123</v>
@@ -13342,13 +13342,13 @@
         <v>116.5477830188681</v>
       </c>
       <c r="C441" t="n">
-        <v>74.79633599202393</v>
+        <v>4.607995233666585</v>
       </c>
       <c r="D441" t="n">
-        <v>132.0066666666667</v>
+        <v>136.9187567385446</v>
       </c>
       <c r="E441" t="n">
-        <v>74.79633599202393</v>
+        <v>5.920466461288065</v>
       </c>
       <c r="F441" t="n">
         <v>-123</v>
@@ -13371,13 +13371,13 @@
         <v>116.4411287061996</v>
       </c>
       <c r="C442" t="n">
-        <v>74.83299451645064</v>
+        <v>4.488679667519179</v>
       </c>
       <c r="D442" t="n">
-        <v>132.0066666666667</v>
+        <v>136.8121024258761</v>
       </c>
       <c r="E442" t="n">
-        <v>74.83299451645064</v>
+        <v>5.801150895140658</v>
       </c>
       <c r="F442" t="n">
         <v>-123</v>
@@ -13400,13 +13400,13 @@
         <v>116.3344743935312</v>
       </c>
       <c r="C443" t="n">
-        <v>74.86965304087735</v>
+        <v>4.369364101371772</v>
       </c>
       <c r="D443" t="n">
-        <v>132.0066666666667</v>
+        <v>136.7054481132077</v>
       </c>
       <c r="E443" t="n">
-        <v>74.86965304087735</v>
+        <v>5.681835328993252</v>
       </c>
       <c r="F443" t="n">
         <v>-123</v>
@@ -13429,13 +13429,13 @@
         <v>116.2278200808627</v>
       </c>
       <c r="C444" t="n">
-        <v>74.90631156530408</v>
+        <v>4.250048535224359</v>
       </c>
       <c r="D444" t="n">
-        <v>132.0066666666667</v>
+        <v>136.5987938005392</v>
       </c>
       <c r="E444" t="n">
-        <v>74.90631156530408</v>
+        <v>5.562519762845845</v>
       </c>
       <c r="F444" t="n">
         <v>-123</v>
@@ -13458,13 +13458,13 @@
         <v>116.1211657681942</v>
       </c>
       <c r="C445" t="n">
-        <v>74.94297008973081</v>
+        <v>4.130732969076952</v>
       </c>
       <c r="D445" t="n">
-        <v>132.0066666666667</v>
+        <v>136.4921394878707</v>
       </c>
       <c r="E445" t="n">
-        <v>74.94297008973081</v>
+        <v>5.443204196698439</v>
       </c>
       <c r="F445" t="n">
         <v>-123</v>
@@ -13487,13 +13487,13 @@
         <v>116.0145114555258</v>
       </c>
       <c r="C446" t="n">
-        <v>74.97962861415752</v>
+        <v>4.011417402929546</v>
       </c>
       <c r="D446" t="n">
-        <v>132.0066666666667</v>
+        <v>136.3854851752023</v>
       </c>
       <c r="E446" t="n">
-        <v>74.97962861415752</v>
+        <v>5.323888630551032</v>
       </c>
       <c r="F446" t="n">
         <v>-123</v>
@@ -13516,13 +13516,13 @@
         <v>115.9078571428573</v>
       </c>
       <c r="C447" t="n">
-        <v>75.01628713858423</v>
+        <v>3.892101836782139</v>
       </c>
       <c r="D447" t="n">
-        <v>132.0066666666667</v>
+        <v>136.2788308625338</v>
       </c>
       <c r="E447" t="n">
-        <v>75.01628713858423</v>
+        <v>5.204573064403625</v>
       </c>
       <c r="F447" t="n">
         <v>-123</v>
@@ -13545,13 +13545,13 @@
         <v>115.8012028301888</v>
       </c>
       <c r="C448" t="n">
-        <v>75.05294566301096</v>
+        <v>3.772786270634732</v>
       </c>
       <c r="D448" t="n">
-        <v>132.0066666666667</v>
+        <v>136.1721765498654</v>
       </c>
       <c r="E448" t="n">
-        <v>75.05294566301096</v>
+        <v>5.085257498256212</v>
       </c>
       <c r="F448" t="n">
         <v>-123</v>
@@ -13574,13 +13574,13 @@
         <v>115.6945485175204</v>
       </c>
       <c r="C449" t="n">
-        <v>75.08960418743769</v>
+        <v>3.653470704487326</v>
       </c>
       <c r="D449" t="n">
-        <v>132.0066666666667</v>
+        <v>136.0655222371969</v>
       </c>
       <c r="E449" t="n">
-        <v>75.08960418743769</v>
+        <v>4.965941932108805</v>
       </c>
       <c r="F449" t="n">
         <v>-123</v>
@@ -13603,13 +13603,13 @@
         <v>115.5878942048519</v>
       </c>
       <c r="C450" t="n">
-        <v>75.1262627118644</v>
+        <v>3.534155138339919</v>
       </c>
       <c r="D450" t="n">
-        <v>132.0066666666667</v>
+        <v>135.9588679245284</v>
       </c>
       <c r="E450" t="n">
-        <v>75.1262627118644</v>
+        <v>4.846626365961399</v>
       </c>
       <c r="F450" t="n">
         <v>-123</v>
@@ -13632,13 +13632,13 @@
         <v>115.4812398921835</v>
       </c>
       <c r="C451" t="n">
-        <v>75.16292123629111</v>
+        <v>3.414839572192506</v>
       </c>
       <c r="D451" t="n">
-        <v>132.0066666666667</v>
+        <v>135.85221361186</v>
       </c>
       <c r="E451" t="n">
-        <v>75.16292123629111</v>
+        <v>4.727310799813992</v>
       </c>
       <c r="F451" t="n">
         <v>-123</v>
@@ -13661,13 +13661,13 @@
         <v>115.374585579515</v>
       </c>
       <c r="C452" t="n">
-        <v>75.19957976071784</v>
+        <v>3.295524006045099</v>
       </c>
       <c r="D452" t="n">
-        <v>132.0066666666667</v>
+        <v>135.7455592991915</v>
       </c>
       <c r="E452" t="n">
-        <v>75.19957976071784</v>
+        <v>4.607995233666585</v>
       </c>
       <c r="F452" t="n">
         <v>-123</v>
@@ -13690,13 +13690,13 @@
         <v>115.2679312668465</v>
       </c>
       <c r="C453" t="n">
-        <v>75.23623828514457</v>
+        <v>3.176208439897692</v>
       </c>
       <c r="D453" t="n">
-        <v>132.0066666666667</v>
+        <v>135.638904986523</v>
       </c>
       <c r="E453" t="n">
-        <v>75.23623828514457</v>
+        <v>4.488679667519179</v>
       </c>
       <c r="F453" t="n">
         <v>-123</v>
@@ -13719,13 +13719,13 @@
         <v>115.1612769541781</v>
       </c>
       <c r="C454" t="n">
-        <v>75.27289680957128</v>
+        <v>3.056892873750286</v>
       </c>
       <c r="D454" t="n">
-        <v>132.0066666666667</v>
+        <v>135.5322506738545</v>
       </c>
       <c r="E454" t="n">
-        <v>75.27289680957128</v>
+        <v>4.369364101371772</v>
       </c>
       <c r="F454" t="n">
         <v>-123</v>
@@ -13748,13 +13748,13 @@
         <v>115.0546226415096</v>
       </c>
       <c r="C455" t="n">
-        <v>75.30955533399799</v>
+        <v>2.937577307602879</v>
       </c>
       <c r="D455" t="n">
-        <v>132.0066666666667</v>
+        <v>135.4255963611861</v>
       </c>
       <c r="E455" t="n">
-        <v>75.30955533399799</v>
+        <v>4.250048535224359</v>
       </c>
       <c r="F455" t="n">
         <v>-123</v>
@@ -13777,13 +13777,13 @@
         <v>114.9479683288411</v>
       </c>
       <c r="C456" t="n">
-        <v>75.34621385842472</v>
+        <v>2.818261741455473</v>
       </c>
       <c r="D456" t="n">
-        <v>132.0066666666667</v>
+        <v>135.3189420485176</v>
       </c>
       <c r="E456" t="n">
-        <v>75.34621385842472</v>
+        <v>4.130732969076952</v>
       </c>
       <c r="F456" t="n">
         <v>-123</v>
@@ -13806,13 +13806,13 @@
         <v>114.8413140161727</v>
       </c>
       <c r="C457" t="n">
-        <v>75.38287238285145</v>
+        <v>2.698946175308066</v>
       </c>
       <c r="D457" t="n">
-        <v>132.0066666666667</v>
+        <v>135.2122877358492</v>
       </c>
       <c r="E457" t="n">
-        <v>75.38287238285145</v>
+        <v>4.011417402929546</v>
       </c>
       <c r="F457" t="n">
         <v>-123</v>
@@ -13835,13 +13835,13 @@
         <v>114.7346597035042</v>
       </c>
       <c r="C458" t="n">
-        <v>75.41953090727816</v>
+        <v>2.579630609160652</v>
       </c>
       <c r="D458" t="n">
-        <v>132.0066666666667</v>
+        <v>135.1056334231807</v>
       </c>
       <c r="E458" t="n">
-        <v>75.41953090727816</v>
+        <v>3.892101836782139</v>
       </c>
       <c r="F458" t="n">
         <v>-123</v>
@@ -13864,13 +13864,13 @@
         <v>114.6280053908357</v>
       </c>
       <c r="C459" t="n">
-        <v>75.45618943170487</v>
+        <v>2.460315043013246</v>
       </c>
       <c r="D459" t="n">
-        <v>132.0066666666667</v>
+        <v>134.9989791105123</v>
       </c>
       <c r="E459" t="n">
-        <v>75.45618943170487</v>
+        <v>3.772786270634732</v>
       </c>
       <c r="F459" t="n">
         <v>-123</v>
@@ -13893,13 +13893,13 @@
         <v>114.5213510781673</v>
       </c>
       <c r="C460" t="n">
-        <v>75.4928479561316</v>
+        <v>2.340999476865839</v>
       </c>
       <c r="D460" t="n">
-        <v>132.0066666666667</v>
+        <v>134.8923247978438</v>
       </c>
       <c r="E460" t="n">
-        <v>75.4928479561316</v>
+        <v>3.653470704487326</v>
       </c>
       <c r="F460" t="n">
         <v>-123</v>
@@ -13922,13 +13922,13 @@
         <v>114.4146967654988</v>
       </c>
       <c r="C461" t="n">
-        <v>75.52950648055833</v>
+        <v>2.221683910718433</v>
       </c>
       <c r="D461" t="n">
-        <v>132.0066666666667</v>
+        <v>134.7856704851753</v>
       </c>
       <c r="E461" t="n">
-        <v>75.52950648055833</v>
+        <v>3.534155138339919</v>
       </c>
       <c r="F461" t="n">
         <v>-123</v>
@@ -13951,13 +13951,13 @@
         <v>114.3080424528303</v>
       </c>
       <c r="C462" t="n">
-        <v>75.56616500498504</v>
+        <v>2.102368344571026</v>
       </c>
       <c r="D462" t="n">
-        <v>132.0066666666667</v>
+        <v>134.6790161725069</v>
       </c>
       <c r="E462" t="n">
-        <v>75.56616500498504</v>
+        <v>3.414839572192506</v>
       </c>
       <c r="F462" t="n">
         <v>-123</v>
@@ -13980,13 +13980,13 @@
         <v>114.2013881401619</v>
       </c>
       <c r="C463" t="n">
-        <v>75.60282352941175</v>
+        <v>1.98305277842362</v>
       </c>
       <c r="D463" t="n">
-        <v>132.0066666666667</v>
+        <v>134.5723618598384</v>
       </c>
       <c r="E463" t="n">
-        <v>75.60282352941175</v>
+        <v>3.295524006045099</v>
       </c>
       <c r="F463" t="n">
         <v>-123</v>
@@ -14009,13 +14009,13 @@
         <v>114.0947338274934</v>
       </c>
       <c r="C464" t="n">
-        <v>75.63948205383848</v>
+        <v>1.863737212276213</v>
       </c>
       <c r="D464" t="n">
-        <v>132.0066666666667</v>
+        <v>134.4657075471699</v>
       </c>
       <c r="E464" t="n">
-        <v>75.63948205383848</v>
+        <v>3.176208439897692</v>
       </c>
       <c r="F464" t="n">
         <v>-123</v>
@@ -14038,13 +14038,13 @@
         <v>113.988079514825</v>
       </c>
       <c r="C465" t="n">
-        <v>75.6761405782652</v>
+        <v>1.744421646128799</v>
       </c>
       <c r="D465" t="n">
-        <v>132.0066666666667</v>
+        <v>134.3590532345015</v>
       </c>
       <c r="E465" t="n">
-        <v>75.6761405782652</v>
+        <v>3.056892873750286</v>
       </c>
       <c r="F465" t="n">
         <v>-123</v>
@@ -14067,13 +14067,13 @@
         <v>113.8814252021565</v>
       </c>
       <c r="C466" t="n">
-        <v>75.71279910269192</v>
+        <v>1.625106079981393</v>
       </c>
       <c r="D466" t="n">
-        <v>132.0066666666667</v>
+        <v>134.252398921833</v>
       </c>
       <c r="E466" t="n">
-        <v>75.71279910269192</v>
+        <v>2.937577307602879</v>
       </c>
       <c r="F466" t="n">
         <v>-123</v>
@@ -14096,13 +14096,13 @@
         <v>113.774770889488</v>
       </c>
       <c r="C467" t="n">
-        <v>75.74945762711863</v>
+        <v>1.505790513833986</v>
       </c>
       <c r="D467" t="n">
-        <v>132.0066666666667</v>
+        <v>134.1457446091646</v>
       </c>
       <c r="E467" t="n">
-        <v>75.74945762711863</v>
+        <v>2.818261741455473</v>
       </c>
       <c r="F467" t="n">
         <v>-123</v>
@@ -14125,13 +14125,13 @@
         <v>113.6681165768196</v>
       </c>
       <c r="C468" t="n">
-        <v>75.78611615154536</v>
+        <v>1.38647494768658</v>
       </c>
       <c r="D468" t="n">
-        <v>132.0066666666667</v>
+        <v>134.0390902964961</v>
       </c>
       <c r="E468" t="n">
-        <v>75.78611615154536</v>
+        <v>2.698946175308066</v>
       </c>
       <c r="F468" t="n">
         <v>-123</v>
@@ -14154,13 +14154,13 @@
         <v>113.5614622641511</v>
       </c>
       <c r="C469" t="n">
-        <v>75.82277467597208</v>
+        <v>1.267159381539173</v>
       </c>
       <c r="D469" t="n">
-        <v>132.0066666666667</v>
+        <v>133.9324359838276</v>
       </c>
       <c r="E469" t="n">
-        <v>75.82277467597208</v>
+        <v>2.579630609160652</v>
       </c>
       <c r="F469" t="n">
         <v>-123</v>
@@ -14183,13 +14183,13 @@
         <v>113.4548079514826</v>
       </c>
       <c r="C470" t="n">
-        <v>75.8594332003988</v>
+        <v>1.147843815391766</v>
       </c>
       <c r="D470" t="n">
-        <v>132.0066666666667</v>
+        <v>133.8257816711591</v>
       </c>
       <c r="E470" t="n">
-        <v>75.8594332003988</v>
+        <v>2.460315043013246</v>
       </c>
       <c r="F470" t="n">
         <v>-123</v>
@@ -14212,13 +14212,13 @@
         <v>113.3481536388142</v>
       </c>
       <c r="C471" t="n">
-        <v>75.89609172482551</v>
+        <v>1.02852824924436</v>
       </c>
       <c r="D471" t="n">
-        <v>132.0066666666667</v>
+        <v>133.7191273584907</v>
       </c>
       <c r="E471" t="n">
-        <v>75.89609172482551</v>
+        <v>2.340999476865839</v>
       </c>
       <c r="F471" t="n">
         <v>-123</v>
@@ -14241,13 +14241,13 @@
         <v>113.2414993261457</v>
       </c>
       <c r="C472" t="n">
-        <v>75.93275024925224</v>
+        <v>0.9092126830969463</v>
       </c>
       <c r="D472" t="n">
-        <v>132.0066666666667</v>
+        <v>133.6124730458222</v>
       </c>
       <c r="E472" t="n">
-        <v>75.93275024925224</v>
+        <v>2.221683910718433</v>
       </c>
       <c r="F472" t="n">
         <v>-123</v>
@@ -14270,13 +14270,13 @@
         <v>113.1348450134773</v>
       </c>
       <c r="C473" t="n">
-        <v>75.96940877367896</v>
+        <v>0.7898971169495397</v>
       </c>
       <c r="D473" t="n">
-        <v>132.0066666666667</v>
+        <v>133.5058187331538</v>
       </c>
       <c r="E473" t="n">
-        <v>75.96940877367896</v>
+        <v>2.102368344571026</v>
       </c>
       <c r="F473" t="n">
         <v>-123</v>
@@ -14299,13 +14299,13 @@
         <v>113.0281907008088</v>
       </c>
       <c r="C474" t="n">
-        <v>76.00606729810568</v>
+        <v>0.6705815508021331</v>
       </c>
       <c r="D474" t="n">
-        <v>132.0066666666667</v>
+        <v>133.3991644204853</v>
       </c>
       <c r="E474" t="n">
-        <v>76.00606729810568</v>
+        <v>1.98305277842362</v>
       </c>
       <c r="F474" t="n">
         <v>-123</v>
@@ -14328,13 +14328,13 @@
         <v>112.9215363881403</v>
       </c>
       <c r="C475" t="n">
-        <v>76.04272582253239</v>
+        <v>0.5512659846547265</v>
       </c>
       <c r="D475" t="n">
-        <v>132.0066666666667</v>
+        <v>133.2925101078168</v>
       </c>
       <c r="E475" t="n">
-        <v>76.04272582253239</v>
+        <v>1.863737212276213</v>
       </c>
       <c r="F475" t="n">
         <v>-123</v>
@@ -14357,13 +14357,13 @@
         <v>112.8148820754719</v>
       </c>
       <c r="C476" t="n">
-        <v>76.07938434695912</v>
+        <v>0.43195041850732</v>
       </c>
       <c r="D476" t="n">
-        <v>132.0066666666667</v>
+        <v>133.1858557951484</v>
       </c>
       <c r="E476" t="n">
-        <v>76.07938434695912</v>
+        <v>1.744421646128799</v>
       </c>
       <c r="F476" t="n">
         <v>-123</v>
@@ -14386,13 +14386,13 @@
         <v>112.7082277628034</v>
       </c>
       <c r="C477" t="n">
-        <v>76.11604287138584</v>
+        <v>0.3126348523599134</v>
       </c>
       <c r="D477" t="n">
-        <v>132.0066666666667</v>
+        <v>133.0792014824799</v>
       </c>
       <c r="E477" t="n">
-        <v>76.11604287138584</v>
+        <v>1.625106079981393</v>
       </c>
       <c r="F477" t="n">
         <v>-123</v>
@@ -14415,13 +14415,13 @@
         <v>112.6015734501349</v>
       </c>
       <c r="C478" t="n">
-        <v>76.15270139581256</v>
+        <v>0.1933192862125068</v>
       </c>
       <c r="D478" t="n">
-        <v>132.0066666666667</v>
+        <v>132.9725471698114</v>
       </c>
       <c r="E478" t="n">
-        <v>76.15270139581256</v>
+        <v>1.505790513833986</v>
       </c>
       <c r="F478" t="n">
         <v>-123</v>
@@ -14444,13 +14444,13 @@
         <v>112.4949191374665</v>
       </c>
       <c r="C479" t="n">
-        <v>76.18935992023927</v>
+        <v>0.07400372006509315</v>
       </c>
       <c r="D479" t="n">
-        <v>132.0066666666667</v>
+        <v>132.865892857143</v>
       </c>
       <c r="E479" t="n">
-        <v>76.18935992023927</v>
+        <v>1.38647494768658</v>
       </c>
       <c r="F479" t="n">
         <v>-123</v>
@@ -14473,13 +14473,13 @@
         <v>112.388264824798</v>
       </c>
       <c r="C480" t="n">
-        <v>76.226018444666</v>
+        <v>-0.04531184608231342</v>
       </c>
       <c r="D480" t="n">
-        <v>132.0066666666667</v>
+        <v>132.7592385444745</v>
       </c>
       <c r="E480" t="n">
-        <v>76.226018444666</v>
+        <v>1.267159381539173</v>
       </c>
       <c r="F480" t="n">
         <v>-123</v>
@@ -14502,13 +14502,13 @@
         <v>112.2816105121295</v>
       </c>
       <c r="C481" t="n">
-        <v>76.26267696909271</v>
+        <v>-0.16462741222972</v>
       </c>
       <c r="D481" t="n">
-        <v>132.0066666666667</v>
+        <v>132.6525842318061</v>
       </c>
       <c r="E481" t="n">
-        <v>76.26267696909271</v>
+        <v>1.147843815391766</v>
       </c>
       <c r="F481" t="n">
         <v>-123</v>
@@ -14531,13 +14531,13 @@
         <v>112.1749561994611</v>
       </c>
       <c r="C482" t="n">
-        <v>76.29933549351944</v>
+        <v>-0.2839429783771266</v>
       </c>
       <c r="D482" t="n">
-        <v>132.0066666666667</v>
+        <v>132.5459299191376</v>
       </c>
       <c r="E482" t="n">
-        <v>76.29933549351944</v>
+        <v>1.02852824924436</v>
       </c>
       <c r="F482" t="n">
         <v>-123</v>
@@ -14560,13 +14560,13 @@
         <v>112.0683018867926</v>
       </c>
       <c r="C483" t="n">
-        <v>76.33599401794615</v>
+        <v>-0.4032585445245331</v>
       </c>
       <c r="D483" t="n">
-        <v>132.0066666666667</v>
+        <v>132.4392756064691</v>
       </c>
       <c r="E483" t="n">
-        <v>76.33599401794615</v>
+        <v>0.9092126830969463</v>
       </c>
       <c r="F483" t="n">
         <v>-123</v>
@@ -14589,13 +14589,13 @@
         <v>111.9616475741242</v>
       </c>
       <c r="C484" t="n">
-        <v>76.37265254237288</v>
+        <v>-0.5225741106719397</v>
       </c>
       <c r="D484" t="n">
-        <v>132.0066666666667</v>
+        <v>132.3326212938007</v>
       </c>
       <c r="E484" t="n">
-        <v>76.37265254237288</v>
+        <v>0.7898971169495397</v>
       </c>
       <c r="F484" t="n">
         <v>-123</v>
@@ -14618,13 +14618,13 @@
         <v>111.8549932614557</v>
       </c>
       <c r="C485" t="n">
-        <v>76.40931106679959</v>
+        <v>-0.6418896768193463</v>
       </c>
       <c r="D485" t="n">
-        <v>132.0066666666667</v>
+        <v>132.2259669811322</v>
       </c>
       <c r="E485" t="n">
-        <v>76.40931106679959</v>
+        <v>0.6705815508021331</v>
       </c>
       <c r="F485" t="n">
         <v>-123</v>
@@ -14647,13 +14647,13 @@
         <v>111.7483389487872</v>
       </c>
       <c r="C486" t="n">
-        <v>76.44596959122632</v>
+        <v>-0.76120524296676</v>
       </c>
       <c r="D486" t="n">
-        <v>132.0066666666667</v>
+        <v>132.1193126684637</v>
       </c>
       <c r="E486" t="n">
-        <v>76.44596959122632</v>
+        <v>0.5512659846547265</v>
       </c>
       <c r="F486" t="n">
         <v>-123</v>
@@ -14676,13 +14676,13 @@
         <v>111.6416846361188</v>
       </c>
       <c r="C487" t="n">
-        <v>76.48262811565303</v>
+        <v>-0.8805208091141665</v>
       </c>
       <c r="D487" t="n">
-        <v>132.0066666666667</v>
+        <v>132.0126583557953</v>
       </c>
       <c r="E487" t="n">
-        <v>76.48262811565303</v>
+        <v>0.43195041850732</v>
       </c>
       <c r="F487" t="n">
         <v>-123</v>
@@ -14705,13 +14705,13 @@
         <v>111.5350303234503</v>
       </c>
       <c r="C488" t="n">
-        <v>76.51928664007976</v>
+        <v>-0.9998363752615731</v>
       </c>
       <c r="D488" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E488" t="n">
-        <v>76.51928664007976</v>
+        <v>0.3126348523599134</v>
       </c>
       <c r="F488" t="n">
         <v>-123</v>
@@ -14734,13 +14734,13 @@
         <v>111.4283760107818</v>
       </c>
       <c r="C489" t="n">
-        <v>76.55594516450647</v>
+        <v>-1.11915194140898</v>
       </c>
       <c r="D489" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E489" t="n">
-        <v>76.55594516450647</v>
+        <v>0.1933192862125068</v>
       </c>
       <c r="F489" t="n">
         <v>-123</v>
@@ -14763,13 +14763,13 @@
         <v>111.3217216981134</v>
       </c>
       <c r="C490" t="n">
-        <v>76.5926036889332</v>
+        <v>-1.238467507556386</v>
       </c>
       <c r="D490" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E490" t="n">
-        <v>76.5926036889332</v>
+        <v>0.07400372006509315</v>
       </c>
       <c r="F490" t="n">
         <v>-123</v>
@@ -14792,13 +14792,13 @@
         <v>111.2150673854449</v>
       </c>
       <c r="C491" t="n">
-        <v>76.62926221335991</v>
+        <v>-1.357783073703793</v>
       </c>
       <c r="D491" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E491" t="n">
-        <v>76.62926221335991</v>
+        <v>-0.04531184608231342</v>
       </c>
       <c r="F491" t="n">
         <v>-123</v>
@@ -14821,13 +14821,13 @@
         <v>111.1084130727765</v>
       </c>
       <c r="C492" t="n">
-        <v>76.66592073778664</v>
+        <v>-1.477098639851199</v>
       </c>
       <c r="D492" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E492" t="n">
-        <v>76.66592073778664</v>
+        <v>-0.16462741222972</v>
       </c>
       <c r="F492" t="n">
         <v>-123</v>
@@ -14850,13 +14850,13 @@
         <v>111.001758760108</v>
       </c>
       <c r="C493" t="n">
-        <v>76.70257926221335</v>
+        <v>-1.596414205998613</v>
       </c>
       <c r="D493" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E493" t="n">
-        <v>76.70257926221335</v>
+        <v>-0.2839429783771266</v>
       </c>
       <c r="F493" t="n">
         <v>-123</v>
@@ -14879,13 +14879,13 @@
         <v>110.8951044474395</v>
       </c>
       <c r="C494" t="n">
-        <v>76.73923778664008</v>
+        <v>-1.71572977214602</v>
       </c>
       <c r="D494" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E494" t="n">
-        <v>76.73923778664008</v>
+        <v>-0.4032585445245331</v>
       </c>
       <c r="F494" t="n">
         <v>-123</v>
@@ -14908,13 +14908,13 @@
         <v>110.7884501347711</v>
       </c>
       <c r="C495" t="n">
-        <v>76.77589631106679</v>
+        <v>-1.835045338293426</v>
       </c>
       <c r="D495" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E495" t="n">
-        <v>76.77589631106679</v>
+        <v>-0.5225741106719397</v>
       </c>
       <c r="F495" t="n">
         <v>-123</v>
@@ -14937,13 +14937,13 @@
         <v>110.6817958221026</v>
       </c>
       <c r="C496" t="n">
-        <v>76.81255483549351</v>
+        <v>-1.954360904440833</v>
       </c>
       <c r="D496" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E496" t="n">
-        <v>76.81255483549351</v>
+        <v>-0.6418896768193463</v>
       </c>
       <c r="F496" t="n">
         <v>-123</v>
@@ -14966,13 +14966,13 @@
         <v>110.5751415094341</v>
       </c>
       <c r="C497" t="n">
-        <v>76.84921335992023</v>
+        <v>-2.073676470588239</v>
       </c>
       <c r="D497" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E497" t="n">
-        <v>76.84921335992023</v>
+        <v>-0.76120524296676</v>
       </c>
       <c r="F497" t="n">
         <v>-123</v>
@@ -14995,13 +14995,13 @@
         <v>110.4684871967657</v>
       </c>
       <c r="C498" t="n">
-        <v>76.88587188434695</v>
+        <v>-2.192992036735646</v>
       </c>
       <c r="D498" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E498" t="n">
-        <v>76.88587188434695</v>
+        <v>-0.8805208091141665</v>
       </c>
       <c r="F498" t="n">
         <v>-123</v>
@@ -15024,13 +15024,13 @@
         <v>110.3618328840972</v>
       </c>
       <c r="C499" t="n">
-        <v>76.92253040877367</v>
+        <v>-2.312307602883052</v>
       </c>
       <c r="D499" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E499" t="n">
-        <v>76.92253040877367</v>
+        <v>-0.9998363752615731</v>
       </c>
       <c r="F499" t="n">
         <v>-123</v>
@@ -15053,13 +15053,13 @@
         <v>110.2551785714287</v>
       </c>
       <c r="C500" t="n">
-        <v>76.95918893320039</v>
+        <v>-2.431623169030466</v>
       </c>
       <c r="D500" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E500" t="n">
-        <v>76.95918893320039</v>
+        <v>-1.11915194140898</v>
       </c>
       <c r="F500" t="n">
         <v>-123</v>
@@ -15082,13 +15082,13 @@
         <v>110.1485242587603</v>
       </c>
       <c r="C501" t="n">
-        <v>76.99584745762711</v>
+        <v>-2.550938735177873</v>
       </c>
       <c r="D501" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E501" t="n">
-        <v>76.99584745762711</v>
+        <v>-1.238467507556386</v>
       </c>
       <c r="F501" t="n">
         <v>-123</v>
@@ -15111,13 +15111,13 @@
         <v>110.0418699460918</v>
       </c>
       <c r="C502" t="n">
-        <v>77.03250598205383</v>
+        <v>-2.670254301325279</v>
       </c>
       <c r="D502" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E502" t="n">
-        <v>77.03250598205383</v>
+        <v>-1.357783073703793</v>
       </c>
       <c r="F502" t="n">
         <v>-123</v>
@@ -15140,13 +15140,13 @@
         <v>109.9352156334234</v>
       </c>
       <c r="C503" t="n">
-        <v>77.06916450648055</v>
+        <v>-2.789569867472686</v>
       </c>
       <c r="D503" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E503" t="n">
-        <v>77.06916450648055</v>
+        <v>-1.477098639851199</v>
       </c>
       <c r="F503" t="n">
         <v>-123</v>
@@ -15169,13 +15169,13 @@
         <v>109.8285613207549</v>
       </c>
       <c r="C504" t="n">
-        <v>77.10582303090727</v>
+        <v>-2.908885433620092</v>
       </c>
       <c r="D504" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E504" t="n">
-        <v>77.10582303090727</v>
+        <v>-1.596414205998613</v>
       </c>
       <c r="F504" t="n">
         <v>-123</v>
@@ -15198,13 +15198,13 @@
         <v>109.7219070080864</v>
       </c>
       <c r="C505" t="n">
-        <v>77.14248155533399</v>
+        <v>-3.028200999767499</v>
       </c>
       <c r="D505" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E505" t="n">
-        <v>77.14248155533399</v>
+        <v>-1.71572977214602</v>
       </c>
       <c r="F505" t="n">
         <v>-123</v>
@@ -15227,13 +15227,13 @@
         <v>109.615252695418</v>
       </c>
       <c r="C506" t="n">
-        <v>77.17914007976071</v>
+        <v>-3.147516565914906</v>
       </c>
       <c r="D506" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E506" t="n">
-        <v>77.17914007976071</v>
+        <v>-1.835045338293426</v>
       </c>
       <c r="F506" t="n">
         <v>-123</v>
@@ -15256,13 +15256,13 @@
         <v>109.5085983827495</v>
       </c>
       <c r="C507" t="n">
-        <v>77.21579860418743</v>
+        <v>-3.266832132062319</v>
       </c>
       <c r="D507" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E507" t="n">
-        <v>77.21579860418743</v>
+        <v>-1.954360904440833</v>
       </c>
       <c r="F507" t="n">
         <v>-123</v>
@@ -15285,13 +15285,13 @@
         <v>109.401944070081</v>
       </c>
       <c r="C508" t="n">
-        <v>77.25245712861415</v>
+        <v>-3.386147698209726</v>
       </c>
       <c r="D508" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E508" t="n">
-        <v>77.25245712861415</v>
+        <v>-2.073676470588239</v>
       </c>
       <c r="F508" t="n">
         <v>-123</v>
@@ -15314,13 +15314,13 @@
         <v>109.2952897574126</v>
       </c>
       <c r="C509" t="n">
-        <v>77.28911565304087</v>
+        <v>-3.505463264357132</v>
       </c>
       <c r="D509" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E509" t="n">
-        <v>77.28911565304087</v>
+        <v>-2.192992036735646</v>
       </c>
       <c r="F509" t="n">
         <v>-123</v>
@@ -15343,13 +15343,13 @@
         <v>109.1886354447441</v>
       </c>
       <c r="C510" t="n">
-        <v>77.32577417746759</v>
+        <v>-3.624778830504539</v>
       </c>
       <c r="D510" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E510" t="n">
-        <v>77.32577417746759</v>
+        <v>-2.312307602883052</v>
       </c>
       <c r="F510" t="n">
         <v>-123</v>
@@ -15372,13 +15372,13 @@
         <v>109.0819811320757</v>
       </c>
       <c r="C511" t="n">
-        <v>77.36243270189431</v>
+        <v>-3.744094396651946</v>
       </c>
       <c r="D511" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E511" t="n">
-        <v>77.36243270189431</v>
+        <v>-2.431623169030466</v>
       </c>
       <c r="F511" t="n">
         <v>-123</v>
@@ -15401,13 +15401,13 @@
         <v>108.9753268194072</v>
       </c>
       <c r="C512" t="n">
-        <v>77.39909122632103</v>
+        <v>-3.863409962799352</v>
       </c>
       <c r="D512" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E512" t="n">
-        <v>77.39909122632103</v>
+        <v>-2.550938735177873</v>
       </c>
       <c r="F512" t="n">
         <v>-123</v>
@@ -15430,13 +15430,13 @@
         <v>108.8686725067387</v>
       </c>
       <c r="C513" t="n">
-        <v>77.43574975074775</v>
+        <v>-3.982725528946759</v>
       </c>
       <c r="D513" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E513" t="n">
-        <v>77.43574975074775</v>
+        <v>-2.670254301325279</v>
       </c>
       <c r="F513" t="n">
         <v>-123</v>
@@ -15459,13 +15459,13 @@
         <v>108.7620181940703</v>
       </c>
       <c r="C514" t="n">
-        <v>77.47240827517447</v>
+        <v>-4.102041095094172</v>
       </c>
       <c r="D514" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E514" t="n">
-        <v>77.47240827517447</v>
+        <v>-2.789569867472686</v>
       </c>
       <c r="F514" t="n">
         <v>-123</v>
@@ -15488,13 +15488,13 @@
         <v>108.6553638814018</v>
       </c>
       <c r="C515" t="n">
-        <v>77.50906679960119</v>
+        <v>-4.221356661241579</v>
       </c>
       <c r="D515" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E515" t="n">
-        <v>77.50906679960119</v>
+        <v>-2.908885433620092</v>
       </c>
       <c r="F515" t="n">
         <v>-123</v>
@@ -15517,13 +15517,13 @@
         <v>108.5487095687333</v>
       </c>
       <c r="C516" t="n">
-        <v>77.54572532402791</v>
+        <v>-4.340672227388986</v>
       </c>
       <c r="D516" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E516" t="n">
-        <v>77.54572532402791</v>
+        <v>-3.028200999767499</v>
       </c>
       <c r="F516" t="n">
         <v>-123</v>
@@ -15546,13 +15546,13 @@
         <v>108.4420552560649</v>
       </c>
       <c r="C517" t="n">
-        <v>77.58238384845463</v>
+        <v>-4.459987793536392</v>
       </c>
       <c r="D517" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E517" t="n">
-        <v>77.58238384845463</v>
+        <v>-3.147516565914906</v>
       </c>
       <c r="F517" t="n">
         <v>-123</v>
@@ -15575,13 +15575,13 @@
         <v>108.3354009433964</v>
       </c>
       <c r="C518" t="n">
-        <v>77.61904237288135</v>
+        <v>-4.579303359683799</v>
       </c>
       <c r="D518" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E518" t="n">
-        <v>77.61904237288135</v>
+        <v>-3.266832132062319</v>
       </c>
       <c r="F518" t="n">
         <v>-123</v>
@@ -15604,13 +15604,13 @@
         <v>108.2287466307279</v>
       </c>
       <c r="C519" t="n">
-        <v>77.65570089730807</v>
+        <v>-4.698618925831205</v>
       </c>
       <c r="D519" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E519" t="n">
-        <v>77.65570089730807</v>
+        <v>-3.386147698209726</v>
       </c>
       <c r="F519" t="n">
         <v>-123</v>
@@ -15633,13 +15633,13 @@
         <v>108.1220923180595</v>
       </c>
       <c r="C520" t="n">
-        <v>77.69235942173479</v>
+        <v>-4.817934491978612</v>
       </c>
       <c r="D520" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E520" t="n">
-        <v>77.69235942173479</v>
+        <v>-3.505463264357132</v>
       </c>
       <c r="F520" t="n">
         <v>-123</v>
@@ -15662,13 +15662,13 @@
         <v>108.015438005391</v>
       </c>
       <c r="C521" t="n">
-        <v>77.72901794616151</v>
+        <v>-4.937250058126025</v>
       </c>
       <c r="D521" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E521" t="n">
-        <v>77.72901794616151</v>
+        <v>-3.624778830504539</v>
       </c>
       <c r="F521" t="n">
         <v>-123</v>
@@ -15691,13 +15691,13 @@
         <v>107.9087836927226</v>
       </c>
       <c r="C522" t="n">
-        <v>77.76567647058823</v>
+        <v>-5.056565624273432</v>
       </c>
       <c r="D522" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E522" t="n">
-        <v>77.76567647058823</v>
+        <v>-3.744094396651946</v>
       </c>
       <c r="F522" t="n">
         <v>-123</v>
@@ -15720,13 +15720,13 @@
         <v>107.8021293800541</v>
       </c>
       <c r="C523" t="n">
-        <v>77.80233499501495</v>
+        <v>-5.175881190420839</v>
       </c>
       <c r="D523" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E523" t="n">
-        <v>77.80233499501495</v>
+        <v>-3.863409962799352</v>
       </c>
       <c r="F523" t="n">
         <v>-123</v>
@@ -15749,13 +15749,13 @@
         <v>107.6954750673856</v>
       </c>
       <c r="C524" t="n">
-        <v>77.83899351944167</v>
+        <v>-5.295196756568245</v>
       </c>
       <c r="D524" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E524" t="n">
-        <v>77.83899351944167</v>
+        <v>-3.982725528946759</v>
       </c>
       <c r="F524" t="n">
         <v>-123</v>
@@ -15778,13 +15778,13 @@
         <v>107.5888207547172</v>
       </c>
       <c r="C525" t="n">
-        <v>77.87565204386839</v>
+        <v>-5.414512322715652</v>
       </c>
       <c r="D525" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E525" t="n">
-        <v>77.87565204386839</v>
+        <v>-4.102041095094172</v>
       </c>
       <c r="F525" t="n">
         <v>-123</v>
@@ -15807,13 +15807,13 @@
         <v>107.4821664420487</v>
       </c>
       <c r="C526" t="n">
-        <v>77.91231056829511</v>
+        <v>-5.533827888863058</v>
       </c>
       <c r="D526" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E526" t="n">
-        <v>77.91231056829511</v>
+        <v>-4.221356661241579</v>
       </c>
       <c r="F526" t="n">
         <v>-123</v>
@@ -15836,13 +15836,13 @@
         <v>107.3755121293802</v>
       </c>
       <c r="C527" t="n">
-        <v>77.94896909272182</v>
+        <v>-5.653143455010465</v>
       </c>
       <c r="D527" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E527" t="n">
-        <v>77.94896909272182</v>
+        <v>-4.340672227388986</v>
       </c>
       <c r="F527" t="n">
         <v>-123</v>
@@ -15865,13 +15865,13 @@
         <v>107.2688578167118</v>
       </c>
       <c r="C528" t="n">
-        <v>77.98562761714854</v>
+        <v>-5.772459021157871</v>
       </c>
       <c r="D528" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E528" t="n">
-        <v>77.98562761714854</v>
+        <v>-4.459987793536392</v>
       </c>
       <c r="F528" t="n">
         <v>-123</v>
@@ -15894,13 +15894,13 @@
         <v>107.1622035040433</v>
       </c>
       <c r="C529" t="n">
-        <v>78.02228614157526</v>
+        <v>-5.891774587305278</v>
       </c>
       <c r="D529" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E529" t="n">
-        <v>78.02228614157526</v>
+        <v>-4.579303359683799</v>
       </c>
       <c r="F529" t="n">
         <v>-123</v>
@@ -15923,13 +15923,13 @@
         <v>107.0555491913749</v>
       </c>
       <c r="C530" t="n">
-        <v>78.05894466600199</v>
+        <v>-6.011090153452685</v>
       </c>
       <c r="D530" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E530" t="n">
-        <v>78.05894466600199</v>
+        <v>-4.698618925831205</v>
       </c>
       <c r="F530" t="n">
         <v>-123</v>
@@ -15952,13 +15952,13 @@
         <v>106.9488948787064</v>
       </c>
       <c r="C531" t="n">
-        <v>78.0956031904287</v>
+        <v>-6.130405719600091</v>
       </c>
       <c r="D531" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E531" t="n">
-        <v>78.0956031904287</v>
+        <v>-4.817934491978612</v>
       </c>
       <c r="F531" t="n">
         <v>-123</v>
@@ -15981,13 +15981,13 @@
         <v>106.8422405660379</v>
       </c>
       <c r="C532" t="n">
-        <v>78.13226171485542</v>
+        <v>-6.249721285747512</v>
       </c>
       <c r="D532" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E532" t="n">
-        <v>78.13226171485542</v>
+        <v>-4.937250058126025</v>
       </c>
       <c r="F532" t="n">
         <v>-123</v>
@@ -16010,13 +16010,13 @@
         <v>106.7355862533695</v>
       </c>
       <c r="C533" t="n">
-        <v>78.16892023928214</v>
+        <v>-6.369036851894919</v>
       </c>
       <c r="D533" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E533" t="n">
-        <v>78.16892023928214</v>
+        <v>-5.056565624273432</v>
       </c>
       <c r="F533" t="n">
         <v>-123</v>
@@ -16039,13 +16039,13 @@
         <v>106.628931940701</v>
       </c>
       <c r="C534" t="n">
-        <v>78.20557876370887</v>
+        <v>-6.488352418042325</v>
       </c>
       <c r="D534" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E534" t="n">
-        <v>78.20557876370887</v>
+        <v>-5.175881190420839</v>
       </c>
       <c r="F534" t="n">
         <v>-123</v>
@@ -16068,13 +16068,13 @@
         <v>106.5222776280325</v>
       </c>
       <c r="C535" t="n">
-        <v>78.24223728813558</v>
+        <v>-6.607667984189732</v>
       </c>
       <c r="D535" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E535" t="n">
-        <v>78.24223728813558</v>
+        <v>-5.295196756568245</v>
       </c>
       <c r="F535" t="n">
         <v>-123</v>
@@ -16097,13 +16097,13 @@
         <v>106.4156233153641</v>
       </c>
       <c r="C536" t="n">
-        <v>78.2788958125623</v>
+        <v>-6.726983550337138</v>
       </c>
       <c r="D536" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E536" t="n">
-        <v>78.2788958125623</v>
+        <v>-5.414512322715652</v>
       </c>
       <c r="F536" t="n">
         <v>-123</v>
@@ -16126,13 +16126,13 @@
         <v>106.3089690026956</v>
       </c>
       <c r="C537" t="n">
-        <v>78.31555433698902</v>
+        <v>-6.846299116484545</v>
       </c>
       <c r="D537" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E537" t="n">
-        <v>78.31555433698902</v>
+        <v>-5.533827888863058</v>
       </c>
       <c r="F537" t="n">
         <v>-123</v>
@@ -16155,13 +16155,13 @@
         <v>106.2023146900271</v>
       </c>
       <c r="C538" t="n">
-        <v>78.35221286141575</v>
+        <v>-6.965614682631951</v>
       </c>
       <c r="D538" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E538" t="n">
-        <v>78.35221286141575</v>
+        <v>-5.653143455010465</v>
       </c>
       <c r="F538" t="n">
         <v>-123</v>
@@ -16184,13 +16184,13 @@
         <v>106.0956603773587</v>
       </c>
       <c r="C539" t="n">
-        <v>78.38887138584246</v>
+        <v>-7.084930248779358</v>
       </c>
       <c r="D539" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E539" t="n">
-        <v>78.38887138584246</v>
+        <v>-5.772459021157871</v>
       </c>
       <c r="F539" t="n">
         <v>-123</v>
@@ -16213,13 +16213,13 @@
         <v>105.9890060646902</v>
       </c>
       <c r="C540" t="n">
-        <v>78.42552991026918</v>
+        <v>-7.204245814926765</v>
       </c>
       <c r="D540" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E540" t="n">
-        <v>78.42552991026918</v>
+        <v>-5.891774587305278</v>
       </c>
       <c r="F540" t="n">
         <v>-123</v>
@@ -16242,13 +16242,13 @@
         <v>105.8823517520217</v>
       </c>
       <c r="C541" t="n">
-        <v>78.4621884346959</v>
+        <v>-7.323561381074171</v>
       </c>
       <c r="D541" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E541" t="n">
-        <v>78.4621884346959</v>
+        <v>-6.011090153452685</v>
       </c>
       <c r="F541" t="n">
         <v>-123</v>
@@ -16271,13 +16271,13 @@
         <v>105.7756974393533</v>
       </c>
       <c r="C542" t="n">
-        <v>78.49884695912263</v>
+        <v>-7.442876947221578</v>
       </c>
       <c r="D542" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E542" t="n">
-        <v>78.49884695912263</v>
+        <v>-6.130405719600091</v>
       </c>
       <c r="F542" t="n">
         <v>-123</v>
@@ -16300,13 +16300,13 @@
         <v>105.6690431266848</v>
       </c>
       <c r="C543" t="n">
-        <v>78.53550548354934</v>
+        <v>-7.562192513368984</v>
       </c>
       <c r="D543" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E543" t="n">
-        <v>78.53550548354934</v>
+        <v>-6.249721285747512</v>
       </c>
       <c r="F543" t="n">
         <v>-123</v>
@@ -16329,13 +16329,13 @@
         <v>105.5623888140164</v>
       </c>
       <c r="C544" t="n">
-        <v>78.57216400797606</v>
+        <v>-7.681508079516391</v>
       </c>
       <c r="D544" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E544" t="n">
-        <v>78.57216400797606</v>
+        <v>-6.369036851894919</v>
       </c>
       <c r="F544" t="n">
         <v>-123</v>
@@ -16358,13 +16358,13 @@
         <v>105.4557345013479</v>
       </c>
       <c r="C545" t="n">
-        <v>78.60882253240278</v>
+        <v>-7.800823645663797</v>
       </c>
       <c r="D545" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E545" t="n">
-        <v>78.60882253240278</v>
+        <v>-6.488352418042325</v>
       </c>
       <c r="F545" t="n">
         <v>-123</v>
@@ -16387,13 +16387,13 @@
         <v>105.3490801886794</v>
       </c>
       <c r="C546" t="n">
-        <v>78.64548105682951</v>
+        <v>-7.920139211811218</v>
       </c>
       <c r="D546" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E546" t="n">
-        <v>78.64548105682951</v>
+        <v>-6.607667984189732</v>
       </c>
       <c r="F546" t="n">
         <v>-123</v>
@@ -16416,13 +16416,13 @@
         <v>105.242425876011</v>
       </c>
       <c r="C547" t="n">
-        <v>78.68213958125622</v>
+        <v>-8.039454777958625</v>
       </c>
       <c r="D547" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E547" t="n">
-        <v>78.68213958125622</v>
+        <v>-6.726983550337138</v>
       </c>
       <c r="F547" t="n">
         <v>-123</v>
@@ -16445,13 +16445,13 @@
         <v>105.1357715633425</v>
       </c>
       <c r="C548" t="n">
-        <v>78.71879810568294</v>
+        <v>-8.158770344106031</v>
       </c>
       <c r="D548" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E548" t="n">
-        <v>78.71879810568294</v>
+        <v>-6.846299116484545</v>
       </c>
       <c r="F548" t="n">
         <v>-123</v>
@@ -16474,13 +16474,13 @@
         <v>105.029117250674</v>
       </c>
       <c r="C549" t="n">
-        <v>78.75545663010966</v>
+        <v>-8.278085910253438</v>
       </c>
       <c r="D549" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E549" t="n">
-        <v>78.75545663010966</v>
+        <v>-6.965614682631951</v>
       </c>
       <c r="F549" t="n">
         <v>-123</v>
@@ -16503,13 +16503,13 @@
         <v>104.9224629380056</v>
       </c>
       <c r="C550" t="n">
-        <v>78.79211515453639</v>
+        <v>-8.397401476400844</v>
       </c>
       <c r="D550" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E550" t="n">
-        <v>78.79211515453639</v>
+        <v>-7.084930248779358</v>
       </c>
       <c r="F550" t="n">
         <v>-123</v>
@@ -16532,13 +16532,13 @@
         <v>104.8158086253371</v>
       </c>
       <c r="C551" t="n">
-        <v>78.8287736789631</v>
+        <v>-8.516717042548251</v>
       </c>
       <c r="D551" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E551" t="n">
-        <v>78.8287736789631</v>
+        <v>-7.204245814926765</v>
       </c>
       <c r="F551" t="n">
         <v>-123</v>
@@ -16561,13 +16561,13 @@
         <v>104.7091543126687</v>
       </c>
       <c r="C552" t="n">
-        <v>78.86543220338982</v>
+        <v>-8.636032608695658</v>
       </c>
       <c r="D552" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E552" t="n">
-        <v>78.86543220338982</v>
+        <v>-7.323561381074171</v>
       </c>
       <c r="F552" t="n">
         <v>-123</v>
@@ -16590,13 +16590,13 @@
         <v>104.6025000000002</v>
       </c>
       <c r="C553" t="n">
-        <v>78.90209072781654</v>
+        <v>-8.755348174843064</v>
       </c>
       <c r="D553" t="n">
         <v>132.0066666666667</v>
       </c>
       <c r="E553" t="n">
-        <v>78.90209072781654</v>
+        <v>-7.442876947221578</v>
       </c>
       <c r="F553" t="n">
         <v>-123</v>
